--- a/Solutions/Day_4_stats _assignment.xlsx
+++ b/Solutions/Day_4_stats _assignment.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="27928"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="28324"/>
   <workbookPr defaultThemeVersion="166925"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\ANANYA SAXENA\Desktop\REVAMP ASSIGNMENT\Solutions\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\ANANYA SAXENA\Downloads\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{F9947C0A-717C-4012-BB1F-2B71E1D212A1}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{A40E4BBF-D653-42B6-8F00-D684F580A2CF}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" activeTab="2" xr2:uid="{CE3B3D7E-0BE9-4D5A-A54B-1240C4612186}"/>
+    <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" activeTab="4" xr2:uid="{CE3B3D7E-0BE9-4D5A-A54B-1240C4612186}"/>
   </bookViews>
   <sheets>
     <sheet name="Dataset" sheetId="1" r:id="rId1"/>
@@ -63,7 +63,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="4128" uniqueCount="495">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="4130" uniqueCount="497">
   <si>
     <t>Customer ID</t>
   </si>
@@ -1718,9 +1718,6 @@
     <t>LARGEST ACCOUNT BALANCE=LARGE(Dataset!G2:G350,1)</t>
   </si>
   <si>
-    <t>total client's who meets this critearia are=COUNTIFS(Dataset!D2:D350,"&gt;30",Dataset!N2:N350,Dataset!N337,Dataset!M2:M350,Dataset!M334)</t>
-  </si>
-  <si>
     <t>Mode=MODE.SNGL(Dataset!K2:K350)</t>
   </si>
   <si>
@@ -1745,9 +1742,6 @@
     <t>Non-Borrowers’ Smallest Balance: The bank’s savings team is conducting a study on customers who haven’t taken out any loans. As part of this, they need you to find the 3rd smallest account balance among these non-borrowers. Can you provide the data?</t>
   </si>
   <si>
-    <t>the 3rd smallest account balance among non-borrowers=SMALL(IF(Dataset!I2:I350="No",Dataset!G2:G350),3)</t>
-  </si>
-  <si>
     <t>Premium Members’ Largest Balances: SwiftBank is offering exclusive rewards to clients with premium memberships and high account balances. Your task is to find the 4th largest account balance among customers who hold premium memberships. Can you help identify this group?</t>
   </si>
   <si>
@@ -1847,9 +1841,6 @@
     <t>Inactive Female Clients’ Minimum Balance: The marketing team is preparing a new campaign targeting inactive online banking users. They need you to find the minimum account balance for female clients who are not using online banking. Additionally, they need to know how many female clients are active versus inactive in online banking. Can you provide this information?</t>
   </si>
   <si>
-    <t xml:space="preserve"> the minimum account balance for female clients who are not using online banking=MINIFS(Dataset!G2:G350,Dataset!E2:E350,Dataset!E330,Dataset!N2:N350,Dataset!N339)</t>
-  </si>
-  <si>
     <t>female clients are active versus inactive in online banking=COUNTIF(Dataset!N2:N350,Dataset!N337)</t>
   </si>
   <si>
@@ -2028,13 +2019,28 @@
   </si>
   <si>
     <t>income above 6k</t>
+  </si>
+  <si>
+    <t>LARGE(UNIQUE(Dataset!K2:K350),3)</t>
+  </si>
+  <si>
+    <t>0r</t>
+  </si>
+  <si>
+    <t>total client's who meets this critearia are=COUNTIFS(Dataset!E2:E350,Dataset!E3,Dataset!D2:D350,"&gt;30",Dataset!N2:N350,Dataset!N2,Dataset!M2:M350,"&lt;&gt;none")</t>
+  </si>
+  <si>
+    <t>the 3rd smallest account balance among non-borrowers=SMALL(UNIQUE(IF(Dataset!I2:I350="no",Dataset!G2:G350)),3)</t>
+  </si>
+  <si>
+    <t xml:space="preserve"> the minimum account balance for female clients who are not using online banking=MINIFS(Dataset!G2:G350,Dataset!E2:E350,"F",Dataset!N2:N350,"Inactive")</t>
   </si>
 </sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
-  <fonts count="5" x14ac:knownFonts="1">
+  <fonts count="6" x14ac:knownFonts="1">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -2075,8 +2081,14 @@
       <family val="2"/>
       <scheme val="minor"/>
     </font>
+    <font>
+      <sz val="11"/>
+      <name val="Calibri"/>
+      <family val="2"/>
+      <scheme val="minor"/>
+    </font>
   </fonts>
-  <fills count="4">
+  <fills count="5">
     <fill>
       <patternFill patternType="none"/>
     </fill>
@@ -2095,6 +2107,12 @@
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="5"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
   </fills>
   <borders count="1">
     <border>
@@ -2108,7 +2126,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="13">
+  <cellXfs count="15">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
@@ -2136,6 +2154,8 @@
     <xf numFmtId="0" fontId="0" fillId="3" borderId="0" xfId="0" applyFill="1" applyAlignment="1">
       <alignment vertical="center"/>
     </xf>
+    <xf numFmtId="0" fontId="5" fillId="4" borderId="0" xfId="0" applyFont="1" applyFill="1"/>
+    <xf numFmtId="0" fontId="0" fillId="4" borderId="0" xfId="0" applyFill="1"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
@@ -2531,7 +2551,7 @@
         <v>346</v>
       </c>
       <c r="Q1" s="9" t="s">
-        <v>470</v>
+        <v>467</v>
       </c>
       <c r="R1" s="1" t="s">
         <v>362</v>
@@ -2540,49 +2560,49 @@
         <v>363</v>
       </c>
       <c r="T1" s="9" t="s">
-        <v>469</v>
+        <v>466</v>
       </c>
       <c r="U1" s="1" t="s">
         <v>368</v>
       </c>
       <c r="V1" s="9" t="s">
-        <v>471</v>
+        <v>468</v>
       </c>
       <c r="W1" s="1" t="s">
         <v>371</v>
       </c>
       <c r="X1" s="9" t="s">
-        <v>472</v>
+        <v>469</v>
       </c>
       <c r="Y1" s="1" t="s">
+        <v>470</v>
+      </c>
+      <c r="Z1" s="10" t="s">
         <v>473</v>
-      </c>
-      <c r="Z1" s="10" t="s">
-        <v>476</v>
       </c>
       <c r="AA1" s="7" t="s">
         <v>366</v>
       </c>
       <c r="AB1" t="s">
-        <v>477</v>
+        <v>474</v>
       </c>
       <c r="AD1" s="7" t="s">
-        <v>471</v>
+        <v>468</v>
       </c>
       <c r="AE1" t="s">
-        <v>478</v>
+        <v>475</v>
       </c>
       <c r="AF1" s="7" t="s">
         <v>374</v>
       </c>
       <c r="AG1" t="s">
-        <v>479</v>
+        <v>476</v>
       </c>
       <c r="AH1" s="7" t="s">
         <v>376</v>
       </c>
       <c r="AI1" t="s">
-        <v>480</v>
+        <v>477</v>
       </c>
       <c r="AL1" s="11" t="s">
         <v>99</v>
@@ -2591,40 +2611,40 @@
         <v>349</v>
       </c>
       <c r="AN1" t="s">
-        <v>481</v>
+        <v>478</v>
       </c>
       <c r="AP1" s="7" t="s">
         <v>354</v>
       </c>
       <c r="AQ1" t="s">
-        <v>482</v>
+        <v>479</v>
       </c>
       <c r="AS1" s="7" t="s">
         <v>356</v>
       </c>
       <c r="AT1" t="s">
-        <v>484</v>
+        <v>481</v>
       </c>
       <c r="AU1" t="s">
-        <v>483</v>
+        <v>480</v>
       </c>
       <c r="AW1" s="8" t="s">
         <v>357</v>
       </c>
       <c r="AX1" s="8" t="s">
-        <v>488</v>
+        <v>485</v>
       </c>
       <c r="AY1" s="8" t="s">
-        <v>477</v>
+        <v>474</v>
       </c>
       <c r="AZ1" s="8" t="s">
-        <v>487</v>
+        <v>484</v>
       </c>
       <c r="BC1" s="7" t="s">
         <v>380</v>
       </c>
       <c r="BD1" t="s">
-        <v>494</v>
+        <v>491</v>
       </c>
     </row>
     <row r="2" spans="1:56" x14ac:dyDescent="0.3">
@@ -2718,17 +2738,17 @@
         <v>good_client</v>
       </c>
       <c r="AS2" t="s">
-        <v>485</v>
+        <v>482</v>
       </c>
       <c r="AT2" t="str">
         <f>IF(AND(Dataset!F2="Savings",Dataset!AS2="eligible"),"YES","NO")</f>
         <v>NO</v>
       </c>
       <c r="AW2" s="12" t="s">
-        <v>490</v>
+        <v>487</v>
       </c>
       <c r="AX2" s="8" t="s">
-        <v>492</v>
+        <v>489</v>
       </c>
       <c r="AY2" s="8" t="str">
         <f>IF(AND(AW2="yes",AX2="Good_user"),"inprogress","not_inprogress")</f>
@@ -2830,17 +2850,17 @@
         <v>bad_client</v>
       </c>
       <c r="AS3" t="s">
-        <v>485</v>
+        <v>482</v>
       </c>
       <c r="AT3" t="str">
         <f>IF(AND(Dataset!F3="Savings",Dataset!AS3="eligible"),"YES","NO")</f>
         <v>NO</v>
       </c>
       <c r="AW3" s="12" t="s">
+        <v>487</v>
+      </c>
+      <c r="AX3" s="8" t="s">
         <v>490</v>
-      </c>
-      <c r="AX3" s="8" t="s">
-        <v>493</v>
       </c>
       <c r="AY3" s="8"/>
       <c r="AZ3" s="8"/>
@@ -2939,17 +2959,17 @@
         <v>bad_client</v>
       </c>
       <c r="AS4" t="s">
-        <v>485</v>
+        <v>482</v>
       </c>
       <c r="AT4" t="str">
         <f>IF(AND(Dataset!F4="Savings",Dataset!AS4="eligible"),"YES","NO")</f>
         <v>NO</v>
       </c>
       <c r="AW4" s="12" t="s">
+        <v>486</v>
+      </c>
+      <c r="AX4" s="8" t="s">
         <v>489</v>
-      </c>
-      <c r="AX4" s="8" t="s">
-        <v>492</v>
       </c>
       <c r="AY4" s="8"/>
       <c r="AZ4" s="8"/>
@@ -3048,17 +3068,17 @@
         <v>bad_client</v>
       </c>
       <c r="AS5" t="s">
-        <v>485</v>
+        <v>482</v>
       </c>
       <c r="AT5" t="str">
         <f>IF(AND(Dataset!F5="Savings",Dataset!AS5="eligible"),"YES","NO")</f>
         <v>NO</v>
       </c>
       <c r="AW5" s="12" t="s">
-        <v>490</v>
+        <v>487</v>
       </c>
       <c r="AX5" s="8" t="s">
-        <v>492</v>
+        <v>489</v>
       </c>
       <c r="AY5" s="8"/>
       <c r="AZ5" s="8"/>
@@ -3157,17 +3177,17 @@
         <v>bad_client</v>
       </c>
       <c r="AS6" t="s">
-        <v>485</v>
+        <v>482</v>
       </c>
       <c r="AT6" t="str">
         <f>IF(AND(Dataset!F6="Savings",Dataset!AS6="eligible"),"YES","NO")</f>
         <v>NO</v>
       </c>
       <c r="AW6" s="12" t="s">
+        <v>487</v>
+      </c>
+      <c r="AX6" s="8" t="s">
         <v>490</v>
-      </c>
-      <c r="AX6" s="8" t="s">
-        <v>493</v>
       </c>
       <c r="AY6" s="8"/>
       <c r="AZ6" s="8"/>
@@ -3266,17 +3286,17 @@
         <v>bad_client</v>
       </c>
       <c r="AS7" t="s">
-        <v>485</v>
+        <v>482</v>
       </c>
       <c r="AT7" t="str">
         <f>IF(AND(Dataset!F7="Savings",Dataset!AS7="eligible"),"YES","NO")</f>
         <v>NO</v>
       </c>
       <c r="AW7" s="12" t="s">
-        <v>490</v>
+        <v>487</v>
       </c>
       <c r="AX7" s="8" t="s">
-        <v>492</v>
+        <v>489</v>
       </c>
       <c r="AY7" s="8"/>
       <c r="AZ7" s="8"/>
@@ -3375,17 +3395,17 @@
         <v>bad_client</v>
       </c>
       <c r="AS8" t="s">
-        <v>485</v>
+        <v>482</v>
       </c>
       <c r="AT8" t="str">
         <f>IF(AND(Dataset!F8="Savings",Dataset!AS8="eligible"),"YES","NO")</f>
         <v>NO</v>
       </c>
       <c r="AW8" s="12" t="s">
+        <v>487</v>
+      </c>
+      <c r="AX8" s="8" t="s">
         <v>490</v>
-      </c>
-      <c r="AX8" s="8" t="s">
-        <v>493</v>
       </c>
       <c r="AY8" s="8"/>
       <c r="AZ8" s="8"/>
@@ -3484,17 +3504,17 @@
         <v>bad_client</v>
       </c>
       <c r="AS9" t="s">
-        <v>485</v>
+        <v>482</v>
       </c>
       <c r="AT9" t="str">
         <f>IF(AND(Dataset!F9="Savings",Dataset!AS9="eligible"),"YES","NO")</f>
         <v>NO</v>
       </c>
       <c r="AW9" s="12" t="s">
-        <v>490</v>
+        <v>487</v>
       </c>
       <c r="AX9" s="8" t="s">
-        <v>492</v>
+        <v>489</v>
       </c>
       <c r="AY9" s="8"/>
       <c r="AZ9" s="8"/>
@@ -3593,17 +3613,17 @@
         <v>bad_client</v>
       </c>
       <c r="AS10" t="s">
-        <v>485</v>
+        <v>482</v>
       </c>
       <c r="AT10" t="str">
         <f>IF(AND(Dataset!F10="Savings",Dataset!AS10="eligible"),"YES","NO")</f>
         <v>NO</v>
       </c>
       <c r="AW10" s="12" t="s">
-        <v>490</v>
+        <v>487</v>
       </c>
       <c r="AX10" s="8" t="s">
-        <v>492</v>
+        <v>489</v>
       </c>
       <c r="AY10" s="8"/>
       <c r="AZ10" s="8"/>
@@ -3702,17 +3722,17 @@
         <v>bad_client</v>
       </c>
       <c r="AS11" t="s">
-        <v>485</v>
+        <v>482</v>
       </c>
       <c r="AT11" t="str">
         <f>IF(AND(Dataset!F11="Savings",Dataset!AS11="eligible"),"YES","NO")</f>
         <v>NO</v>
       </c>
       <c r="AW11" s="12" t="s">
-        <v>489</v>
+        <v>486</v>
       </c>
       <c r="AX11" s="8" t="s">
-        <v>493</v>
+        <v>490</v>
       </c>
       <c r="AY11" s="8"/>
       <c r="AZ11" s="8"/>
@@ -3811,17 +3831,17 @@
         <v>bad_client</v>
       </c>
       <c r="AS12" t="s">
-        <v>485</v>
+        <v>482</v>
       </c>
       <c r="AT12" t="str">
         <f>IF(AND(Dataset!F12="Savings",Dataset!AS12="eligible"),"YES","NO")</f>
         <v>NO</v>
       </c>
       <c r="AW12" s="12" t="s">
-        <v>490</v>
+        <v>487</v>
       </c>
       <c r="AX12" s="8" t="s">
-        <v>492</v>
+        <v>489</v>
       </c>
       <c r="AY12" s="8"/>
       <c r="AZ12" s="8"/>
@@ -3920,17 +3940,17 @@
         <v>bad_client</v>
       </c>
       <c r="AS13" t="s">
-        <v>485</v>
+        <v>482</v>
       </c>
       <c r="AT13" t="str">
         <f>IF(AND(Dataset!F13="Savings",Dataset!AS13="eligible"),"YES","NO")</f>
         <v>NO</v>
       </c>
       <c r="AW13" s="12" t="s">
-        <v>491</v>
+        <v>488</v>
       </c>
       <c r="AX13" s="8" t="s">
-        <v>492</v>
+        <v>489</v>
       </c>
       <c r="AY13" s="8"/>
       <c r="AZ13" s="8"/>
@@ -4029,17 +4049,17 @@
         <v>bad_client</v>
       </c>
       <c r="AS14" t="s">
-        <v>485</v>
+        <v>482</v>
       </c>
       <c r="AT14" t="str">
         <f>IF(AND(Dataset!F14="Savings",Dataset!AS14="eligible"),"YES","NO")</f>
         <v>NO</v>
       </c>
       <c r="AW14" s="12" t="s">
+        <v>487</v>
+      </c>
+      <c r="AX14" s="8" t="s">
         <v>490</v>
-      </c>
-      <c r="AX14" s="8" t="s">
-        <v>493</v>
       </c>
       <c r="AY14" s="8"/>
       <c r="AZ14" s="8"/>
@@ -4138,17 +4158,17 @@
         <v>bad_client</v>
       </c>
       <c r="AS15" t="s">
-        <v>485</v>
+        <v>482</v>
       </c>
       <c r="AT15" t="str">
         <f>IF(AND(Dataset!F15="Savings",Dataset!AS15="eligible"),"YES","NO")</f>
         <v>NO</v>
       </c>
       <c r="AW15" s="12" t="s">
-        <v>490</v>
+        <v>487</v>
       </c>
       <c r="AX15" s="8" t="s">
-        <v>492</v>
+        <v>489</v>
       </c>
       <c r="AY15" s="8"/>
       <c r="AZ15" s="8"/>
@@ -4247,17 +4267,17 @@
         <v>bad_client</v>
       </c>
       <c r="AS16" t="s">
-        <v>485</v>
+        <v>482</v>
       </c>
       <c r="AT16" t="str">
         <f>IF(AND(Dataset!F16="Savings",Dataset!AS16="eligible"),"YES","NO")</f>
         <v>NO</v>
       </c>
       <c r="AW16" s="12" t="s">
-        <v>489</v>
+        <v>486</v>
       </c>
       <c r="AX16" s="8" t="s">
-        <v>493</v>
+        <v>490</v>
       </c>
       <c r="AY16" s="8"/>
       <c r="AZ16" s="8"/>
@@ -4356,17 +4376,17 @@
         <v>bad_client</v>
       </c>
       <c r="AS17" t="s">
-        <v>485</v>
+        <v>482</v>
       </c>
       <c r="AT17" t="str">
         <f>IF(AND(Dataset!F17="Savings",Dataset!AS17="eligible"),"YES","NO")</f>
         <v>NO</v>
       </c>
       <c r="AW17" s="12" t="s">
-        <v>490</v>
+        <v>487</v>
       </c>
       <c r="AX17" s="8" t="s">
-        <v>492</v>
+        <v>489</v>
       </c>
       <c r="AY17" s="8"/>
       <c r="AZ17" s="8"/>
@@ -4465,17 +4485,17 @@
         <v>good_client</v>
       </c>
       <c r="AS18" t="s">
-        <v>485</v>
+        <v>482</v>
       </c>
       <c r="AT18" t="str">
         <f>IF(AND(Dataset!F18="Savings",Dataset!AS18="eligible"),"YES","NO")</f>
         <v>NO</v>
       </c>
       <c r="AW18" s="12" t="s">
+        <v>487</v>
+      </c>
+      <c r="AX18" s="8" t="s">
         <v>490</v>
-      </c>
-      <c r="AX18" s="8" t="s">
-        <v>493</v>
       </c>
       <c r="AY18" s="8"/>
       <c r="AZ18" s="8"/>
@@ -4574,17 +4594,17 @@
         <v>bad_client</v>
       </c>
       <c r="AS19" t="s">
-        <v>485</v>
+        <v>482</v>
       </c>
       <c r="AT19" t="str">
         <f>IF(AND(Dataset!F19="Savings",Dataset!AS19="eligible"),"YES","NO")</f>
         <v>NO</v>
       </c>
       <c r="AW19" s="12" t="s">
+        <v>486</v>
+      </c>
+      <c r="AX19" s="8" t="s">
         <v>489</v>
-      </c>
-      <c r="AX19" s="8" t="s">
-        <v>492</v>
       </c>
       <c r="AY19" s="8"/>
       <c r="AZ19" s="8"/>
@@ -4683,17 +4703,17 @@
         <v>bad_client</v>
       </c>
       <c r="AS20" t="s">
-        <v>485</v>
+        <v>482</v>
       </c>
       <c r="AT20" t="str">
         <f>IF(AND(Dataset!F20="Savings",Dataset!AS20="eligible"),"YES","NO")</f>
         <v>NO</v>
       </c>
       <c r="AW20" s="12" t="s">
+        <v>487</v>
+      </c>
+      <c r="AX20" s="8" t="s">
         <v>490</v>
-      </c>
-      <c r="AX20" s="8" t="s">
-        <v>493</v>
       </c>
       <c r="AY20" s="8"/>
       <c r="AZ20" s="8"/>
@@ -4792,17 +4812,17 @@
         <v>bad_client</v>
       </c>
       <c r="AS21" t="s">
-        <v>485</v>
+        <v>482</v>
       </c>
       <c r="AT21" t="str">
         <f>IF(AND(Dataset!F21="Savings",Dataset!AS21="eligible"),"YES","NO")</f>
         <v>NO</v>
       </c>
       <c r="AW21" s="12" t="s">
+        <v>486</v>
+      </c>
+      <c r="AX21" s="8" t="s">
         <v>489</v>
-      </c>
-      <c r="AX21" s="8" t="s">
-        <v>492</v>
       </c>
       <c r="AY21" s="8"/>
       <c r="AZ21" s="8"/>
@@ -4901,17 +4921,17 @@
         <v>bad_client</v>
       </c>
       <c r="AS22" t="s">
-        <v>485</v>
+        <v>482</v>
       </c>
       <c r="AT22" t="str">
         <f>IF(AND(Dataset!F22="Savings",Dataset!AS22="eligible"),"YES","NO")</f>
         <v>NO</v>
       </c>
       <c r="AW22" s="12" t="s">
+        <v>487</v>
+      </c>
+      <c r="AX22" s="8" t="s">
         <v>490</v>
-      </c>
-      <c r="AX22" s="8" t="s">
-        <v>493</v>
       </c>
       <c r="AY22" s="8"/>
       <c r="AZ22" s="8"/>
@@ -5010,17 +5030,17 @@
         <v>bad_client</v>
       </c>
       <c r="AS23" t="s">
-        <v>485</v>
+        <v>482</v>
       </c>
       <c r="AT23" t="str">
         <f>IF(AND(Dataset!F23="Savings",Dataset!AS23="eligible"),"YES","NO")</f>
         <v>NO</v>
       </c>
       <c r="AW23" s="12" t="s">
-        <v>490</v>
+        <v>487</v>
       </c>
       <c r="AX23" s="8" t="s">
-        <v>492</v>
+        <v>489</v>
       </c>
       <c r="AY23" s="8"/>
       <c r="AZ23" s="8"/>
@@ -5119,17 +5139,17 @@
         <v>bad_client</v>
       </c>
       <c r="AS24" t="s">
-        <v>485</v>
+        <v>482</v>
       </c>
       <c r="AT24" t="str">
         <f>IF(AND(Dataset!F24="Savings",Dataset!AS24="eligible"),"YES","NO")</f>
         <v>NO</v>
       </c>
       <c r="AW24" s="12" t="s">
+        <v>487</v>
+      </c>
+      <c r="AX24" s="8" t="s">
         <v>490</v>
-      </c>
-      <c r="AX24" s="8" t="s">
-        <v>493</v>
       </c>
       <c r="AY24" s="8"/>
       <c r="AZ24" s="8"/>
@@ -5228,7 +5248,7 @@
         <v>bad_client</v>
       </c>
       <c r="AT25" t="s">
-        <v>485</v>
+        <v>482</v>
       </c>
       <c r="AU25" t="str">
         <f>IF(AND(Dataset!F25="Savings",Dataset!AT25="eligible"),"YES","NO")</f>
@@ -5236,10 +5256,10 @@
       </c>
       <c r="AW25" s="8"/>
       <c r="AX25" s="12" t="s">
-        <v>490</v>
+        <v>487</v>
       </c>
       <c r="AY25" s="8" t="s">
-        <v>492</v>
+        <v>489</v>
       </c>
       <c r="AZ25" s="8"/>
       <c r="BD25" t="str">
@@ -5337,7 +5357,7 @@
         <v>bad_client</v>
       </c>
       <c r="AT26" t="s">
-        <v>485</v>
+        <v>482</v>
       </c>
       <c r="AU26" t="str">
         <f>IF(AND(Dataset!F26="Savings",Dataset!AT26="eligible"),"YES","NO")</f>
@@ -5345,10 +5365,10 @@
       </c>
       <c r="AW26" s="8"/>
       <c r="AX26" s="12" t="s">
-        <v>489</v>
+        <v>486</v>
       </c>
       <c r="AY26" s="8" t="s">
-        <v>493</v>
+        <v>490</v>
       </c>
       <c r="AZ26" s="8"/>
       <c r="BD26" t="str">
@@ -5446,7 +5466,7 @@
         <v>bad_client</v>
       </c>
       <c r="AT27" t="s">
-        <v>485</v>
+        <v>482</v>
       </c>
       <c r="AU27" t="str">
         <f>IF(AND(Dataset!F27="Savings",Dataset!AT27="eligible"),"YES","NO")</f>
@@ -5454,10 +5474,10 @@
       </c>
       <c r="AW27" s="8"/>
       <c r="AX27" s="12" t="s">
+        <v>486</v>
+      </c>
+      <c r="AY27" s="8" t="s">
         <v>489</v>
-      </c>
-      <c r="AY27" s="8" t="s">
-        <v>492</v>
       </c>
       <c r="AZ27" s="8"/>
       <c r="BD27" t="str">
@@ -5555,7 +5575,7 @@
         <v>bad_client</v>
       </c>
       <c r="AT28" t="s">
-        <v>485</v>
+        <v>482</v>
       </c>
       <c r="AU28" t="str">
         <f>IF(AND(Dataset!F28="Savings",Dataset!AT28="eligible"),"YES","NO")</f>
@@ -5563,10 +5583,10 @@
       </c>
       <c r="AW28" s="8"/>
       <c r="AX28" s="12" t="s">
+        <v>487</v>
+      </c>
+      <c r="AY28" s="8" t="s">
         <v>490</v>
-      </c>
-      <c r="AY28" s="8" t="s">
-        <v>493</v>
       </c>
       <c r="AZ28" s="8"/>
       <c r="BD28" t="str">
@@ -5664,7 +5684,7 @@
         <v>bad_client</v>
       </c>
       <c r="AT29" t="s">
-        <v>485</v>
+        <v>482</v>
       </c>
       <c r="AU29" t="str">
         <f>IF(AND(Dataset!F29="Savings",Dataset!AT29="eligible"),"YES","NO")</f>
@@ -5672,10 +5692,10 @@
       </c>
       <c r="AW29" s="8"/>
       <c r="AX29" s="12" t="s">
-        <v>490</v>
+        <v>487</v>
       </c>
       <c r="AY29" s="8" t="s">
-        <v>492</v>
+        <v>489</v>
       </c>
       <c r="AZ29" s="8"/>
       <c r="BD29" t="str">
@@ -5773,7 +5793,7 @@
         <v>bad_client</v>
       </c>
       <c r="AT30" t="s">
-        <v>485</v>
+        <v>482</v>
       </c>
       <c r="AU30" t="str">
         <f>IF(AND(Dataset!F30="Savings",Dataset!AT30="eligible"),"YES","NO")</f>
@@ -5781,10 +5801,10 @@
       </c>
       <c r="AW30" s="8"/>
       <c r="AX30" s="12" t="s">
-        <v>489</v>
+        <v>486</v>
       </c>
       <c r="AY30" s="8" t="s">
-        <v>493</v>
+        <v>490</v>
       </c>
       <c r="AZ30" s="8"/>
       <c r="BD30" t="str">
@@ -5882,7 +5902,7 @@
         <v>bad_client</v>
       </c>
       <c r="AT31" t="s">
-        <v>485</v>
+        <v>482</v>
       </c>
       <c r="AU31" t="str">
         <f>IF(AND(Dataset!F31="Savings",Dataset!AT31="eligible"),"YES","NO")</f>
@@ -5890,10 +5910,10 @@
       </c>
       <c r="AW31" s="8"/>
       <c r="AX31" s="12" t="s">
+        <v>486</v>
+      </c>
+      <c r="AY31" s="8" t="s">
         <v>489</v>
-      </c>
-      <c r="AY31" s="8" t="s">
-        <v>492</v>
       </c>
       <c r="AZ31" s="8"/>
       <c r="BD31" t="str">
@@ -5991,7 +6011,7 @@
         <v>bad_client</v>
       </c>
       <c r="AT32" t="s">
-        <v>485</v>
+        <v>482</v>
       </c>
       <c r="AU32" t="str">
         <f>IF(AND(Dataset!F32="Savings",Dataset!AT32="eligible"),"YES","NO")</f>
@@ -5999,10 +6019,10 @@
       </c>
       <c r="AW32" s="8"/>
       <c r="AX32" s="12" t="s">
+        <v>487</v>
+      </c>
+      <c r="AY32" s="8" t="s">
         <v>490</v>
-      </c>
-      <c r="AY32" s="8" t="s">
-        <v>493</v>
       </c>
       <c r="AZ32" s="8"/>
       <c r="BD32" t="str">
@@ -6100,7 +6120,7 @@
         <v>bad_client</v>
       </c>
       <c r="AT33" t="s">
-        <v>485</v>
+        <v>482</v>
       </c>
       <c r="AU33" t="str">
         <f>IF(AND(Dataset!F33="Savings",Dataset!AT33="eligible"),"YES","NO")</f>
@@ -6108,10 +6128,10 @@
       </c>
       <c r="AW33" s="8"/>
       <c r="AX33" s="12" t="s">
-        <v>490</v>
+        <v>487</v>
       </c>
       <c r="AY33" s="8" t="s">
-        <v>492</v>
+        <v>489</v>
       </c>
       <c r="AZ33" s="8"/>
       <c r="BD33" t="str">
@@ -6209,7 +6229,7 @@
         <v>bad_client</v>
       </c>
       <c r="AT34" t="s">
-        <v>485</v>
+        <v>482</v>
       </c>
       <c r="AU34" t="str">
         <f>IF(AND(Dataset!F34="Savings",Dataset!AT34="eligible"),"YES","NO")</f>
@@ -6217,10 +6237,10 @@
       </c>
       <c r="AW34" s="8"/>
       <c r="AX34" s="12" t="s">
+        <v>487</v>
+      </c>
+      <c r="AY34" s="8" t="s">
         <v>490</v>
-      </c>
-      <c r="AY34" s="8" t="s">
-        <v>493</v>
       </c>
       <c r="AZ34" s="8"/>
       <c r="BD34" t="str">
@@ -6318,7 +6338,7 @@
         <v>good_client</v>
       </c>
       <c r="AT35" t="s">
-        <v>485</v>
+        <v>482</v>
       </c>
       <c r="AU35" t="str">
         <f>IF(AND(Dataset!F35="Savings",Dataset!AT35="eligible"),"YES","NO")</f>
@@ -6326,10 +6346,10 @@
       </c>
       <c r="AW35" s="8"/>
       <c r="AX35" s="12" t="s">
-        <v>490</v>
+        <v>487</v>
       </c>
       <c r="AY35" s="8" t="s">
-        <v>492</v>
+        <v>489</v>
       </c>
       <c r="AZ35" s="8"/>
       <c r="BD35" t="str">
@@ -6427,7 +6447,7 @@
         <v>bad_client</v>
       </c>
       <c r="AT36" t="s">
-        <v>485</v>
+        <v>482</v>
       </c>
       <c r="AU36" t="str">
         <f>IF(AND(Dataset!F36="Savings",Dataset!AT36="eligible"),"YES","NO")</f>
@@ -6435,10 +6455,10 @@
       </c>
       <c r="AW36" s="8"/>
       <c r="AX36" s="12" t="s">
+        <v>487</v>
+      </c>
+      <c r="AY36" s="8" t="s">
         <v>490</v>
-      </c>
-      <c r="AY36" s="8" t="s">
-        <v>493</v>
       </c>
       <c r="AZ36" s="8"/>
       <c r="BD36" t="str">
@@ -6536,7 +6556,7 @@
         <v>bad_client</v>
       </c>
       <c r="AT37" t="s">
-        <v>485</v>
+        <v>482</v>
       </c>
       <c r="AU37" t="str">
         <f>IF(AND(Dataset!F37="Savings",Dataset!AT37="eligible"),"YES","NO")</f>
@@ -6544,10 +6564,10 @@
       </c>
       <c r="AW37" s="8"/>
       <c r="AX37" s="12" t="s">
-        <v>490</v>
+        <v>487</v>
       </c>
       <c r="AY37" s="8" t="s">
-        <v>492</v>
+        <v>489</v>
       </c>
       <c r="AZ37" s="8"/>
       <c r="BD37" t="str">
@@ -6645,7 +6665,7 @@
         <v>bad_client</v>
       </c>
       <c r="AT38" t="s">
-        <v>485</v>
+        <v>482</v>
       </c>
       <c r="AU38" t="str">
         <f>IF(AND(Dataset!F38="Savings",Dataset!AT38="eligible"),"YES","NO")</f>
@@ -6653,10 +6673,10 @@
       </c>
       <c r="AW38" s="8"/>
       <c r="AX38" s="12" t="s">
-        <v>489</v>
+        <v>486</v>
       </c>
       <c r="AY38" s="8" t="s">
-        <v>493</v>
+        <v>490</v>
       </c>
       <c r="AZ38" s="8"/>
       <c r="BD38" t="str">
@@ -6754,7 +6774,7 @@
         <v>bad_client</v>
       </c>
       <c r="AT39" t="s">
-        <v>485</v>
+        <v>482</v>
       </c>
       <c r="AU39" t="str">
         <f>IF(AND(Dataset!F39="Savings",Dataset!AT39="eligible"),"YES","NO")</f>
@@ -6762,10 +6782,10 @@
       </c>
       <c r="AW39" s="8"/>
       <c r="AX39" s="12" t="s">
+        <v>486</v>
+      </c>
+      <c r="AY39" s="8" t="s">
         <v>489</v>
-      </c>
-      <c r="AY39" s="8" t="s">
-        <v>492</v>
       </c>
       <c r="AZ39" s="8"/>
       <c r="BD39" t="str">
@@ -6863,7 +6883,7 @@
         <v>bad_client</v>
       </c>
       <c r="AT40" t="s">
-        <v>485</v>
+        <v>482</v>
       </c>
       <c r="AU40" t="str">
         <f>IF(AND(Dataset!F40="Savings",Dataset!AT40="eligible"),"YES","NO")</f>
@@ -6871,10 +6891,10 @@
       </c>
       <c r="AW40" s="8"/>
       <c r="AX40" s="12" t="s">
-        <v>489</v>
+        <v>486</v>
       </c>
       <c r="AY40" s="8" t="s">
-        <v>493</v>
+        <v>490</v>
       </c>
       <c r="AZ40" s="8"/>
       <c r="BD40" t="str">
@@ -6972,7 +6992,7 @@
         <v>bad_client</v>
       </c>
       <c r="AT41" t="s">
-        <v>485</v>
+        <v>482</v>
       </c>
       <c r="AU41" t="str">
         <f>IF(AND(Dataset!F41="Savings",Dataset!AT41="eligible"),"YES","NO")</f>
@@ -6980,10 +7000,10 @@
       </c>
       <c r="AW41" s="8"/>
       <c r="AX41" s="12" t="s">
+        <v>486</v>
+      </c>
+      <c r="AY41" s="8" t="s">
         <v>489</v>
-      </c>
-      <c r="AY41" s="8" t="s">
-        <v>492</v>
       </c>
       <c r="AZ41" s="8"/>
       <c r="BD41" t="str">
@@ -7081,7 +7101,7 @@
         <v>bad_client</v>
       </c>
       <c r="AT42" t="s">
-        <v>485</v>
+        <v>482</v>
       </c>
       <c r="AU42" t="str">
         <f>IF(AND(Dataset!F42="Savings",Dataset!AT42="eligible"),"YES","NO")</f>
@@ -7089,10 +7109,10 @@
       </c>
       <c r="AW42" s="8"/>
       <c r="AX42" s="12" t="s">
-        <v>489</v>
+        <v>486</v>
       </c>
       <c r="AY42" s="8" t="s">
-        <v>493</v>
+        <v>490</v>
       </c>
       <c r="AZ42" s="8"/>
       <c r="BD42" t="str">
@@ -7190,7 +7210,7 @@
         <v>bad_client</v>
       </c>
       <c r="AT43" t="s">
-        <v>485</v>
+        <v>482</v>
       </c>
       <c r="AU43" t="str">
         <f>IF(AND(Dataset!F43="Savings",Dataset!AT43="eligible"),"YES","NO")</f>
@@ -7198,10 +7218,10 @@
       </c>
       <c r="AW43" s="8"/>
       <c r="AX43" s="12" t="s">
+        <v>486</v>
+      </c>
+      <c r="AY43" s="8" t="s">
         <v>489</v>
-      </c>
-      <c r="AY43" s="8" t="s">
-        <v>492</v>
       </c>
       <c r="AZ43" s="8"/>
       <c r="BD43" t="str">
@@ -7299,7 +7319,7 @@
         <v>bad_client</v>
       </c>
       <c r="AT44" t="s">
-        <v>485</v>
+        <v>482</v>
       </c>
       <c r="AU44" t="str">
         <f>IF(AND(Dataset!F44="Savings",Dataset!AT44="eligible"),"YES","NO")</f>
@@ -7307,10 +7327,10 @@
       </c>
       <c r="AW44" s="8"/>
       <c r="AX44" s="12" t="s">
+        <v>487</v>
+      </c>
+      <c r="AY44" s="8" t="s">
         <v>490</v>
-      </c>
-      <c r="AY44" s="8" t="s">
-        <v>493</v>
       </c>
       <c r="AZ44" s="8"/>
       <c r="BD44" t="str">
@@ -7408,7 +7428,7 @@
         <v>bad_client</v>
       </c>
       <c r="AT45" t="s">
-        <v>485</v>
+        <v>482</v>
       </c>
       <c r="AU45" t="str">
         <f>IF(AND(Dataset!F45="Savings",Dataset!AT45="eligible"),"YES","NO")</f>
@@ -7416,10 +7436,10 @@
       </c>
       <c r="AW45" s="8"/>
       <c r="AX45" s="12" t="s">
-        <v>490</v>
+        <v>487</v>
       </c>
       <c r="AY45" s="8" t="s">
-        <v>492</v>
+        <v>489</v>
       </c>
       <c r="AZ45" s="8"/>
       <c r="BD45" t="str">
@@ -7517,7 +7537,7 @@
         <v>bad_client</v>
       </c>
       <c r="AT46" t="s">
-        <v>485</v>
+        <v>482</v>
       </c>
       <c r="AU46" t="str">
         <f>IF(AND(Dataset!F46="Savings",Dataset!AT46="eligible"),"YES","NO")</f>
@@ -7525,10 +7545,10 @@
       </c>
       <c r="AW46" s="8"/>
       <c r="AX46" s="12" t="s">
+        <v>487</v>
+      </c>
+      <c r="AY46" s="8" t="s">
         <v>490</v>
-      </c>
-      <c r="AY46" s="8" t="s">
-        <v>493</v>
       </c>
       <c r="AZ46" s="8"/>
       <c r="BD46" t="str">
@@ -7626,7 +7646,7 @@
         <v>bad_client</v>
       </c>
       <c r="AT47" t="s">
-        <v>485</v>
+        <v>482</v>
       </c>
       <c r="AU47" t="str">
         <f>IF(AND(Dataset!F47="Savings",Dataset!AT47="eligible"),"YES","NO")</f>
@@ -7634,10 +7654,10 @@
       </c>
       <c r="AW47" s="8"/>
       <c r="AX47" s="12" t="s">
-        <v>490</v>
+        <v>487</v>
       </c>
       <c r="AY47" s="8" t="s">
-        <v>492</v>
+        <v>489</v>
       </c>
       <c r="AZ47" s="8"/>
       <c r="BD47" t="str">
@@ -7735,7 +7755,7 @@
         <v>bad_client</v>
       </c>
       <c r="AT48" t="s">
-        <v>485</v>
+        <v>482</v>
       </c>
       <c r="AU48" t="str">
         <f>IF(AND(Dataset!F48="Savings",Dataset!AT48="eligible"),"YES","NO")</f>
@@ -7743,10 +7763,10 @@
       </c>
       <c r="AW48" s="8"/>
       <c r="AX48" s="12" t="s">
+        <v>487</v>
+      </c>
+      <c r="AY48" s="8" t="s">
         <v>490</v>
-      </c>
-      <c r="AY48" s="8" t="s">
-        <v>493</v>
       </c>
       <c r="AZ48" s="8"/>
       <c r="BD48" t="str">
@@ -7844,7 +7864,7 @@
         <v>bad_client</v>
       </c>
       <c r="AT49" t="s">
-        <v>485</v>
+        <v>482</v>
       </c>
       <c r="AU49" t="str">
         <f>IF(AND(Dataset!F49="Savings",Dataset!AT49="eligible"),"YES","NO")</f>
@@ -7852,10 +7872,10 @@
       </c>
       <c r="AW49" s="8"/>
       <c r="AX49" s="12" t="s">
-        <v>490</v>
+        <v>487</v>
       </c>
       <c r="AY49" s="8" t="s">
-        <v>492</v>
+        <v>489</v>
       </c>
       <c r="AZ49" s="8"/>
       <c r="BD49" t="str">
@@ -7953,7 +7973,7 @@
         <v>bad_client</v>
       </c>
       <c r="AT50" t="s">
-        <v>485</v>
+        <v>482</v>
       </c>
       <c r="AU50" t="str">
         <f>IF(AND(Dataset!F50="Savings",Dataset!AT50="eligible"),"YES","NO")</f>
@@ -7961,10 +7981,10 @@
       </c>
       <c r="AW50" s="8"/>
       <c r="AX50" s="12" t="s">
+        <v>487</v>
+      </c>
+      <c r="AY50" s="8" t="s">
         <v>490</v>
-      </c>
-      <c r="AY50" s="8" t="s">
-        <v>493</v>
       </c>
       <c r="AZ50" s="8"/>
       <c r="BD50" t="str">
@@ -8062,7 +8082,7 @@
         <v>bad_client</v>
       </c>
       <c r="AT51" t="s">
-        <v>485</v>
+        <v>482</v>
       </c>
       <c r="AU51" t="str">
         <f>IF(AND(Dataset!F51="Savings",Dataset!AT51="eligible"),"YES","NO")</f>
@@ -8070,10 +8090,10 @@
       </c>
       <c r="AW51" s="8"/>
       <c r="AX51" s="12" t="s">
-        <v>490</v>
+        <v>487</v>
       </c>
       <c r="AY51" s="8" t="s">
-        <v>492</v>
+        <v>489</v>
       </c>
       <c r="AZ51" s="8"/>
       <c r="BD51" t="str">
@@ -8171,7 +8191,7 @@
         <v>bad_client</v>
       </c>
       <c r="AT52" t="s">
-        <v>485</v>
+        <v>482</v>
       </c>
       <c r="AU52" t="str">
         <f>IF(AND(Dataset!F52="Savings",Dataset!AT52="eligible"),"YES","NO")</f>
@@ -8179,10 +8199,10 @@
       </c>
       <c r="AW52" s="8"/>
       <c r="AX52" s="12" t="s">
+        <v>487</v>
+      </c>
+      <c r="AY52" s="8" t="s">
         <v>490</v>
-      </c>
-      <c r="AY52" s="8" t="s">
-        <v>493</v>
       </c>
       <c r="AZ52" s="8"/>
       <c r="BD52" t="str">
@@ -8280,7 +8300,7 @@
         <v>bad_client</v>
       </c>
       <c r="AT53" t="s">
-        <v>485</v>
+        <v>482</v>
       </c>
       <c r="AU53" t="str">
         <f>IF(AND(Dataset!F53="Savings",Dataset!AT53="eligible"),"YES","NO")</f>
@@ -8288,10 +8308,10 @@
       </c>
       <c r="AW53" s="8"/>
       <c r="AX53" s="12" t="s">
-        <v>490</v>
+        <v>487</v>
       </c>
       <c r="AY53" s="8" t="s">
-        <v>492</v>
+        <v>489</v>
       </c>
       <c r="AZ53" s="8"/>
       <c r="BD53" t="str">
@@ -8389,7 +8409,7 @@
         <v>bad_client</v>
       </c>
       <c r="AT54" t="s">
-        <v>485</v>
+        <v>482</v>
       </c>
       <c r="AU54" t="str">
         <f>IF(AND(Dataset!F54="Savings",Dataset!AT54="eligible"),"YES","NO")</f>
@@ -8397,10 +8417,10 @@
       </c>
       <c r="AW54" s="8"/>
       <c r="AX54" s="12" t="s">
+        <v>487</v>
+      </c>
+      <c r="AY54" s="8" t="s">
         <v>490</v>
-      </c>
-      <c r="AY54" s="8" t="s">
-        <v>493</v>
       </c>
       <c r="AZ54" s="8"/>
       <c r="BD54" t="str">
@@ -8498,7 +8518,7 @@
         <v>bad_client</v>
       </c>
       <c r="AT55" t="s">
-        <v>485</v>
+        <v>482</v>
       </c>
       <c r="AU55" t="str">
         <f>IF(AND(Dataset!F55="Savings",Dataset!AT55="eligible"),"YES","NO")</f>
@@ -8506,10 +8526,10 @@
       </c>
       <c r="AW55" s="8"/>
       <c r="AX55" s="12" t="s">
+        <v>486</v>
+      </c>
+      <c r="AY55" s="8" t="s">
         <v>489</v>
-      </c>
-      <c r="AY55" s="8" t="s">
-        <v>492</v>
       </c>
       <c r="AZ55" s="8"/>
       <c r="BD55" t="str">
@@ -8607,7 +8627,7 @@
         <v>bad_client</v>
       </c>
       <c r="AT56" t="s">
-        <v>485</v>
+        <v>482</v>
       </c>
       <c r="AU56" t="str">
         <f>IF(AND(Dataset!F56="Savings",Dataset!AT56="eligible"),"YES","NO")</f>
@@ -8615,10 +8635,10 @@
       </c>
       <c r="AW56" s="8"/>
       <c r="AX56" s="12" t="s">
-        <v>489</v>
+        <v>486</v>
       </c>
       <c r="AY56" s="8" t="s">
-        <v>493</v>
+        <v>490</v>
       </c>
       <c r="AZ56" s="8"/>
       <c r="BD56" t="str">
@@ -8716,7 +8736,7 @@
         <v>bad_client</v>
       </c>
       <c r="AT57" t="s">
-        <v>485</v>
+        <v>482</v>
       </c>
       <c r="AU57" t="str">
         <f>IF(AND(Dataset!F57="Savings",Dataset!AT57="eligible"),"YES","NO")</f>
@@ -8724,10 +8744,10 @@
       </c>
       <c r="AW57" s="8"/>
       <c r="AX57" s="12" t="s">
+        <v>486</v>
+      </c>
+      <c r="AY57" s="8" t="s">
         <v>489</v>
-      </c>
-      <c r="AY57" s="8" t="s">
-        <v>492</v>
       </c>
       <c r="AZ57" s="8"/>
       <c r="BD57" t="str">
@@ -8825,7 +8845,7 @@
         <v>bad_client</v>
       </c>
       <c r="AT58" t="s">
-        <v>485</v>
+        <v>482</v>
       </c>
       <c r="AU58" t="str">
         <f>IF(AND(Dataset!F58="Savings",Dataset!AT58="eligible"),"YES","NO")</f>
@@ -8833,10 +8853,10 @@
       </c>
       <c r="AW58" s="8"/>
       <c r="AX58" s="12" t="s">
+        <v>487</v>
+      </c>
+      <c r="AY58" s="8" t="s">
         <v>490</v>
-      </c>
-      <c r="AY58" s="8" t="s">
-        <v>493</v>
       </c>
       <c r="AZ58" s="8"/>
       <c r="BD58" t="str">
@@ -8934,7 +8954,7 @@
         <v>bad_client</v>
       </c>
       <c r="AT59" t="s">
-        <v>485</v>
+        <v>482</v>
       </c>
       <c r="AU59" t="str">
         <f>IF(AND(Dataset!F59="Savings",Dataset!AT59="eligible"),"YES","NO")</f>
@@ -8942,10 +8962,10 @@
       </c>
       <c r="AW59" s="8"/>
       <c r="AX59" s="12" t="s">
-        <v>490</v>
+        <v>487</v>
       </c>
       <c r="AY59" s="8" t="s">
-        <v>492</v>
+        <v>489</v>
       </c>
       <c r="AZ59" s="8"/>
       <c r="BD59" t="str">
@@ -9043,7 +9063,7 @@
         <v>bad_client</v>
       </c>
       <c r="AT60" t="s">
-        <v>485</v>
+        <v>482</v>
       </c>
       <c r="AU60" t="str">
         <f>IF(AND(Dataset!F60="Savings",Dataset!AT60="eligible"),"YES","NO")</f>
@@ -9051,10 +9071,10 @@
       </c>
       <c r="AW60" s="8"/>
       <c r="AX60" s="12" t="s">
+        <v>487</v>
+      </c>
+      <c r="AY60" s="8" t="s">
         <v>490</v>
-      </c>
-      <c r="AY60" s="8" t="s">
-        <v>493</v>
       </c>
       <c r="AZ60" s="8"/>
       <c r="BD60" t="str">
@@ -9152,7 +9172,7 @@
         <v>bad_client</v>
       </c>
       <c r="AT61" t="s">
-        <v>485</v>
+        <v>482</v>
       </c>
       <c r="AU61" t="str">
         <f>IF(AND(Dataset!F61="Savings",Dataset!AT61="eligible"),"YES","NO")</f>
@@ -9160,10 +9180,10 @@
       </c>
       <c r="AW61" s="8"/>
       <c r="AX61" s="12" t="s">
-        <v>490</v>
+        <v>487</v>
       </c>
       <c r="AY61" s="8" t="s">
-        <v>492</v>
+        <v>489</v>
       </c>
       <c r="AZ61" s="8"/>
       <c r="BD61" t="str">
@@ -9261,7 +9281,7 @@
         <v>bad_client</v>
       </c>
       <c r="AT62" t="s">
-        <v>485</v>
+        <v>482</v>
       </c>
       <c r="AU62" t="str">
         <f>IF(AND(Dataset!F62="Savings",Dataset!AT62="eligible"),"YES","NO")</f>
@@ -9269,10 +9289,10 @@
       </c>
       <c r="AW62" s="8"/>
       <c r="AX62" s="12" t="s">
+        <v>487</v>
+      </c>
+      <c r="AY62" s="8" t="s">
         <v>490</v>
-      </c>
-      <c r="AY62" s="8" t="s">
-        <v>493</v>
       </c>
       <c r="AZ62" s="8"/>
       <c r="BD62" t="str">
@@ -9370,7 +9390,7 @@
         <v>bad_client</v>
       </c>
       <c r="AT63" t="s">
-        <v>485</v>
+        <v>482</v>
       </c>
       <c r="AU63" t="str">
         <f>IF(AND(Dataset!F63="Savings",Dataset!AT63="eligible"),"YES","NO")</f>
@@ -9378,10 +9398,10 @@
       </c>
       <c r="AW63" s="8"/>
       <c r="AX63" s="12" t="s">
-        <v>490</v>
+        <v>487</v>
       </c>
       <c r="AY63" s="8" t="s">
-        <v>492</v>
+        <v>489</v>
       </c>
       <c r="AZ63" s="8"/>
       <c r="BD63" t="str">
@@ -9479,7 +9499,7 @@
         <v>bad_client</v>
       </c>
       <c r="AT64" t="s">
-        <v>485</v>
+        <v>482</v>
       </c>
       <c r="AU64" t="str">
         <f>IF(AND(Dataset!F64="Savings",Dataset!AT64="eligible"),"YES","NO")</f>
@@ -9487,10 +9507,10 @@
       </c>
       <c r="AW64" s="8"/>
       <c r="AX64" s="12" t="s">
+        <v>487</v>
+      </c>
+      <c r="AY64" s="8" t="s">
         <v>490</v>
-      </c>
-      <c r="AY64" s="8" t="s">
-        <v>493</v>
       </c>
       <c r="AZ64" s="8"/>
       <c r="BD64" t="str">
@@ -9588,7 +9608,7 @@
         <v>good_client</v>
       </c>
       <c r="AT65" t="s">
-        <v>485</v>
+        <v>482</v>
       </c>
       <c r="AU65" t="str">
         <f>IF(AND(Dataset!F65="Savings",Dataset!AT65="eligible"),"YES","NO")</f>
@@ -9596,10 +9616,10 @@
       </c>
       <c r="AW65" s="8"/>
       <c r="AX65" s="12" t="s">
-        <v>490</v>
+        <v>487</v>
       </c>
       <c r="AY65" s="8" t="s">
-        <v>492</v>
+        <v>489</v>
       </c>
       <c r="AZ65" s="8"/>
       <c r="BD65" t="str">
@@ -9697,7 +9717,7 @@
         <v>bad_client</v>
       </c>
       <c r="AT66" t="s">
-        <v>485</v>
+        <v>482</v>
       </c>
       <c r="AU66" t="str">
         <f>IF(AND(Dataset!F66="Savings",Dataset!AT66="eligible"),"YES","NO")</f>
@@ -9705,10 +9725,10 @@
       </c>
       <c r="AW66" s="8"/>
       <c r="AX66" s="12" t="s">
-        <v>489</v>
+        <v>486</v>
       </c>
       <c r="AY66" s="8" t="s">
-        <v>493</v>
+        <v>490</v>
       </c>
       <c r="AZ66" s="8"/>
       <c r="BD66" t="str">
@@ -9806,7 +9826,7 @@
         <v>good_client</v>
       </c>
       <c r="AT67" t="s">
-        <v>485</v>
+        <v>482</v>
       </c>
       <c r="AU67" t="str">
         <f>IF(AND(Dataset!F67="Savings",Dataset!AT67="eligible"),"YES","NO")</f>
@@ -9814,10 +9834,10 @@
       </c>
       <c r="AW67" s="8"/>
       <c r="AX67" s="12" t="s">
+        <v>486</v>
+      </c>
+      <c r="AY67" s="8" t="s">
         <v>489</v>
-      </c>
-      <c r="AY67" s="8" t="s">
-        <v>492</v>
       </c>
       <c r="AZ67" s="8"/>
       <c r="BD67" t="str">
@@ -9915,7 +9935,7 @@
         <v>bad_client</v>
       </c>
       <c r="AT68" t="s">
-        <v>485</v>
+        <v>482</v>
       </c>
       <c r="AU68" t="str">
         <f>IF(AND(Dataset!F68="Savings",Dataset!AT68="eligible"),"YES","NO")</f>
@@ -9923,10 +9943,10 @@
       </c>
       <c r="AW68" s="8"/>
       <c r="AX68" s="12" t="s">
-        <v>489</v>
+        <v>486</v>
       </c>
       <c r="AY68" s="8" t="s">
-        <v>493</v>
+        <v>490</v>
       </c>
       <c r="AZ68" s="8"/>
       <c r="BD68" t="str">
@@ -10024,7 +10044,7 @@
         <v>bad_client</v>
       </c>
       <c r="AT69" t="s">
-        <v>485</v>
+        <v>482</v>
       </c>
       <c r="AU69" t="str">
         <f>IF(AND(Dataset!F69="Savings",Dataset!AT69="eligible"),"YES","NO")</f>
@@ -10032,10 +10052,10 @@
       </c>
       <c r="AW69" s="8"/>
       <c r="AX69" s="12" t="s">
+        <v>486</v>
+      </c>
+      <c r="AY69" s="8" t="s">
         <v>489</v>
-      </c>
-      <c r="AY69" s="8" t="s">
-        <v>492</v>
       </c>
       <c r="AZ69" s="8"/>
       <c r="BD69" t="str">
@@ -10133,7 +10153,7 @@
         <v>bad_client</v>
       </c>
       <c r="AT70" t="s">
-        <v>485</v>
+        <v>482</v>
       </c>
       <c r="AU70" t="str">
         <f>IF(AND(Dataset!F70="Savings",Dataset!AT70="eligible"),"YES","NO")</f>
@@ -10141,10 +10161,10 @@
       </c>
       <c r="AW70" s="8"/>
       <c r="AX70" s="12" t="s">
+        <v>487</v>
+      </c>
+      <c r="AY70" s="8" t="s">
         <v>490</v>
-      </c>
-      <c r="AY70" s="8" t="s">
-        <v>493</v>
       </c>
       <c r="AZ70" s="8"/>
       <c r="BD70" t="str">
@@ -10242,7 +10262,7 @@
         <v>bad_client</v>
       </c>
       <c r="AT71" t="s">
-        <v>485</v>
+        <v>482</v>
       </c>
       <c r="AU71" t="str">
         <f>IF(AND(Dataset!F71="Savings",Dataset!AT71="eligible"),"YES","NO")</f>
@@ -10250,10 +10270,10 @@
       </c>
       <c r="AW71" s="8"/>
       <c r="AX71" s="12" t="s">
-        <v>490</v>
+        <v>487</v>
       </c>
       <c r="AY71" s="8" t="s">
-        <v>492</v>
+        <v>489</v>
       </c>
       <c r="AZ71" s="8"/>
       <c r="BD71" t="str">
@@ -10351,7 +10371,7 @@
         <v>bad_client</v>
       </c>
       <c r="AT72" t="s">
-        <v>485</v>
+        <v>482</v>
       </c>
       <c r="AU72" t="str">
         <f>IF(AND(Dataset!F72="Savings",Dataset!AT72="eligible"),"YES","NO")</f>
@@ -10359,10 +10379,10 @@
       </c>
       <c r="AW72" s="8"/>
       <c r="AX72" s="12" t="s">
+        <v>487</v>
+      </c>
+      <c r="AY72" s="8" t="s">
         <v>490</v>
-      </c>
-      <c r="AY72" s="8" t="s">
-        <v>493</v>
       </c>
       <c r="AZ72" s="8"/>
       <c r="BD72" t="str">
@@ -10460,7 +10480,7 @@
         <v>good_client</v>
       </c>
       <c r="AT73" t="s">
-        <v>485</v>
+        <v>482</v>
       </c>
       <c r="AU73" t="str">
         <f>IF(AND(Dataset!F73="Savings",Dataset!AT73="eligible"),"YES","NO")</f>
@@ -10468,10 +10488,10 @@
       </c>
       <c r="AW73" s="8"/>
       <c r="AX73" s="12" t="s">
-        <v>490</v>
+        <v>487</v>
       </c>
       <c r="AY73" s="8" t="s">
-        <v>492</v>
+        <v>489</v>
       </c>
       <c r="AZ73" s="8"/>
       <c r="BD73" t="str">
@@ -10569,7 +10589,7 @@
         <v>bad_client</v>
       </c>
       <c r="AT74" t="s">
-        <v>485</v>
+        <v>482</v>
       </c>
       <c r="AU74" t="str">
         <f>IF(AND(Dataset!F74="Savings",Dataset!AT74="eligible"),"YES","NO")</f>
@@ -10577,10 +10597,10 @@
       </c>
       <c r="AW74" s="8"/>
       <c r="AX74" s="12" t="s">
+        <v>487</v>
+      </c>
+      <c r="AY74" s="8" t="s">
         <v>490</v>
-      </c>
-      <c r="AY74" s="8" t="s">
-        <v>493</v>
       </c>
       <c r="AZ74" s="8"/>
       <c r="BD74" t="str">
@@ -10678,7 +10698,7 @@
         <v>bad_client</v>
       </c>
       <c r="AT75" t="s">
-        <v>485</v>
+        <v>482</v>
       </c>
       <c r="AU75" t="str">
         <f>IF(AND(Dataset!F75="Savings",Dataset!AT75="eligible"),"YES","NO")</f>
@@ -10686,10 +10706,10 @@
       </c>
       <c r="AW75" s="8"/>
       <c r="AX75" s="12" t="s">
-        <v>490</v>
+        <v>487</v>
       </c>
       <c r="AY75" s="8" t="s">
-        <v>492</v>
+        <v>489</v>
       </c>
       <c r="AZ75" s="8"/>
       <c r="BD75" t="str">
@@ -10787,7 +10807,7 @@
         <v>bad_client</v>
       </c>
       <c r="AT76" t="s">
-        <v>485</v>
+        <v>482</v>
       </c>
       <c r="AU76" t="str">
         <f>IF(AND(Dataset!F76="Savings",Dataset!AT76="eligible"),"YES","NO")</f>
@@ -10795,10 +10815,10 @@
       </c>
       <c r="AW76" s="8"/>
       <c r="AX76" s="12" t="s">
-        <v>489</v>
+        <v>486</v>
       </c>
       <c r="AY76" s="8" t="s">
-        <v>493</v>
+        <v>490</v>
       </c>
       <c r="AZ76" s="8"/>
       <c r="BD76" t="str">
@@ -10896,7 +10916,7 @@
         <v>bad_client</v>
       </c>
       <c r="AT77" t="s">
-        <v>485</v>
+        <v>482</v>
       </c>
       <c r="AU77" t="str">
         <f>IF(AND(Dataset!F77="Savings",Dataset!AT77="eligible"),"YES","NO")</f>
@@ -10904,10 +10924,10 @@
       </c>
       <c r="AW77" s="8"/>
       <c r="AX77" s="12" t="s">
+        <v>486</v>
+      </c>
+      <c r="AY77" s="8" t="s">
         <v>489</v>
-      </c>
-      <c r="AY77" s="8" t="s">
-        <v>492</v>
       </c>
       <c r="AZ77" s="8"/>
       <c r="BD77" t="str">
@@ -11005,7 +11025,7 @@
         <v>bad_client</v>
       </c>
       <c r="AT78" t="s">
-        <v>485</v>
+        <v>482</v>
       </c>
       <c r="AU78" t="str">
         <f>IF(AND(Dataset!F78="Savings",Dataset!AT78="eligible"),"YES","NO")</f>
@@ -11013,10 +11033,10 @@
       </c>
       <c r="AW78" s="8"/>
       <c r="AX78" s="12" t="s">
-        <v>489</v>
+        <v>486</v>
       </c>
       <c r="AY78" s="8" t="s">
-        <v>493</v>
+        <v>490</v>
       </c>
       <c r="AZ78" s="8"/>
       <c r="BD78" t="str">
@@ -11114,7 +11134,7 @@
         <v>bad_client</v>
       </c>
       <c r="AT79" t="s">
-        <v>485</v>
+        <v>482</v>
       </c>
       <c r="AU79" t="str">
         <f>IF(AND(Dataset!F79="Savings",Dataset!AT79="eligible"),"YES","NO")</f>
@@ -11122,10 +11142,10 @@
       </c>
       <c r="AW79" s="8"/>
       <c r="AX79" s="12" t="s">
-        <v>490</v>
+        <v>487</v>
       </c>
       <c r="AY79" s="8" t="s">
-        <v>492</v>
+        <v>489</v>
       </c>
       <c r="AZ79" s="8"/>
       <c r="BD79" t="str">
@@ -11223,7 +11243,7 @@
         <v>bad_client</v>
       </c>
       <c r="AT80" t="s">
-        <v>485</v>
+        <v>482</v>
       </c>
       <c r="AU80" t="str">
         <f>IF(AND(Dataset!F80="Savings",Dataset!AT80="eligible"),"YES","NO")</f>
@@ -11231,10 +11251,10 @@
       </c>
       <c r="AW80" s="8"/>
       <c r="AX80" s="12" t="s">
+        <v>487</v>
+      </c>
+      <c r="AY80" s="8" t="s">
         <v>490</v>
-      </c>
-      <c r="AY80" s="8" t="s">
-        <v>493</v>
       </c>
       <c r="AZ80" s="8"/>
       <c r="BD80" t="str">
@@ -11332,7 +11352,7 @@
         <v>bad_client</v>
       </c>
       <c r="AT81" t="s">
-        <v>485</v>
+        <v>482</v>
       </c>
       <c r="AU81" t="str">
         <f>IF(AND(Dataset!F81="Savings",Dataset!AT81="eligible"),"YES","NO")</f>
@@ -11340,10 +11360,10 @@
       </c>
       <c r="AW81" s="8"/>
       <c r="AX81" s="12" t="s">
-        <v>490</v>
+        <v>487</v>
       </c>
       <c r="AY81" s="8" t="s">
-        <v>492</v>
+        <v>489</v>
       </c>
       <c r="AZ81" s="8"/>
       <c r="BD81" t="str">
@@ -11441,7 +11461,7 @@
         <v>good_client</v>
       </c>
       <c r="AT82" t="s">
-        <v>485</v>
+        <v>482</v>
       </c>
       <c r="AU82" t="str">
         <f>IF(AND(Dataset!F82="Savings",Dataset!AT82="eligible"),"YES","NO")</f>
@@ -11449,10 +11469,10 @@
       </c>
       <c r="AW82" s="8"/>
       <c r="AX82" s="12" t="s">
-        <v>490</v>
+        <v>487</v>
       </c>
       <c r="AY82" s="8" t="s">
-        <v>492</v>
+        <v>489</v>
       </c>
       <c r="AZ82" s="8"/>
       <c r="BD82" t="str">
@@ -11550,7 +11570,7 @@
         <v>bad_client</v>
       </c>
       <c r="AT83" t="s">
-        <v>485</v>
+        <v>482</v>
       </c>
       <c r="AU83" t="str">
         <f>IF(AND(Dataset!F83="Savings",Dataset!AT83="eligible"),"YES","NO")</f>
@@ -11558,10 +11578,10 @@
       </c>
       <c r="AW83" s="8"/>
       <c r="AX83" s="12" t="s">
+        <v>487</v>
+      </c>
+      <c r="AY83" s="8" t="s">
         <v>490</v>
-      </c>
-      <c r="AY83" s="8" t="s">
-        <v>493</v>
       </c>
       <c r="AZ83" s="8"/>
       <c r="BD83" t="str">
@@ -11659,7 +11679,7 @@
         <v>bad_client</v>
       </c>
       <c r="AT84" t="s">
-        <v>485</v>
+        <v>482</v>
       </c>
       <c r="AU84" t="str">
         <f>IF(AND(Dataset!F84="Savings",Dataset!AT84="eligible"),"YES","NO")</f>
@@ -11667,10 +11687,10 @@
       </c>
       <c r="AW84" s="8"/>
       <c r="AX84" s="12" t="s">
+        <v>486</v>
+      </c>
+      <c r="AY84" s="8" t="s">
         <v>489</v>
-      </c>
-      <c r="AY84" s="8" t="s">
-        <v>492</v>
       </c>
       <c r="AZ84" s="8"/>
       <c r="BD84" t="str">
@@ -11768,7 +11788,7 @@
         <v>bad_client</v>
       </c>
       <c r="AT85" t="s">
-        <v>485</v>
+        <v>482</v>
       </c>
       <c r="AU85" t="str">
         <f>IF(AND(Dataset!F85="Savings",Dataset!AT85="eligible"),"YES","NO")</f>
@@ -11776,10 +11796,10 @@
       </c>
       <c r="AW85" s="8"/>
       <c r="AX85" s="12" t="s">
-        <v>490</v>
+        <v>487</v>
       </c>
       <c r="AY85" s="8" t="s">
-        <v>492</v>
+        <v>489</v>
       </c>
       <c r="AZ85" s="8"/>
       <c r="BD85" t="str">
@@ -11877,7 +11897,7 @@
         <v>bad_client</v>
       </c>
       <c r="AT86" t="s">
-        <v>485</v>
+        <v>482</v>
       </c>
       <c r="AU86" t="str">
         <f>IF(AND(Dataset!F86="Savings",Dataset!AT86="eligible"),"YES","NO")</f>
@@ -11885,10 +11905,10 @@
       </c>
       <c r="AW86" s="8"/>
       <c r="AX86" s="12" t="s">
+        <v>487</v>
+      </c>
+      <c r="AY86" s="8" t="s">
         <v>490</v>
-      </c>
-      <c r="AY86" s="8" t="s">
-        <v>493</v>
       </c>
       <c r="AZ86" s="8"/>
       <c r="BD86" t="str">
@@ -11986,7 +12006,7 @@
         <v>bad_client</v>
       </c>
       <c r="AT87" t="s">
-        <v>485</v>
+        <v>482</v>
       </c>
       <c r="AU87" t="str">
         <f>IF(AND(Dataset!F87="Savings",Dataset!AT87="eligible"),"YES","NO")</f>
@@ -11994,10 +12014,10 @@
       </c>
       <c r="AW87" s="8"/>
       <c r="AX87" s="12" t="s">
-        <v>490</v>
+        <v>487</v>
       </c>
       <c r="AY87" s="8" t="s">
-        <v>492</v>
+        <v>489</v>
       </c>
       <c r="AZ87" s="8"/>
       <c r="BD87" t="str">
@@ -12096,7 +12116,7 @@
         <v>bad_client</v>
       </c>
       <c r="AT88" t="s">
-        <v>485</v>
+        <v>482</v>
       </c>
       <c r="AU88" t="str">
         <f>IF(AND(Dataset!F88="Savings",Dataset!AT88="eligible"),"YES","NO")</f>
@@ -12104,10 +12124,10 @@
       </c>
       <c r="AW88" s="8"/>
       <c r="AX88" s="12" t="s">
+        <v>487</v>
+      </c>
+      <c r="AY88" s="8" t="s">
         <v>490</v>
-      </c>
-      <c r="AY88" s="8" t="s">
-        <v>493</v>
       </c>
       <c r="AZ88" s="8"/>
       <c r="BD88" t="str">
@@ -12206,7 +12226,7 @@
         <v>bad_client</v>
       </c>
       <c r="AT89" t="s">
-        <v>485</v>
+        <v>482</v>
       </c>
       <c r="AU89" t="str">
         <f>IF(AND(Dataset!F89="Savings",Dataset!AT89="eligible"),"YES","NO")</f>
@@ -12214,10 +12234,10 @@
       </c>
       <c r="AW89" s="8"/>
       <c r="AX89" s="12" t="s">
-        <v>490</v>
+        <v>487</v>
       </c>
       <c r="AY89" s="8" t="s">
-        <v>492</v>
+        <v>489</v>
       </c>
       <c r="AZ89" s="8"/>
       <c r="BD89" t="str">
@@ -12316,7 +12336,7 @@
         <v>bad_client</v>
       </c>
       <c r="AT90" t="s">
-        <v>485</v>
+        <v>482</v>
       </c>
       <c r="AU90" t="str">
         <f>IF(AND(Dataset!F90="Savings",Dataset!AT90="eligible"),"YES","NO")</f>
@@ -12324,10 +12344,10 @@
       </c>
       <c r="AW90" s="8"/>
       <c r="AX90" s="12" t="s">
-        <v>490</v>
+        <v>487</v>
       </c>
       <c r="AY90" s="8" t="s">
-        <v>492</v>
+        <v>489</v>
       </c>
       <c r="AZ90" s="8"/>
       <c r="BD90" t="str">
@@ -12426,7 +12446,7 @@
         <v>bad_client</v>
       </c>
       <c r="AT91" t="s">
-        <v>485</v>
+        <v>482</v>
       </c>
       <c r="AU91" t="str">
         <f>IF(AND(Dataset!F91="Savings",Dataset!AT91="eligible"),"YES","NO")</f>
@@ -12434,10 +12454,10 @@
       </c>
       <c r="AW91" s="8"/>
       <c r="AX91" s="12" t="s">
-        <v>489</v>
+        <v>486</v>
       </c>
       <c r="AY91" s="8" t="s">
-        <v>493</v>
+        <v>490</v>
       </c>
       <c r="AZ91" s="8"/>
       <c r="BD91" t="str">
@@ -12536,7 +12556,7 @@
         <v>bad_client</v>
       </c>
       <c r="AT92" t="s">
-        <v>485</v>
+        <v>482</v>
       </c>
       <c r="AU92" t="str">
         <f>IF(AND(Dataset!F92="Savings",Dataset!AT92="eligible"),"YES","NO")</f>
@@ -12544,10 +12564,10 @@
       </c>
       <c r="AW92" s="8"/>
       <c r="AX92" s="12" t="s">
-        <v>490</v>
+        <v>487</v>
       </c>
       <c r="AY92" s="8" t="s">
-        <v>492</v>
+        <v>489</v>
       </c>
       <c r="AZ92" s="8"/>
       <c r="BD92" t="str">
@@ -12646,7 +12666,7 @@
         <v>bad_client</v>
       </c>
       <c r="AT93" t="s">
-        <v>485</v>
+        <v>482</v>
       </c>
       <c r="AU93" t="str">
         <f>IF(AND(Dataset!F93="Savings",Dataset!AT93="eligible"),"YES","NO")</f>
@@ -12654,10 +12674,10 @@
       </c>
       <c r="AW93" s="8"/>
       <c r="AX93" s="12" t="s">
+        <v>486</v>
+      </c>
+      <c r="AY93" s="8" t="s">
         <v>489</v>
-      </c>
-      <c r="AY93" s="8" t="s">
-        <v>492</v>
       </c>
       <c r="AZ93" s="8"/>
       <c r="BD93" t="str">
@@ -12756,7 +12776,7 @@
         <v>bad_client</v>
       </c>
       <c r="AT94" t="s">
-        <v>485</v>
+        <v>482</v>
       </c>
       <c r="AU94" t="str">
         <f>IF(AND(Dataset!F94="Savings",Dataset!AT94="eligible"),"YES","NO")</f>
@@ -12764,10 +12784,10 @@
       </c>
       <c r="AW94" s="8"/>
       <c r="AX94" s="12" t="s">
+        <v>487</v>
+      </c>
+      <c r="AY94" s="8" t="s">
         <v>490</v>
-      </c>
-      <c r="AY94" s="8" t="s">
-        <v>493</v>
       </c>
       <c r="AZ94" s="8"/>
       <c r="BD94" t="str">
@@ -12866,7 +12886,7 @@
         <v>bad_client</v>
       </c>
       <c r="AT95" t="s">
-        <v>485</v>
+        <v>482</v>
       </c>
       <c r="AU95" t="str">
         <f>IF(AND(Dataset!F95="Savings",Dataset!AT95="eligible"),"YES","NO")</f>
@@ -12874,10 +12894,10 @@
       </c>
       <c r="AW95" s="8"/>
       <c r="AX95" s="12" t="s">
-        <v>490</v>
+        <v>487</v>
       </c>
       <c r="AY95" s="8" t="s">
-        <v>492</v>
+        <v>489</v>
       </c>
       <c r="AZ95" s="8"/>
       <c r="BD95" t="str">
@@ -12976,7 +12996,7 @@
         <v>bad_client</v>
       </c>
       <c r="AT96" t="s">
-        <v>485</v>
+        <v>482</v>
       </c>
       <c r="AU96" t="str">
         <f>IF(AND(Dataset!F96="Savings",Dataset!AT96="eligible"),"YES","NO")</f>
@@ -12984,10 +13004,10 @@
       </c>
       <c r="AW96" s="8"/>
       <c r="AX96" s="12" t="s">
-        <v>489</v>
+        <v>486</v>
       </c>
       <c r="AY96" s="8" t="s">
-        <v>493</v>
+        <v>490</v>
       </c>
       <c r="AZ96" s="8"/>
       <c r="BD96" t="str">
@@ -13086,7 +13106,7 @@
         <v>bad_client</v>
       </c>
       <c r="AT97" t="s">
-        <v>485</v>
+        <v>482</v>
       </c>
       <c r="AU97" t="str">
         <f>IF(AND(Dataset!F97="Savings",Dataset!AT97="eligible"),"YES","NO")</f>
@@ -13094,10 +13114,10 @@
       </c>
       <c r="AW97" s="8"/>
       <c r="AX97" s="12" t="s">
-        <v>490</v>
+        <v>487</v>
       </c>
       <c r="AY97" s="8" t="s">
-        <v>492</v>
+        <v>489</v>
       </c>
       <c r="AZ97" s="8"/>
       <c r="BD97" t="str">
@@ -13196,7 +13216,7 @@
         <v>good_client</v>
       </c>
       <c r="AT98" t="s">
-        <v>485</v>
+        <v>482</v>
       </c>
       <c r="AU98" t="str">
         <f>IF(AND(Dataset!F98="Savings",Dataset!AT98="eligible"),"YES","NO")</f>
@@ -13204,10 +13224,10 @@
       </c>
       <c r="AW98" s="8"/>
       <c r="AX98" s="12" t="s">
+        <v>487</v>
+      </c>
+      <c r="AY98" s="8" t="s">
         <v>490</v>
-      </c>
-      <c r="AY98" s="8" t="s">
-        <v>493</v>
       </c>
       <c r="AZ98" s="8"/>
       <c r="BD98" t="str">
@@ -13306,7 +13326,7 @@
         <v>bad_client</v>
       </c>
       <c r="AT99" t="s">
-        <v>485</v>
+        <v>482</v>
       </c>
       <c r="AU99" t="str">
         <f>IF(AND(Dataset!F99="Savings",Dataset!AT99="eligible"),"YES","NO")</f>
@@ -13314,10 +13334,10 @@
       </c>
       <c r="AW99" s="8"/>
       <c r="AX99" s="12" t="s">
+        <v>486</v>
+      </c>
+      <c r="AY99" s="8" t="s">
         <v>489</v>
-      </c>
-      <c r="AY99" s="8" t="s">
-        <v>492</v>
       </c>
       <c r="AZ99" s="8"/>
       <c r="BD99" t="str">
@@ -13416,7 +13436,7 @@
         <v>bad_client</v>
       </c>
       <c r="AT100" t="s">
-        <v>485</v>
+        <v>482</v>
       </c>
       <c r="AU100" t="str">
         <f>IF(AND(Dataset!F100="Savings",Dataset!AT100="eligible"),"YES","NO")</f>
@@ -13424,10 +13444,10 @@
       </c>
       <c r="AW100" s="8"/>
       <c r="AX100" s="12" t="s">
+        <v>487</v>
+      </c>
+      <c r="AY100" s="8" t="s">
         <v>490</v>
-      </c>
-      <c r="AY100" s="8" t="s">
-        <v>493</v>
       </c>
       <c r="AZ100" s="8"/>
       <c r="BD100" t="str">
@@ -13526,7 +13546,7 @@
         <v>bad_client</v>
       </c>
       <c r="AT101" t="s">
-        <v>485</v>
+        <v>482</v>
       </c>
       <c r="AU101" t="str">
         <f>IF(AND(Dataset!F101="Savings",Dataset!AT101="eligible"),"YES","NO")</f>
@@ -13534,10 +13554,10 @@
       </c>
       <c r="AW101" s="8"/>
       <c r="AX101" s="12" t="s">
+        <v>486</v>
+      </c>
+      <c r="AY101" s="8" t="s">
         <v>489</v>
-      </c>
-      <c r="AY101" s="8" t="s">
-        <v>492</v>
       </c>
       <c r="AZ101" s="8"/>
       <c r="BD101" t="str">
@@ -13636,7 +13656,7 @@
         <v>bad_client</v>
       </c>
       <c r="AT102" t="s">
-        <v>485</v>
+        <v>482</v>
       </c>
       <c r="AU102" t="str">
         <f>IF(AND(Dataset!F102="Savings",Dataset!AT102="eligible"),"YES","NO")</f>
@@ -13644,10 +13664,10 @@
       </c>
       <c r="AW102" s="8"/>
       <c r="AX102" s="12" t="s">
+        <v>487</v>
+      </c>
+      <c r="AY102" s="8" t="s">
         <v>490</v>
-      </c>
-      <c r="AY102" s="8" t="s">
-        <v>493</v>
       </c>
       <c r="AZ102" s="8"/>
       <c r="BD102" t="str">
@@ -13746,7 +13766,7 @@
         <v>bad_client</v>
       </c>
       <c r="AT103" t="s">
-        <v>485</v>
+        <v>482</v>
       </c>
       <c r="AU103" t="str">
         <f>IF(AND(Dataset!F103="Savings",Dataset!AT103="eligible"),"YES","NO")</f>
@@ -13754,10 +13774,10 @@
       </c>
       <c r="AW103" s="8"/>
       <c r="AX103" s="12" t="s">
-        <v>490</v>
+        <v>487</v>
       </c>
       <c r="AY103" s="8" t="s">
-        <v>492</v>
+        <v>489</v>
       </c>
       <c r="AZ103" s="8"/>
       <c r="BD103" t="str">
@@ -13856,7 +13876,7 @@
         <v>bad_client</v>
       </c>
       <c r="AT104" t="s">
-        <v>485</v>
+        <v>482</v>
       </c>
       <c r="AU104" t="str">
         <f>IF(AND(Dataset!F104="Savings",Dataset!AT104="eligible"),"YES","NO")</f>
@@ -13864,10 +13884,10 @@
       </c>
       <c r="AW104" s="8"/>
       <c r="AX104" s="12" t="s">
+        <v>487</v>
+      </c>
+      <c r="AY104" s="8" t="s">
         <v>490</v>
-      </c>
-      <c r="AY104" s="8" t="s">
-        <v>493</v>
       </c>
       <c r="AZ104" s="8"/>
       <c r="BD104" t="str">
@@ -13966,7 +13986,7 @@
         <v>bad_client</v>
       </c>
       <c r="AT105" t="s">
-        <v>485</v>
+        <v>482</v>
       </c>
       <c r="AU105" t="str">
         <f>IF(AND(Dataset!F105="Savings",Dataset!AT105="eligible"),"YES","NO")</f>
@@ -13974,10 +13994,10 @@
       </c>
       <c r="AW105" s="8"/>
       <c r="AX105" s="12" t="s">
-        <v>490</v>
+        <v>487</v>
       </c>
       <c r="AY105" s="8" t="s">
-        <v>492</v>
+        <v>489</v>
       </c>
       <c r="AZ105" s="8"/>
       <c r="BD105" t="str">
@@ -14076,7 +14096,7 @@
         <v>bad_client</v>
       </c>
       <c r="AT106" t="s">
-        <v>485</v>
+        <v>482</v>
       </c>
       <c r="AU106" t="str">
         <f>IF(AND(Dataset!F106="Savings",Dataset!AT106="eligible"),"YES","NO")</f>
@@ -14084,10 +14104,10 @@
       </c>
       <c r="AW106" s="8"/>
       <c r="AX106" s="12" t="s">
-        <v>489</v>
+        <v>486</v>
       </c>
       <c r="AY106" s="8" t="s">
-        <v>493</v>
+        <v>490</v>
       </c>
       <c r="AZ106" s="8"/>
       <c r="BD106" t="str">
@@ -14186,7 +14206,7 @@
         <v>bad_client</v>
       </c>
       <c r="AT107" t="s">
-        <v>485</v>
+        <v>482</v>
       </c>
       <c r="AU107" t="str">
         <f>IF(AND(Dataset!F107="Savings",Dataset!AT107="eligible"),"YES","NO")</f>
@@ -14194,10 +14214,10 @@
       </c>
       <c r="AW107" s="8"/>
       <c r="AX107" s="12" t="s">
+        <v>486</v>
+      </c>
+      <c r="AY107" s="8" t="s">
         <v>489</v>
-      </c>
-      <c r="AY107" s="8" t="s">
-        <v>492</v>
       </c>
       <c r="AZ107" s="8"/>
       <c r="BD107" t="str">
@@ -14296,7 +14316,7 @@
         <v>bad_client</v>
       </c>
       <c r="AT108" t="s">
-        <v>485</v>
+        <v>482</v>
       </c>
       <c r="AU108" t="str">
         <f>IF(AND(Dataset!F108="Savings",Dataset!AT108="eligible"),"YES","NO")</f>
@@ -14304,10 +14324,10 @@
       </c>
       <c r="AW108" s="8"/>
       <c r="AX108" s="12" t="s">
+        <v>487</v>
+      </c>
+      <c r="AY108" s="8" t="s">
         <v>490</v>
-      </c>
-      <c r="AY108" s="8" t="s">
-        <v>493</v>
       </c>
       <c r="AZ108" s="8"/>
       <c r="BD108" t="str">
@@ -14406,7 +14426,7 @@
         <v>bad_client</v>
       </c>
       <c r="AT109" t="s">
-        <v>485</v>
+        <v>482</v>
       </c>
       <c r="AU109" t="str">
         <f>IF(AND(Dataset!F109="Savings",Dataset!AT109="eligible"),"YES","NO")</f>
@@ -14414,10 +14434,10 @@
       </c>
       <c r="AW109" s="8"/>
       <c r="AX109" s="12" t="s">
-        <v>490</v>
+        <v>487</v>
       </c>
       <c r="AY109" s="8" t="s">
-        <v>492</v>
+        <v>489</v>
       </c>
       <c r="AZ109" s="8"/>
       <c r="BD109" t="str">
@@ -14516,7 +14536,7 @@
         <v>bad_client</v>
       </c>
       <c r="AT110" t="s">
-        <v>485</v>
+        <v>482</v>
       </c>
       <c r="AU110" t="str">
         <f>IF(AND(Dataset!F110="Savings",Dataset!AT110="eligible"),"YES","NO")</f>
@@ -14524,10 +14544,10 @@
       </c>
       <c r="AW110" s="8"/>
       <c r="AX110" s="12" t="s">
-        <v>489</v>
+        <v>486</v>
       </c>
       <c r="AY110" s="8" t="s">
-        <v>493</v>
+        <v>490</v>
       </c>
       <c r="AZ110" s="8"/>
       <c r="BD110" t="str">
@@ -14626,7 +14646,7 @@
         <v>bad_client</v>
       </c>
       <c r="AT111" t="s">
-        <v>485</v>
+        <v>482</v>
       </c>
       <c r="AU111" t="str">
         <f>IF(AND(Dataset!F111="Savings",Dataset!AT111="eligible"),"YES","NO")</f>
@@ -14634,10 +14654,10 @@
       </c>
       <c r="AW111" s="8"/>
       <c r="AX111" s="12" t="s">
+        <v>486</v>
+      </c>
+      <c r="AY111" s="8" t="s">
         <v>489</v>
-      </c>
-      <c r="AY111" s="8" t="s">
-        <v>492</v>
       </c>
       <c r="AZ111" s="8"/>
       <c r="BD111" t="str">
@@ -14736,7 +14756,7 @@
         <v>bad_client</v>
       </c>
       <c r="AT112" t="s">
-        <v>485</v>
+        <v>482</v>
       </c>
       <c r="AU112" t="str">
         <f>IF(AND(Dataset!F112="Savings",Dataset!AT112="eligible"),"YES","NO")</f>
@@ -14744,10 +14764,10 @@
       </c>
       <c r="AW112" s="8"/>
       <c r="AX112" s="12" t="s">
+        <v>487</v>
+      </c>
+      <c r="AY112" s="8" t="s">
         <v>490</v>
-      </c>
-      <c r="AY112" s="8" t="s">
-        <v>493</v>
       </c>
       <c r="AZ112" s="8"/>
       <c r="BD112" t="str">
@@ -14846,7 +14866,7 @@
         <v>bad_client</v>
       </c>
       <c r="AT113" t="s">
-        <v>485</v>
+        <v>482</v>
       </c>
       <c r="AU113" t="str">
         <f>IF(AND(Dataset!F113="Savings",Dataset!AT113="eligible"),"YES","NO")</f>
@@ -14854,10 +14874,10 @@
       </c>
       <c r="AW113" s="8"/>
       <c r="AX113" s="12" t="s">
-        <v>490</v>
+        <v>487</v>
       </c>
       <c r="AY113" s="8" t="s">
-        <v>492</v>
+        <v>489</v>
       </c>
       <c r="AZ113" s="8"/>
       <c r="BD113" t="str">
@@ -14956,7 +14976,7 @@
         <v>bad_client</v>
       </c>
       <c r="AT114" t="s">
-        <v>485</v>
+        <v>482</v>
       </c>
       <c r="AU114" t="str">
         <f>IF(AND(Dataset!F114="Savings",Dataset!AT114="eligible"),"YES","NO")</f>
@@ -14964,10 +14984,10 @@
       </c>
       <c r="AW114" s="8"/>
       <c r="AX114" s="12" t="s">
+        <v>487</v>
+      </c>
+      <c r="AY114" s="8" t="s">
         <v>490</v>
-      </c>
-      <c r="AY114" s="8" t="s">
-        <v>493</v>
       </c>
       <c r="AZ114" s="8"/>
       <c r="BD114" t="str">
@@ -15066,7 +15086,7 @@
         <v>good_client</v>
       </c>
       <c r="AT115" t="s">
-        <v>485</v>
+        <v>482</v>
       </c>
       <c r="AU115" t="str">
         <f>IF(AND(Dataset!F115="Savings",Dataset!AT115="eligible"),"YES","NO")</f>
@@ -15074,10 +15094,10 @@
       </c>
       <c r="AW115" s="8"/>
       <c r="AX115" s="12" t="s">
-        <v>490</v>
+        <v>487</v>
       </c>
       <c r="AY115" s="8" t="s">
-        <v>492</v>
+        <v>489</v>
       </c>
       <c r="AZ115" s="8"/>
       <c r="BD115" t="str">
@@ -15176,7 +15196,7 @@
         <v>bad_client</v>
       </c>
       <c r="AT116" t="s">
-        <v>485</v>
+        <v>482</v>
       </c>
       <c r="AU116" t="str">
         <f>IF(AND(Dataset!F116="Savings",Dataset!AT116="eligible"),"YES","NO")</f>
@@ -15184,10 +15204,10 @@
       </c>
       <c r="AW116" s="8"/>
       <c r="AX116" s="12" t="s">
+        <v>487</v>
+      </c>
+      <c r="AY116" s="8" t="s">
         <v>490</v>
-      </c>
-      <c r="AY116" s="8" t="s">
-        <v>493</v>
       </c>
       <c r="AZ116" s="8"/>
       <c r="BD116" t="str">
@@ -15286,7 +15306,7 @@
         <v>bad_client</v>
       </c>
       <c r="AT117" t="s">
-        <v>485</v>
+        <v>482</v>
       </c>
       <c r="AU117" t="str">
         <f>IF(AND(Dataset!F117="Savings",Dataset!AT117="eligible"),"YES","NO")</f>
@@ -15294,10 +15314,10 @@
       </c>
       <c r="AW117" s="8"/>
       <c r="AX117" s="12" t="s">
-        <v>490</v>
+        <v>487</v>
       </c>
       <c r="AY117" s="8" t="s">
-        <v>492</v>
+        <v>489</v>
       </c>
       <c r="AZ117" s="8"/>
       <c r="BD117" t="str">
@@ -15396,7 +15416,7 @@
         <v>bad_client</v>
       </c>
       <c r="AT118" t="s">
-        <v>485</v>
+        <v>482</v>
       </c>
       <c r="AU118" t="str">
         <f>IF(AND(Dataset!F118="Savings",Dataset!AT118="eligible"),"YES","NO")</f>
@@ -15404,10 +15424,10 @@
       </c>
       <c r="AW118" s="8"/>
       <c r="AX118" s="12" t="s">
-        <v>489</v>
+        <v>486</v>
       </c>
       <c r="AY118" s="8" t="s">
-        <v>493</v>
+        <v>490</v>
       </c>
       <c r="AZ118" s="8"/>
       <c r="BD118" t="str">
@@ -15506,7 +15526,7 @@
         <v>bad_client</v>
       </c>
       <c r="AT119" t="s">
-        <v>485</v>
+        <v>482</v>
       </c>
       <c r="AU119" t="str">
         <f>IF(AND(Dataset!F119="Savings",Dataset!AT119="eligible"),"YES","NO")</f>
@@ -15514,10 +15534,10 @@
       </c>
       <c r="AW119" s="8"/>
       <c r="AX119" s="12" t="s">
+        <v>486</v>
+      </c>
+      <c r="AY119" s="8" t="s">
         <v>489</v>
-      </c>
-      <c r="AY119" s="8" t="s">
-        <v>492</v>
       </c>
       <c r="AZ119" s="8"/>
       <c r="BD119" t="str">
@@ -15616,7 +15636,7 @@
         <v>bad_client</v>
       </c>
       <c r="AT120" t="s">
-        <v>485</v>
+        <v>482</v>
       </c>
       <c r="AU120" t="str">
         <f>IF(AND(Dataset!F120="Savings",Dataset!AT120="eligible"),"YES","NO")</f>
@@ -15624,10 +15644,10 @@
       </c>
       <c r="AW120" s="8"/>
       <c r="AX120" s="12" t="s">
-        <v>489</v>
+        <v>486</v>
       </c>
       <c r="AY120" s="8" t="s">
-        <v>493</v>
+        <v>490</v>
       </c>
       <c r="AZ120" s="8"/>
       <c r="BD120" t="str">
@@ -15726,7 +15746,7 @@
         <v>bad_client</v>
       </c>
       <c r="AT121" t="s">
-        <v>485</v>
+        <v>482</v>
       </c>
       <c r="AU121" t="str">
         <f>IF(AND(Dataset!F121="Savings",Dataset!AT121="eligible"),"YES","NO")</f>
@@ -15734,10 +15754,10 @@
       </c>
       <c r="AW121" s="8"/>
       <c r="AX121" s="12" t="s">
+        <v>486</v>
+      </c>
+      <c r="AY121" s="8" t="s">
         <v>489</v>
-      </c>
-      <c r="AY121" s="8" t="s">
-        <v>492</v>
       </c>
       <c r="AZ121" s="8"/>
       <c r="BD121" t="str">
@@ -15836,7 +15856,7 @@
         <v>bad_client</v>
       </c>
       <c r="AT122" t="s">
-        <v>485</v>
+        <v>482</v>
       </c>
       <c r="AU122" t="str">
         <f>IF(AND(Dataset!F122="Savings",Dataset!AT122="eligible"),"YES","NO")</f>
@@ -15844,10 +15864,10 @@
       </c>
       <c r="AW122" s="8"/>
       <c r="AX122" s="12" t="s">
-        <v>489</v>
+        <v>486</v>
       </c>
       <c r="AY122" s="8" t="s">
-        <v>493</v>
+        <v>490</v>
       </c>
       <c r="AZ122" s="8"/>
       <c r="BD122" t="str">
@@ -15946,7 +15966,7 @@
         <v>bad_client</v>
       </c>
       <c r="AT123" t="s">
-        <v>485</v>
+        <v>482</v>
       </c>
       <c r="AU123" t="str">
         <f>IF(AND(Dataset!F123="Savings",Dataset!AT123="eligible"),"YES","NO")</f>
@@ -15954,10 +15974,10 @@
       </c>
       <c r="AW123" s="8"/>
       <c r="AX123" s="12" t="s">
+        <v>486</v>
+      </c>
+      <c r="AY123" s="8" t="s">
         <v>489</v>
-      </c>
-      <c r="AY123" s="8" t="s">
-        <v>492</v>
       </c>
       <c r="AZ123" s="8"/>
       <c r="BD123" t="str">
@@ -16056,7 +16076,7 @@
         <v>bad_client</v>
       </c>
       <c r="AT124" t="s">
-        <v>485</v>
+        <v>482</v>
       </c>
       <c r="AU124" t="str">
         <f>IF(AND(Dataset!F124="Savings",Dataset!AT124="eligible"),"YES","NO")</f>
@@ -16064,10 +16084,10 @@
       </c>
       <c r="AW124" s="8"/>
       <c r="AX124" s="12" t="s">
+        <v>487</v>
+      </c>
+      <c r="AY124" s="8" t="s">
         <v>490</v>
-      </c>
-      <c r="AY124" s="8" t="s">
-        <v>493</v>
       </c>
       <c r="AZ124" s="8"/>
       <c r="BD124" t="str">
@@ -16166,7 +16186,7 @@
         <v>bad_client</v>
       </c>
       <c r="AT125" t="s">
-        <v>485</v>
+        <v>482</v>
       </c>
       <c r="AU125" t="str">
         <f>IF(AND(Dataset!F125="Savings",Dataset!AT125="eligible"),"YES","NO")</f>
@@ -16174,10 +16194,10 @@
       </c>
       <c r="AW125" s="8"/>
       <c r="AX125" s="12" t="s">
-        <v>490</v>
+        <v>487</v>
       </c>
       <c r="AY125" s="8" t="s">
-        <v>492</v>
+        <v>489</v>
       </c>
       <c r="AZ125" s="8"/>
       <c r="BD125" t="str">
@@ -16276,7 +16296,7 @@
         <v>bad_client</v>
       </c>
       <c r="AT126" t="s">
-        <v>485</v>
+        <v>482</v>
       </c>
       <c r="AU126" t="str">
         <f>IF(AND(Dataset!F126="Savings",Dataset!AT126="eligible"),"YES","NO")</f>
@@ -16284,10 +16304,10 @@
       </c>
       <c r="AW126" s="8"/>
       <c r="AX126" s="12" t="s">
+        <v>487</v>
+      </c>
+      <c r="AY126" s="8" t="s">
         <v>490</v>
-      </c>
-      <c r="AY126" s="8" t="s">
-        <v>493</v>
       </c>
       <c r="AZ126" s="8"/>
       <c r="BD126" t="str">
@@ -16386,7 +16406,7 @@
         <v>bad_client</v>
       </c>
       <c r="AT127" t="s">
-        <v>485</v>
+        <v>482</v>
       </c>
       <c r="AU127" t="str">
         <f>IF(AND(Dataset!F127="Savings",Dataset!AT127="eligible"),"YES","NO")</f>
@@ -16394,10 +16414,10 @@
       </c>
       <c r="AW127" s="8"/>
       <c r="AX127" s="12" t="s">
-        <v>490</v>
+        <v>487</v>
       </c>
       <c r="AY127" s="8" t="s">
-        <v>492</v>
+        <v>489</v>
       </c>
       <c r="AZ127" s="8"/>
       <c r="BD127" t="str">
@@ -16496,7 +16516,7 @@
         <v>bad_client</v>
       </c>
       <c r="AT128" t="s">
-        <v>485</v>
+        <v>482</v>
       </c>
       <c r="AU128" t="str">
         <f>IF(AND(Dataset!F128="Savings",Dataset!AT128="eligible"),"YES","NO")</f>
@@ -16504,10 +16524,10 @@
       </c>
       <c r="AW128" s="8"/>
       <c r="AX128" s="12" t="s">
+        <v>487</v>
+      </c>
+      <c r="AY128" s="8" t="s">
         <v>490</v>
-      </c>
-      <c r="AY128" s="8" t="s">
-        <v>493</v>
       </c>
       <c r="AZ128" s="8"/>
       <c r="BD128" t="str">
@@ -16606,7 +16626,7 @@
         <v>bad_client</v>
       </c>
       <c r="AT129" t="s">
-        <v>485</v>
+        <v>482</v>
       </c>
       <c r="AU129" t="str">
         <f>IF(AND(Dataset!F129="Savings",Dataset!AT129="eligible"),"YES","NO")</f>
@@ -16614,10 +16634,10 @@
       </c>
       <c r="AW129" s="8"/>
       <c r="AX129" s="12" t="s">
-        <v>490</v>
+        <v>487</v>
       </c>
       <c r="AY129" s="8" t="s">
-        <v>492</v>
+        <v>489</v>
       </c>
       <c r="AZ129" s="8"/>
       <c r="BD129" t="str">
@@ -16716,7 +16736,7 @@
         <v>bad_client</v>
       </c>
       <c r="AT130" t="s">
-        <v>485</v>
+        <v>482</v>
       </c>
       <c r="AU130" t="str">
         <f>IF(AND(Dataset!F130="Savings",Dataset!AT130="eligible"),"YES","NO")</f>
@@ -16724,10 +16744,10 @@
       </c>
       <c r="AW130" s="8"/>
       <c r="AX130" s="12" t="s">
+        <v>487</v>
+      </c>
+      <c r="AY130" s="8" t="s">
         <v>490</v>
-      </c>
-      <c r="AY130" s="8" t="s">
-        <v>493</v>
       </c>
       <c r="AZ130" s="8"/>
       <c r="BD130" t="str">
@@ -16826,7 +16846,7 @@
         <v>bad_client</v>
       </c>
       <c r="AT131" t="s">
-        <v>485</v>
+        <v>482</v>
       </c>
       <c r="AU131" t="str">
         <f>IF(AND(Dataset!F131="Savings",Dataset!AT131="eligible"),"YES","NO")</f>
@@ -16834,10 +16854,10 @@
       </c>
       <c r="AW131" s="8"/>
       <c r="AX131" s="12" t="s">
-        <v>490</v>
+        <v>487</v>
       </c>
       <c r="AY131" s="8" t="s">
-        <v>492</v>
+        <v>489</v>
       </c>
       <c r="AZ131" s="8"/>
       <c r="BD131" t="str">
@@ -16936,7 +16956,7 @@
         <v>bad_client</v>
       </c>
       <c r="AT132" t="s">
-        <v>485</v>
+        <v>482</v>
       </c>
       <c r="AU132" t="str">
         <f>IF(AND(Dataset!F132="Savings",Dataset!AT132="eligible"),"YES","NO")</f>
@@ -16944,10 +16964,10 @@
       </c>
       <c r="AW132" s="8"/>
       <c r="AX132" s="12" t="s">
+        <v>487</v>
+      </c>
+      <c r="AY132" s="8" t="s">
         <v>490</v>
-      </c>
-      <c r="AY132" s="8" t="s">
-        <v>493</v>
       </c>
       <c r="AZ132" s="8"/>
       <c r="BD132" t="str">
@@ -17046,7 +17066,7 @@
         <v>bad_client</v>
       </c>
       <c r="AT133" t="s">
-        <v>485</v>
+        <v>482</v>
       </c>
       <c r="AU133" t="str">
         <f>IF(AND(Dataset!F133="Savings",Dataset!AT133="eligible"),"YES","NO")</f>
@@ -17054,10 +17074,10 @@
       </c>
       <c r="AW133" s="8"/>
       <c r="AX133" s="12" t="s">
-        <v>490</v>
+        <v>487</v>
       </c>
       <c r="AY133" s="8" t="s">
-        <v>492</v>
+        <v>489</v>
       </c>
       <c r="AZ133" s="8"/>
       <c r="BD133" t="str">
@@ -17156,7 +17176,7 @@
         <v>bad_client</v>
       </c>
       <c r="AT134" t="s">
-        <v>485</v>
+        <v>482</v>
       </c>
       <c r="AU134" t="str">
         <f>IF(AND(Dataset!F134="Savings",Dataset!AT134="eligible"),"YES","NO")</f>
@@ -17164,10 +17184,10 @@
       </c>
       <c r="AW134" s="8"/>
       <c r="AX134" s="12" t="s">
+        <v>487</v>
+      </c>
+      <c r="AY134" s="8" t="s">
         <v>490</v>
-      </c>
-      <c r="AY134" s="8" t="s">
-        <v>493</v>
       </c>
       <c r="AZ134" s="8"/>
       <c r="BD134" t="str">
@@ -17266,7 +17286,7 @@
         <v>bad_client</v>
       </c>
       <c r="AT135" t="s">
-        <v>485</v>
+        <v>482</v>
       </c>
       <c r="AU135" t="str">
         <f>IF(AND(Dataset!F135="Savings",Dataset!AT135="eligible"),"YES","NO")</f>
@@ -17274,10 +17294,10 @@
       </c>
       <c r="AW135" s="8"/>
       <c r="AX135" s="12" t="s">
+        <v>486</v>
+      </c>
+      <c r="AY135" s="8" t="s">
         <v>489</v>
-      </c>
-      <c r="AY135" s="8" t="s">
-        <v>492</v>
       </c>
       <c r="AZ135" s="8"/>
       <c r="BD135" t="str">
@@ -17376,7 +17396,7 @@
         <v>bad_client</v>
       </c>
       <c r="AT136" t="s">
-        <v>485</v>
+        <v>482</v>
       </c>
       <c r="AU136" t="str">
         <f>IF(AND(Dataset!F136="Savings",Dataset!AT136="eligible"),"YES","NO")</f>
@@ -17384,10 +17404,10 @@
       </c>
       <c r="AW136" s="8"/>
       <c r="AX136" s="12" t="s">
-        <v>489</v>
+        <v>486</v>
       </c>
       <c r="AY136" s="8" t="s">
-        <v>493</v>
+        <v>490</v>
       </c>
       <c r="AZ136" s="8"/>
       <c r="BD136" t="str">
@@ -17486,7 +17506,7 @@
         <v>bad_client</v>
       </c>
       <c r="AT137" t="s">
-        <v>485</v>
+        <v>482</v>
       </c>
       <c r="AU137" t="str">
         <f>IF(AND(Dataset!F137="Savings",Dataset!AT137="eligible"),"YES","NO")</f>
@@ -17494,10 +17514,10 @@
       </c>
       <c r="AW137" s="8"/>
       <c r="AX137" s="12" t="s">
+        <v>486</v>
+      </c>
+      <c r="AY137" s="8" t="s">
         <v>489</v>
-      </c>
-      <c r="AY137" s="8" t="s">
-        <v>492</v>
       </c>
       <c r="AZ137" s="8"/>
       <c r="BD137" t="str">
@@ -17596,7 +17616,7 @@
         <v>bad_client</v>
       </c>
       <c r="AT138" t="s">
-        <v>485</v>
+        <v>482</v>
       </c>
       <c r="AU138" t="str">
         <f>IF(AND(Dataset!F138="Savings",Dataset!AT138="eligible"),"YES","NO")</f>
@@ -17604,10 +17624,10 @@
       </c>
       <c r="AW138" s="8"/>
       <c r="AX138" s="12" t="s">
+        <v>487</v>
+      </c>
+      <c r="AY138" s="8" t="s">
         <v>490</v>
-      </c>
-      <c r="AY138" s="8" t="s">
-        <v>493</v>
       </c>
       <c r="AZ138" s="8"/>
       <c r="BD138" t="str">
@@ -17706,7 +17726,7 @@
         <v>bad_client</v>
       </c>
       <c r="AT139" t="s">
-        <v>485</v>
+        <v>482</v>
       </c>
       <c r="AU139" t="str">
         <f>IF(AND(Dataset!F139="Savings",Dataset!AT139="eligible"),"YES","NO")</f>
@@ -17714,10 +17734,10 @@
       </c>
       <c r="AW139" s="8"/>
       <c r="AX139" s="12" t="s">
-        <v>490</v>
+        <v>487</v>
       </c>
       <c r="AY139" s="8" t="s">
-        <v>492</v>
+        <v>489</v>
       </c>
       <c r="AZ139" s="8"/>
       <c r="BD139" t="str">
@@ -17816,7 +17836,7 @@
         <v>bad_client</v>
       </c>
       <c r="AT140" t="s">
-        <v>485</v>
+        <v>482</v>
       </c>
       <c r="AU140" t="str">
         <f>IF(AND(Dataset!F140="Savings",Dataset!AT140="eligible"),"YES","NO")</f>
@@ -17824,10 +17844,10 @@
       </c>
       <c r="AW140" s="8"/>
       <c r="AX140" s="12" t="s">
+        <v>487</v>
+      </c>
+      <c r="AY140" s="8" t="s">
         <v>490</v>
-      </c>
-      <c r="AY140" s="8" t="s">
-        <v>493</v>
       </c>
       <c r="AZ140" s="8"/>
       <c r="BD140" t="str">
@@ -17926,7 +17946,7 @@
         <v>bad_client</v>
       </c>
       <c r="AT141" t="s">
-        <v>485</v>
+        <v>482</v>
       </c>
       <c r="AU141" t="str">
         <f>IF(AND(Dataset!F141="Savings",Dataset!AT141="eligible"),"YES","NO")</f>
@@ -17934,10 +17954,10 @@
       </c>
       <c r="AW141" s="8"/>
       <c r="AX141" s="12" t="s">
-        <v>490</v>
+        <v>487</v>
       </c>
       <c r="AY141" s="8" t="s">
-        <v>492</v>
+        <v>489</v>
       </c>
       <c r="AZ141" s="8"/>
       <c r="BD141" t="str">
@@ -18036,7 +18056,7 @@
         <v>bad_client</v>
       </c>
       <c r="AT142" t="s">
-        <v>485</v>
+        <v>482</v>
       </c>
       <c r="AU142" t="str">
         <f>IF(AND(Dataset!F142="Savings",Dataset!AT142="eligible"),"YES","NO")</f>
@@ -18044,10 +18064,10 @@
       </c>
       <c r="AW142" s="8"/>
       <c r="AX142" s="12" t="s">
+        <v>487</v>
+      </c>
+      <c r="AY142" s="8" t="s">
         <v>490</v>
-      </c>
-      <c r="AY142" s="8" t="s">
-        <v>493</v>
       </c>
       <c r="AZ142" s="8"/>
       <c r="BD142" t="str">
@@ -18146,7 +18166,7 @@
         <v>bad_client</v>
       </c>
       <c r="AT143" t="s">
-        <v>485</v>
+        <v>482</v>
       </c>
       <c r="AU143" t="str">
         <f>IF(AND(Dataset!F143="Savings",Dataset!AT143="eligible"),"YES","NO")</f>
@@ -18154,10 +18174,10 @@
       </c>
       <c r="AW143" s="8"/>
       <c r="AX143" s="12" t="s">
-        <v>490</v>
+        <v>487</v>
       </c>
       <c r="AY143" s="8" t="s">
-        <v>492</v>
+        <v>489</v>
       </c>
       <c r="AZ143" s="8"/>
       <c r="BD143" t="str">
@@ -18256,7 +18276,7 @@
         <v>bad_client</v>
       </c>
       <c r="AT144" t="s">
-        <v>485</v>
+        <v>482</v>
       </c>
       <c r="AU144" t="str">
         <f>IF(AND(Dataset!F144="Savings",Dataset!AT144="eligible"),"YES","NO")</f>
@@ -18264,10 +18284,10 @@
       </c>
       <c r="AW144" s="8"/>
       <c r="AX144" s="12" t="s">
+        <v>487</v>
+      </c>
+      <c r="AY144" s="8" t="s">
         <v>490</v>
-      </c>
-      <c r="AY144" s="8" t="s">
-        <v>493</v>
       </c>
       <c r="AZ144" s="8"/>
       <c r="BD144" t="str">
@@ -18366,7 +18386,7 @@
         <v>good_client</v>
       </c>
       <c r="AT145" t="s">
-        <v>485</v>
+        <v>482</v>
       </c>
       <c r="AU145" t="str">
         <f>IF(AND(Dataset!F145="Savings",Dataset!AT145="eligible"),"YES","NO")</f>
@@ -18374,10 +18394,10 @@
       </c>
       <c r="AW145" s="8"/>
       <c r="AX145" s="12" t="s">
-        <v>490</v>
+        <v>487</v>
       </c>
       <c r="AY145" s="8" t="s">
-        <v>492</v>
+        <v>489</v>
       </c>
       <c r="AZ145" s="8"/>
       <c r="BD145" t="str">
@@ -18476,7 +18496,7 @@
         <v>bad_client</v>
       </c>
       <c r="AT146" t="s">
-        <v>485</v>
+        <v>482</v>
       </c>
       <c r="AU146" t="str">
         <f>IF(AND(Dataset!F146="Savings",Dataset!AT146="eligible"),"YES","NO")</f>
@@ -18484,10 +18504,10 @@
       </c>
       <c r="AW146" s="8"/>
       <c r="AX146" s="12" t="s">
-        <v>489</v>
+        <v>486</v>
       </c>
       <c r="AY146" s="8" t="s">
-        <v>493</v>
+        <v>490</v>
       </c>
       <c r="AZ146" s="8"/>
       <c r="BD146" t="str">
@@ -18586,7 +18606,7 @@
         <v>good_client</v>
       </c>
       <c r="AT147" t="s">
-        <v>485</v>
+        <v>482</v>
       </c>
       <c r="AU147" t="str">
         <f>IF(AND(Dataset!F147="Savings",Dataset!AT147="eligible"),"YES","NO")</f>
@@ -18594,10 +18614,10 @@
       </c>
       <c r="AW147" s="8"/>
       <c r="AX147" s="12" t="s">
+        <v>486</v>
+      </c>
+      <c r="AY147" s="8" t="s">
         <v>489</v>
-      </c>
-      <c r="AY147" s="8" t="s">
-        <v>492</v>
       </c>
       <c r="AZ147" s="8"/>
       <c r="BD147" t="str">
@@ -18696,7 +18716,7 @@
         <v>bad_client</v>
       </c>
       <c r="AT148" t="s">
-        <v>485</v>
+        <v>482</v>
       </c>
       <c r="AU148" t="str">
         <f>IF(AND(Dataset!F148="Savings",Dataset!AT148="eligible"),"YES","NO")</f>
@@ -18704,10 +18724,10 @@
       </c>
       <c r="AW148" s="8"/>
       <c r="AX148" s="12" t="s">
-        <v>489</v>
+        <v>486</v>
       </c>
       <c r="AY148" s="8" t="s">
-        <v>493</v>
+        <v>490</v>
       </c>
       <c r="AZ148" s="8"/>
       <c r="BD148" t="str">
@@ -18806,7 +18826,7 @@
         <v>bad_client</v>
       </c>
       <c r="AT149" t="s">
-        <v>485</v>
+        <v>482</v>
       </c>
       <c r="AU149" t="str">
         <f>IF(AND(Dataset!F149="Savings",Dataset!AT149="eligible"),"YES","NO")</f>
@@ -18814,10 +18834,10 @@
       </c>
       <c r="AW149" s="8"/>
       <c r="AX149" s="12" t="s">
+        <v>486</v>
+      </c>
+      <c r="AY149" s="8" t="s">
         <v>489</v>
-      </c>
-      <c r="AY149" s="8" t="s">
-        <v>492</v>
       </c>
       <c r="AZ149" s="8"/>
       <c r="BD149" t="str">
@@ -18916,7 +18936,7 @@
         <v>bad_client</v>
       </c>
       <c r="AT150" t="s">
-        <v>485</v>
+        <v>482</v>
       </c>
       <c r="AU150" t="str">
         <f>IF(AND(Dataset!F150="Savings",Dataset!AT150="eligible"),"YES","NO")</f>
@@ -18924,10 +18944,10 @@
       </c>
       <c r="AW150" s="8"/>
       <c r="AX150" s="12" t="s">
+        <v>487</v>
+      </c>
+      <c r="AY150" s="8" t="s">
         <v>490</v>
-      </c>
-      <c r="AY150" s="8" t="s">
-        <v>493</v>
       </c>
       <c r="AZ150" s="8"/>
       <c r="BD150" t="str">
@@ -19026,7 +19046,7 @@
         <v>bad_client</v>
       </c>
       <c r="AT151" t="s">
-        <v>485</v>
+        <v>482</v>
       </c>
       <c r="AU151" t="str">
         <f>IF(AND(Dataset!F151="Savings",Dataset!AT151="eligible"),"YES","NO")</f>
@@ -19034,10 +19054,10 @@
       </c>
       <c r="AW151" s="8"/>
       <c r="AX151" s="12" t="s">
-        <v>490</v>
+        <v>487</v>
       </c>
       <c r="AY151" s="8" t="s">
-        <v>492</v>
+        <v>489</v>
       </c>
       <c r="AZ151" s="8"/>
       <c r="BD151" t="str">
@@ -19136,7 +19156,7 @@
         <v>bad_client</v>
       </c>
       <c r="AT152" t="s">
-        <v>485</v>
+        <v>482</v>
       </c>
       <c r="AU152" t="str">
         <f>IF(AND(Dataset!F152="Savings",Dataset!AT152="eligible"),"YES","NO")</f>
@@ -19144,10 +19164,10 @@
       </c>
       <c r="AW152" s="8"/>
       <c r="AX152" s="12" t="s">
+        <v>487</v>
+      </c>
+      <c r="AY152" s="8" t="s">
         <v>490</v>
-      </c>
-      <c r="AY152" s="8" t="s">
-        <v>493</v>
       </c>
       <c r="AZ152" s="8"/>
       <c r="BD152" t="str">
@@ -19246,7 +19266,7 @@
         <v>good_client</v>
       </c>
       <c r="AT153" t="s">
-        <v>485</v>
+        <v>482</v>
       </c>
       <c r="AU153" t="str">
         <f>IF(AND(Dataset!F153="Savings",Dataset!AT153="eligible"),"YES","NO")</f>
@@ -19254,10 +19274,10 @@
       </c>
       <c r="AW153" s="8"/>
       <c r="AX153" s="12" t="s">
-        <v>490</v>
+        <v>487</v>
       </c>
       <c r="AY153" s="8" t="s">
-        <v>492</v>
+        <v>489</v>
       </c>
       <c r="AZ153" s="8"/>
       <c r="BD153" t="str">
@@ -19356,7 +19376,7 @@
         <v>bad_client</v>
       </c>
       <c r="AT154" t="s">
-        <v>485</v>
+        <v>482</v>
       </c>
       <c r="AU154" t="str">
         <f>IF(AND(Dataset!F154="Savings",Dataset!AT154="eligible"),"YES","NO")</f>
@@ -19364,10 +19384,10 @@
       </c>
       <c r="AW154" s="8"/>
       <c r="AX154" s="12" t="s">
+        <v>487</v>
+      </c>
+      <c r="AY154" s="8" t="s">
         <v>490</v>
-      </c>
-      <c r="AY154" s="8" t="s">
-        <v>493</v>
       </c>
       <c r="AZ154" s="8"/>
       <c r="BD154" t="str">
@@ -19466,7 +19486,7 @@
         <v>bad_client</v>
       </c>
       <c r="AT155" t="s">
-        <v>485</v>
+        <v>482</v>
       </c>
       <c r="AU155" t="str">
         <f>IF(AND(Dataset!F155="Savings",Dataset!AT155="eligible"),"YES","NO")</f>
@@ -19474,10 +19494,10 @@
       </c>
       <c r="AW155" s="8"/>
       <c r="AX155" s="12" t="s">
-        <v>490</v>
+        <v>487</v>
       </c>
       <c r="AY155" s="8" t="s">
-        <v>492</v>
+        <v>489</v>
       </c>
       <c r="AZ155" s="8"/>
       <c r="BD155" t="str">
@@ -19576,7 +19596,7 @@
         <v>bad_client</v>
       </c>
       <c r="AT156" t="s">
-        <v>485</v>
+        <v>482</v>
       </c>
       <c r="AU156" t="str">
         <f>IF(AND(Dataset!F156="Savings",Dataset!AT156="eligible"),"YES","NO")</f>
@@ -19584,10 +19604,10 @@
       </c>
       <c r="AW156" s="8"/>
       <c r="AX156" s="12" t="s">
-        <v>489</v>
+        <v>486</v>
       </c>
       <c r="AY156" s="8" t="s">
-        <v>493</v>
+        <v>490</v>
       </c>
       <c r="AZ156" s="8"/>
       <c r="BD156" t="str">
@@ -19686,7 +19706,7 @@
         <v>bad_client</v>
       </c>
       <c r="AT157" t="s">
-        <v>485</v>
+        <v>482</v>
       </c>
       <c r="AU157" t="str">
         <f>IF(AND(Dataset!F157="Savings",Dataset!AT157="eligible"),"YES","NO")</f>
@@ -19694,10 +19714,10 @@
       </c>
       <c r="AW157" s="8"/>
       <c r="AX157" s="12" t="s">
+        <v>486</v>
+      </c>
+      <c r="AY157" s="8" t="s">
         <v>489</v>
-      </c>
-      <c r="AY157" s="8" t="s">
-        <v>492</v>
       </c>
       <c r="AZ157" s="8"/>
       <c r="BD157" t="str">
@@ -19796,7 +19816,7 @@
         <v>bad_client</v>
       </c>
       <c r="AT158" t="s">
-        <v>485</v>
+        <v>482</v>
       </c>
       <c r="AU158" t="str">
         <f>IF(AND(Dataset!F158="Savings",Dataset!AT158="eligible"),"YES","NO")</f>
@@ -19804,10 +19824,10 @@
       </c>
       <c r="AW158" s="8"/>
       <c r="AX158" s="12" t="s">
-        <v>489</v>
+        <v>486</v>
       </c>
       <c r="AY158" s="8" t="s">
-        <v>493</v>
+        <v>490</v>
       </c>
       <c r="AZ158" s="8"/>
       <c r="BD158" t="str">
@@ -19906,7 +19926,7 @@
         <v>bad_client</v>
       </c>
       <c r="AT159" t="s">
-        <v>485</v>
+        <v>482</v>
       </c>
       <c r="AU159" t="str">
         <f>IF(AND(Dataset!F159="Savings",Dataset!AT159="eligible"),"YES","NO")</f>
@@ -19914,10 +19934,10 @@
       </c>
       <c r="AW159" s="8"/>
       <c r="AX159" s="12" t="s">
-        <v>490</v>
+        <v>487</v>
       </c>
       <c r="AY159" s="8" t="s">
-        <v>492</v>
+        <v>489</v>
       </c>
       <c r="AZ159" s="8"/>
       <c r="BD159" t="str">
@@ -20016,7 +20036,7 @@
         <v>bad_client</v>
       </c>
       <c r="AT160" t="s">
-        <v>485</v>
+        <v>482</v>
       </c>
       <c r="AU160" t="str">
         <f>IF(AND(Dataset!F160="Savings",Dataset!AT160="eligible"),"YES","NO")</f>
@@ -20024,10 +20044,10 @@
       </c>
       <c r="AW160" s="8"/>
       <c r="AX160" s="12" t="s">
+        <v>487</v>
+      </c>
+      <c r="AY160" s="8" t="s">
         <v>490</v>
-      </c>
-      <c r="AY160" s="8" t="s">
-        <v>493</v>
       </c>
       <c r="AZ160" s="8"/>
       <c r="BD160" t="str">
@@ -20126,7 +20146,7 @@
         <v>bad_client</v>
       </c>
       <c r="AT161" t="s">
-        <v>485</v>
+        <v>482</v>
       </c>
       <c r="AU161" t="str">
         <f>IF(AND(Dataset!F161="Savings",Dataset!AT161="eligible"),"YES","NO")</f>
@@ -20134,10 +20154,10 @@
       </c>
       <c r="AW161" s="8"/>
       <c r="AX161" s="12" t="s">
-        <v>490</v>
+        <v>487</v>
       </c>
       <c r="AY161" s="8" t="s">
-        <v>492</v>
+        <v>489</v>
       </c>
       <c r="AZ161" s="8"/>
       <c r="BD161" t="str">
@@ -20236,7 +20256,7 @@
         <v>good_client</v>
       </c>
       <c r="AT162" t="s">
-        <v>485</v>
+        <v>482</v>
       </c>
       <c r="AU162" t="str">
         <f>IF(AND(Dataset!F162="Savings",Dataset!AT162="eligible"),"YES","NO")</f>
@@ -20244,10 +20264,10 @@
       </c>
       <c r="AW162" s="8"/>
       <c r="AX162" s="12" t="s">
-        <v>490</v>
+        <v>487</v>
       </c>
       <c r="AY162" s="8" t="s">
-        <v>492</v>
+        <v>489</v>
       </c>
       <c r="AZ162" s="8"/>
       <c r="BD162" t="str">
@@ -20346,7 +20366,7 @@
         <v>bad_client</v>
       </c>
       <c r="AT163" t="s">
-        <v>485</v>
+        <v>482</v>
       </c>
       <c r="AU163" t="str">
         <f>IF(AND(Dataset!F163="Savings",Dataset!AT163="eligible"),"YES","NO")</f>
@@ -20354,10 +20374,10 @@
       </c>
       <c r="AW163" s="8"/>
       <c r="AX163" s="12" t="s">
+        <v>487</v>
+      </c>
+      <c r="AY163" s="8" t="s">
         <v>490</v>
-      </c>
-      <c r="AY163" s="8" t="s">
-        <v>493</v>
       </c>
       <c r="AZ163" s="8"/>
       <c r="BD163" t="str">
@@ -20456,7 +20476,7 @@
         <v>bad_client</v>
       </c>
       <c r="AT164" t="s">
-        <v>485</v>
+        <v>482</v>
       </c>
       <c r="AU164" t="str">
         <f>IF(AND(Dataset!F164="Savings",Dataset!AT164="eligible"),"YES","NO")</f>
@@ -20464,10 +20484,10 @@
       </c>
       <c r="AW164" s="8"/>
       <c r="AX164" s="12" t="s">
+        <v>486</v>
+      </c>
+      <c r="AY164" s="8" t="s">
         <v>489</v>
-      </c>
-      <c r="AY164" s="8" t="s">
-        <v>492</v>
       </c>
       <c r="AZ164" s="8"/>
       <c r="BD164" t="str">
@@ -20566,7 +20586,7 @@
         <v>bad_client</v>
       </c>
       <c r="AT165" t="s">
-        <v>485</v>
+        <v>482</v>
       </c>
       <c r="AU165" t="str">
         <f>IF(AND(Dataset!F165="Savings",Dataset!AT165="eligible"),"YES","NO")</f>
@@ -20574,10 +20594,10 @@
       </c>
       <c r="AW165" s="8"/>
       <c r="AX165" s="12" t="s">
-        <v>490</v>
+        <v>487</v>
       </c>
       <c r="AY165" s="8" t="s">
-        <v>492</v>
+        <v>489</v>
       </c>
       <c r="AZ165" s="8"/>
       <c r="BD165" t="str">
@@ -20676,7 +20696,7 @@
         <v>bad_client</v>
       </c>
       <c r="AT166" t="s">
-        <v>485</v>
+        <v>482</v>
       </c>
       <c r="AU166" t="str">
         <f>IF(AND(Dataset!F166="Savings",Dataset!AT166="eligible"),"YES","NO")</f>
@@ -20684,10 +20704,10 @@
       </c>
       <c r="AW166" s="8"/>
       <c r="AX166" s="12" t="s">
+        <v>487</v>
+      </c>
+      <c r="AY166" s="8" t="s">
         <v>490</v>
-      </c>
-      <c r="AY166" s="8" t="s">
-        <v>493</v>
       </c>
       <c r="AZ166" s="8"/>
       <c r="BD166" t="str">
@@ -20786,7 +20806,7 @@
         <v>bad_client</v>
       </c>
       <c r="AT167" t="s">
-        <v>485</v>
+        <v>482</v>
       </c>
       <c r="AU167" t="str">
         <f>IF(AND(Dataset!F167="Savings",Dataset!AT167="eligible"),"YES","NO")</f>
@@ -20794,10 +20814,10 @@
       </c>
       <c r="AW167" s="8"/>
       <c r="AX167" s="12" t="s">
-        <v>490</v>
+        <v>487</v>
       </c>
       <c r="AY167" s="8" t="s">
-        <v>492</v>
+        <v>489</v>
       </c>
       <c r="AZ167" s="8"/>
       <c r="BD167" t="str">
@@ -20896,7 +20916,7 @@
         <v>bad_client</v>
       </c>
       <c r="AT168" t="s">
-        <v>485</v>
+        <v>482</v>
       </c>
       <c r="AU168" t="str">
         <f>IF(AND(Dataset!F168="Savings",Dataset!AT168="eligible"),"YES","NO")</f>
@@ -20904,10 +20924,10 @@
       </c>
       <c r="AW168" s="8"/>
       <c r="AX168" s="12" t="s">
+        <v>487</v>
+      </c>
+      <c r="AY168" s="8" t="s">
         <v>490</v>
-      </c>
-      <c r="AY168" s="8" t="s">
-        <v>493</v>
       </c>
       <c r="AZ168" s="8"/>
       <c r="BD168" t="str">
@@ -21006,7 +21026,7 @@
         <v>bad_client</v>
       </c>
       <c r="AT169" t="s">
-        <v>485</v>
+        <v>482</v>
       </c>
       <c r="AU169" t="str">
         <f>IF(AND(Dataset!F169="Savings",Dataset!AT169="eligible"),"YES","NO")</f>
@@ -21014,10 +21034,10 @@
       </c>
       <c r="AW169" s="8"/>
       <c r="AX169" s="12" t="s">
-        <v>490</v>
+        <v>487</v>
       </c>
       <c r="AY169" s="8" t="s">
-        <v>492</v>
+        <v>489</v>
       </c>
       <c r="AZ169" s="8"/>
       <c r="BD169" t="str">
@@ -21116,7 +21136,7 @@
         <v>bad_client</v>
       </c>
       <c r="AT170" t="s">
-        <v>485</v>
+        <v>482</v>
       </c>
       <c r="AU170" t="str">
         <f>IF(AND(Dataset!F170="Savings",Dataset!AT170="eligible"),"YES","NO")</f>
@@ -21124,10 +21144,10 @@
       </c>
       <c r="AW170" s="8"/>
       <c r="AX170" s="12" t="s">
-        <v>490</v>
+        <v>487</v>
       </c>
       <c r="AY170" s="8" t="s">
-        <v>492</v>
+        <v>489</v>
       </c>
       <c r="AZ170" s="8"/>
       <c r="BD170" t="str">
@@ -21226,7 +21246,7 @@
         <v>bad_client</v>
       </c>
       <c r="AT171" t="s">
-        <v>485</v>
+        <v>482</v>
       </c>
       <c r="AU171" t="str">
         <f>IF(AND(Dataset!F171="Savings",Dataset!AT171="eligible"),"YES","NO")</f>
@@ -21234,10 +21254,10 @@
       </c>
       <c r="AW171" s="8"/>
       <c r="AX171" s="12" t="s">
-        <v>489</v>
+        <v>486</v>
       </c>
       <c r="AY171" s="8" t="s">
-        <v>493</v>
+        <v>490</v>
       </c>
       <c r="AZ171" s="8"/>
       <c r="BD171" t="str">
@@ -21336,7 +21356,7 @@
         <v>bad_client</v>
       </c>
       <c r="AT172" t="s">
-        <v>485</v>
+        <v>482</v>
       </c>
       <c r="AU172" t="str">
         <f>IF(AND(Dataset!F172="Savings",Dataset!AT172="eligible"),"YES","NO")</f>
@@ -21344,10 +21364,10 @@
       </c>
       <c r="AW172" s="8"/>
       <c r="AX172" s="12" t="s">
-        <v>490</v>
+        <v>487</v>
       </c>
       <c r="AY172" s="8" t="s">
-        <v>492</v>
+        <v>489</v>
       </c>
       <c r="AZ172" s="8"/>
       <c r="BD172" t="str">
@@ -21446,7 +21466,7 @@
         <v>bad_client</v>
       </c>
       <c r="AT173" t="s">
-        <v>485</v>
+        <v>482</v>
       </c>
       <c r="AU173" t="str">
         <f>IF(AND(Dataset!F173="Savings",Dataset!AT173="eligible"),"YES","NO")</f>
@@ -21454,10 +21474,10 @@
       </c>
       <c r="AW173" s="8"/>
       <c r="AX173" s="12" t="s">
+        <v>486</v>
+      </c>
+      <c r="AY173" s="8" t="s">
         <v>489</v>
-      </c>
-      <c r="AY173" s="8" t="s">
-        <v>492</v>
       </c>
       <c r="AZ173" s="8"/>
       <c r="BD173" t="str">
@@ -21556,7 +21576,7 @@
         <v>bad_client</v>
       </c>
       <c r="AT174" t="s">
-        <v>485</v>
+        <v>482</v>
       </c>
       <c r="AU174" t="str">
         <f>IF(AND(Dataset!F174="Savings",Dataset!AT174="eligible"),"YES","NO")</f>
@@ -21564,10 +21584,10 @@
       </c>
       <c r="AW174" s="8"/>
       <c r="AX174" s="12" t="s">
+        <v>487</v>
+      </c>
+      <c r="AY174" s="8" t="s">
         <v>490</v>
-      </c>
-      <c r="AY174" s="8" t="s">
-        <v>493</v>
       </c>
       <c r="AZ174" s="8"/>
       <c r="BD174" t="str">
@@ -21666,7 +21686,7 @@
         <v>bad_client</v>
       </c>
       <c r="AT175" t="s">
-        <v>485</v>
+        <v>482</v>
       </c>
       <c r="AU175" t="str">
         <f>IF(AND(Dataset!F175="Savings",Dataset!AT175="eligible"),"YES","NO")</f>
@@ -21674,10 +21694,10 @@
       </c>
       <c r="AW175" s="8"/>
       <c r="AX175" s="12" t="s">
-        <v>490</v>
+        <v>487</v>
       </c>
       <c r="AY175" s="8" t="s">
-        <v>492</v>
+        <v>489</v>
       </c>
       <c r="AZ175" s="8"/>
       <c r="BD175" t="str">
@@ -21776,7 +21796,7 @@
         <v>bad_client</v>
       </c>
       <c r="AT176" t="s">
-        <v>485</v>
+        <v>482</v>
       </c>
       <c r="AU176" t="str">
         <f>IF(AND(Dataset!F176="Savings",Dataset!AT176="eligible"),"YES","NO")</f>
@@ -21784,10 +21804,10 @@
       </c>
       <c r="AW176" s="8"/>
       <c r="AX176" s="12" t="s">
-        <v>489</v>
+        <v>486</v>
       </c>
       <c r="AY176" s="8" t="s">
-        <v>493</v>
+        <v>490</v>
       </c>
       <c r="AZ176" s="8"/>
       <c r="BD176" t="str">
@@ -21886,7 +21906,7 @@
         <v>bad_client</v>
       </c>
       <c r="AT177" t="s">
-        <v>485</v>
+        <v>482</v>
       </c>
       <c r="AU177" t="str">
         <f>IF(AND(Dataset!F177="Savings",Dataset!AT177="eligible"),"YES","NO")</f>
@@ -21894,10 +21914,10 @@
       </c>
       <c r="AW177" s="8"/>
       <c r="AX177" s="12" t="s">
-        <v>490</v>
+        <v>487</v>
       </c>
       <c r="AY177" s="8" t="s">
-        <v>492</v>
+        <v>489</v>
       </c>
       <c r="AZ177" s="8"/>
       <c r="BD177" t="str">
@@ -21996,7 +22016,7 @@
         <v>good_client</v>
       </c>
       <c r="AT178" t="s">
-        <v>485</v>
+        <v>482</v>
       </c>
       <c r="AU178" t="str">
         <f>IF(AND(Dataset!F178="Savings",Dataset!AT178="eligible"),"YES","NO")</f>
@@ -22004,10 +22024,10 @@
       </c>
       <c r="AW178" s="8"/>
       <c r="AX178" s="12" t="s">
+        <v>487</v>
+      </c>
+      <c r="AY178" s="8" t="s">
         <v>490</v>
-      </c>
-      <c r="AY178" s="8" t="s">
-        <v>493</v>
       </c>
       <c r="AZ178" s="8"/>
       <c r="BD178" t="str">
@@ -22106,7 +22126,7 @@
         <v>bad_client</v>
       </c>
       <c r="AT179" t="s">
-        <v>485</v>
+        <v>482</v>
       </c>
       <c r="AU179" t="str">
         <f>IF(AND(Dataset!F179="Savings",Dataset!AT179="eligible"),"YES","NO")</f>
@@ -22114,10 +22134,10 @@
       </c>
       <c r="AW179" s="8"/>
       <c r="AX179" s="12" t="s">
+        <v>486</v>
+      </c>
+      <c r="AY179" s="8" t="s">
         <v>489</v>
-      </c>
-      <c r="AY179" s="8" t="s">
-        <v>492</v>
       </c>
       <c r="AZ179" s="8"/>
       <c r="BD179" t="str">
@@ -22216,7 +22236,7 @@
         <v>bad_client</v>
       </c>
       <c r="AT180" t="s">
-        <v>485</v>
+        <v>482</v>
       </c>
       <c r="AU180" t="str">
         <f>IF(AND(Dataset!F180="Savings",Dataset!AT180="eligible"),"YES","NO")</f>
@@ -22224,10 +22244,10 @@
       </c>
       <c r="AW180" s="8"/>
       <c r="AX180" s="12" t="s">
+        <v>487</v>
+      </c>
+      <c r="AY180" s="8" t="s">
         <v>490</v>
-      </c>
-      <c r="AY180" s="8" t="s">
-        <v>493</v>
       </c>
       <c r="AZ180" s="8"/>
       <c r="BD180" t="str">
@@ -22326,7 +22346,7 @@
         <v>bad_client</v>
       </c>
       <c r="AT181" t="s">
-        <v>485</v>
+        <v>482</v>
       </c>
       <c r="AU181" t="str">
         <f>IF(AND(Dataset!F181="Savings",Dataset!AT181="eligible"),"YES","NO")</f>
@@ -22334,10 +22354,10 @@
       </c>
       <c r="AW181" s="8"/>
       <c r="AX181" s="12" t="s">
+        <v>486</v>
+      </c>
+      <c r="AY181" s="8" t="s">
         <v>489</v>
-      </c>
-      <c r="AY181" s="8" t="s">
-        <v>492</v>
       </c>
       <c r="AZ181" s="8"/>
       <c r="BD181" t="str">
@@ -22436,7 +22456,7 @@
         <v>bad_client</v>
       </c>
       <c r="AT182" t="s">
-        <v>485</v>
+        <v>482</v>
       </c>
       <c r="AU182" t="str">
         <f>IF(AND(Dataset!F182="Savings",Dataset!AT182="eligible"),"YES","NO")</f>
@@ -22444,10 +22464,10 @@
       </c>
       <c r="AW182" s="8"/>
       <c r="AX182" s="12" t="s">
+        <v>487</v>
+      </c>
+      <c r="AY182" s="8" t="s">
         <v>490</v>
-      </c>
-      <c r="AY182" s="8" t="s">
-        <v>493</v>
       </c>
       <c r="AZ182" s="8"/>
       <c r="BD182" t="str">
@@ -22546,7 +22566,7 @@
         <v>bad_client</v>
       </c>
       <c r="AT183" t="s">
-        <v>485</v>
+        <v>482</v>
       </c>
       <c r="AU183" t="str">
         <f>IF(AND(Dataset!F183="Savings",Dataset!AT183="eligible"),"YES","NO")</f>
@@ -22554,10 +22574,10 @@
       </c>
       <c r="AW183" s="8"/>
       <c r="AX183" s="12" t="s">
-        <v>490</v>
+        <v>487</v>
       </c>
       <c r="AY183" s="8" t="s">
-        <v>492</v>
+        <v>489</v>
       </c>
       <c r="AZ183" s="8"/>
       <c r="BD183" t="str">
@@ -22656,7 +22676,7 @@
         <v>bad_client</v>
       </c>
       <c r="AT184" t="s">
-        <v>485</v>
+        <v>482</v>
       </c>
       <c r="AU184" t="str">
         <f>IF(AND(Dataset!F184="Savings",Dataset!AT184="eligible"),"YES","NO")</f>
@@ -22664,10 +22684,10 @@
       </c>
       <c r="AW184" s="8"/>
       <c r="AX184" s="12" t="s">
+        <v>487</v>
+      </c>
+      <c r="AY184" s="8" t="s">
         <v>490</v>
-      </c>
-      <c r="AY184" s="8" t="s">
-        <v>493</v>
       </c>
       <c r="AZ184" s="8"/>
       <c r="BD184" t="str">
@@ -22766,7 +22786,7 @@
         <v>bad_client</v>
       </c>
       <c r="AT185" t="s">
-        <v>485</v>
+        <v>482</v>
       </c>
       <c r="AU185" t="str">
         <f>IF(AND(Dataset!F185="Savings",Dataset!AT185="eligible"),"YES","NO")</f>
@@ -22774,10 +22794,10 @@
       </c>
       <c r="AW185" s="8"/>
       <c r="AX185" s="12" t="s">
-        <v>490</v>
+        <v>487</v>
       </c>
       <c r="AY185" s="8" t="s">
-        <v>492</v>
+        <v>489</v>
       </c>
       <c r="AZ185" s="8"/>
       <c r="BD185" t="str">
@@ -22876,7 +22896,7 @@
         <v>bad_client</v>
       </c>
       <c r="AT186" t="s">
-        <v>485</v>
+        <v>482</v>
       </c>
       <c r="AU186" t="str">
         <f>IF(AND(Dataset!F186="Savings",Dataset!AT186="eligible"),"YES","NO")</f>
@@ -22884,10 +22904,10 @@
       </c>
       <c r="AW186" s="8"/>
       <c r="AX186" s="12" t="s">
-        <v>489</v>
+        <v>486</v>
       </c>
       <c r="AY186" s="8" t="s">
-        <v>493</v>
+        <v>490</v>
       </c>
       <c r="AZ186" s="8"/>
       <c r="BD186" t="str">
@@ -22986,7 +23006,7 @@
         <v>bad_client</v>
       </c>
       <c r="AT187" t="s">
-        <v>485</v>
+        <v>482</v>
       </c>
       <c r="AU187" t="str">
         <f>IF(AND(Dataset!F187="Savings",Dataset!AT187="eligible"),"YES","NO")</f>
@@ -22994,10 +23014,10 @@
       </c>
       <c r="AW187" s="8"/>
       <c r="AX187" s="12" t="s">
+        <v>486</v>
+      </c>
+      <c r="AY187" s="8" t="s">
         <v>489</v>
-      </c>
-      <c r="AY187" s="8" t="s">
-        <v>492</v>
       </c>
       <c r="AZ187" s="8"/>
       <c r="BD187" t="str">
@@ -23096,7 +23116,7 @@
         <v>bad_client</v>
       </c>
       <c r="AT188" t="s">
-        <v>485</v>
+        <v>482</v>
       </c>
       <c r="AU188" t="str">
         <f>IF(AND(Dataset!F188="Savings",Dataset!AT188="eligible"),"YES","NO")</f>
@@ -23104,10 +23124,10 @@
       </c>
       <c r="AW188" s="8"/>
       <c r="AX188" s="12" t="s">
+        <v>487</v>
+      </c>
+      <c r="AY188" s="8" t="s">
         <v>490</v>
-      </c>
-      <c r="AY188" s="8" t="s">
-        <v>493</v>
       </c>
       <c r="AZ188" s="8"/>
       <c r="BD188" t="str">
@@ -23206,7 +23226,7 @@
         <v>bad_client</v>
       </c>
       <c r="AT189" t="s">
-        <v>485</v>
+        <v>482</v>
       </c>
       <c r="AU189" t="str">
         <f>IF(AND(Dataset!F189="Savings",Dataset!AT189="eligible"),"YES","NO")</f>
@@ -23214,10 +23234,10 @@
       </c>
       <c r="AW189" s="8"/>
       <c r="AX189" s="12" t="s">
-        <v>490</v>
+        <v>487</v>
       </c>
       <c r="AY189" s="8" t="s">
-        <v>492</v>
+        <v>489</v>
       </c>
       <c r="AZ189" s="8"/>
       <c r="BD189" t="str">
@@ -23316,7 +23336,7 @@
         <v>bad_client</v>
       </c>
       <c r="AT190" t="s">
-        <v>485</v>
+        <v>482</v>
       </c>
       <c r="AU190" t="str">
         <f>IF(AND(Dataset!F190="Savings",Dataset!AT190="eligible"),"YES","NO")</f>
@@ -23324,10 +23344,10 @@
       </c>
       <c r="AW190" s="8"/>
       <c r="AX190" s="12" t="s">
-        <v>489</v>
+        <v>486</v>
       </c>
       <c r="AY190" s="8" t="s">
-        <v>493</v>
+        <v>490</v>
       </c>
       <c r="AZ190" s="8"/>
       <c r="BD190" t="str">
@@ -23426,7 +23446,7 @@
         <v>bad_client</v>
       </c>
       <c r="AT191" t="s">
-        <v>485</v>
+        <v>482</v>
       </c>
       <c r="AU191" t="str">
         <f>IF(AND(Dataset!F191="Savings",Dataset!AT191="eligible"),"YES","NO")</f>
@@ -23434,10 +23454,10 @@
       </c>
       <c r="AW191" s="8"/>
       <c r="AX191" s="12" t="s">
+        <v>486</v>
+      </c>
+      <c r="AY191" s="8" t="s">
         <v>489</v>
-      </c>
-      <c r="AY191" s="8" t="s">
-        <v>492</v>
       </c>
       <c r="AZ191" s="8"/>
       <c r="BD191" t="str">
@@ -23536,7 +23556,7 @@
         <v>bad_client</v>
       </c>
       <c r="AT192" t="s">
-        <v>485</v>
+        <v>482</v>
       </c>
       <c r="AU192" t="str">
         <f>IF(AND(Dataset!F192="Savings",Dataset!AT192="eligible"),"YES","NO")</f>
@@ -23544,10 +23564,10 @@
       </c>
       <c r="AW192" s="8"/>
       <c r="AX192" s="12" t="s">
+        <v>487</v>
+      </c>
+      <c r="AY192" s="8" t="s">
         <v>490</v>
-      </c>
-      <c r="AY192" s="8" t="s">
-        <v>493</v>
       </c>
       <c r="AZ192" s="8"/>
       <c r="BD192" t="str">
@@ -23646,7 +23666,7 @@
         <v>bad_client</v>
       </c>
       <c r="AT193" t="s">
-        <v>485</v>
+        <v>482</v>
       </c>
       <c r="AU193" t="str">
         <f>IF(AND(Dataset!F193="Savings",Dataset!AT193="eligible"),"YES","NO")</f>
@@ -23654,10 +23674,10 @@
       </c>
       <c r="AW193" s="8"/>
       <c r="AX193" s="12" t="s">
-        <v>490</v>
+        <v>487</v>
       </c>
       <c r="AY193" s="8" t="s">
-        <v>492</v>
+        <v>489</v>
       </c>
       <c r="AZ193" s="8"/>
       <c r="BD193" t="str">
@@ -23756,7 +23776,7 @@
         <v>bad_client</v>
       </c>
       <c r="AT194" t="s">
-        <v>485</v>
+        <v>482</v>
       </c>
       <c r="AU194" t="str">
         <f>IF(AND(Dataset!F194="Savings",Dataset!AT194="eligible"),"YES","NO")</f>
@@ -23764,10 +23784,10 @@
       </c>
       <c r="AW194" s="8"/>
       <c r="AX194" s="12" t="s">
+        <v>487</v>
+      </c>
+      <c r="AY194" s="8" t="s">
         <v>490</v>
-      </c>
-      <c r="AY194" s="8" t="s">
-        <v>493</v>
       </c>
       <c r="AZ194" s="8"/>
       <c r="BD194" t="str">
@@ -23866,7 +23886,7 @@
         <v>good_client</v>
       </c>
       <c r="AT195" t="s">
-        <v>485</v>
+        <v>482</v>
       </c>
       <c r="AU195" t="str">
         <f>IF(AND(Dataset!F195="Savings",Dataset!AT195="eligible"),"YES","NO")</f>
@@ -23874,10 +23894,10 @@
       </c>
       <c r="AW195" s="8"/>
       <c r="AX195" s="12" t="s">
-        <v>490</v>
+        <v>487</v>
       </c>
       <c r="AY195" s="8" t="s">
-        <v>492</v>
+        <v>489</v>
       </c>
       <c r="AZ195" s="8"/>
       <c r="BD195" t="str">
@@ -23976,7 +23996,7 @@
         <v>bad_client</v>
       </c>
       <c r="AT196" t="s">
-        <v>485</v>
+        <v>482</v>
       </c>
       <c r="AU196" t="str">
         <f>IF(AND(Dataset!F196="Savings",Dataset!AT196="eligible"),"YES","NO")</f>
@@ -23984,10 +24004,10 @@
       </c>
       <c r="AW196" s="8"/>
       <c r="AX196" s="12" t="s">
+        <v>487</v>
+      </c>
+      <c r="AY196" s="8" t="s">
         <v>490</v>
-      </c>
-      <c r="AY196" s="8" t="s">
-        <v>493</v>
       </c>
       <c r="AZ196" s="8"/>
       <c r="BD196" t="str">
@@ -24086,7 +24106,7 @@
         <v>bad_client</v>
       </c>
       <c r="AT197" t="s">
-        <v>485</v>
+        <v>482</v>
       </c>
       <c r="AU197" t="str">
         <f>IF(AND(Dataset!F197="Savings",Dataset!AT197="eligible"),"YES","NO")</f>
@@ -24094,10 +24114,10 @@
       </c>
       <c r="AW197" s="8"/>
       <c r="AX197" s="12" t="s">
-        <v>490</v>
+        <v>487</v>
       </c>
       <c r="AY197" s="8" t="s">
-        <v>492</v>
+        <v>489</v>
       </c>
       <c r="AZ197" s="8"/>
       <c r="BD197" t="str">
@@ -24196,7 +24216,7 @@
         <v>bad_client</v>
       </c>
       <c r="AT198" t="s">
-        <v>485</v>
+        <v>482</v>
       </c>
       <c r="AU198" t="str">
         <f>IF(AND(Dataset!F198="Savings",Dataset!AT198="eligible"),"YES","NO")</f>
@@ -24204,10 +24224,10 @@
       </c>
       <c r="AW198" s="8"/>
       <c r="AX198" s="12" t="s">
-        <v>489</v>
+        <v>486</v>
       </c>
       <c r="AY198" s="8" t="s">
-        <v>493</v>
+        <v>490</v>
       </c>
       <c r="AZ198" s="8"/>
       <c r="BD198" t="str">
@@ -24306,7 +24326,7 @@
         <v>bad_client</v>
       </c>
       <c r="AT199" t="s">
-        <v>485</v>
+        <v>482</v>
       </c>
       <c r="AU199" t="str">
         <f>IF(AND(Dataset!F199="Savings",Dataset!AT199="eligible"),"YES","NO")</f>
@@ -24314,10 +24334,10 @@
       </c>
       <c r="AW199" s="8"/>
       <c r="AX199" s="12" t="s">
+        <v>486</v>
+      </c>
+      <c r="AY199" s="8" t="s">
         <v>489</v>
-      </c>
-      <c r="AY199" s="8" t="s">
-        <v>492</v>
       </c>
       <c r="AZ199" s="8"/>
       <c r="BD199" t="str">
@@ -24416,7 +24436,7 @@
         <v>bad_client</v>
       </c>
       <c r="AT200" t="s">
-        <v>485</v>
+        <v>482</v>
       </c>
       <c r="AU200" t="str">
         <f>IF(AND(Dataset!F200="Savings",Dataset!AT200="eligible"),"YES","NO")</f>
@@ -24424,10 +24444,10 @@
       </c>
       <c r="AW200" s="8"/>
       <c r="AX200" s="12" t="s">
-        <v>489</v>
+        <v>486</v>
       </c>
       <c r="AY200" s="8" t="s">
-        <v>493</v>
+        <v>490</v>
       </c>
       <c r="AZ200" s="8"/>
       <c r="BD200" t="str">
@@ -24526,7 +24546,7 @@
         <v>bad_client</v>
       </c>
       <c r="AT201" t="s">
-        <v>485</v>
+        <v>482</v>
       </c>
       <c r="AU201" t="str">
         <f>IF(AND(Dataset!F201="Savings",Dataset!AT201="eligible"),"YES","NO")</f>
@@ -24534,10 +24554,10 @@
       </c>
       <c r="AW201" s="8"/>
       <c r="AX201" s="12" t="s">
+        <v>486</v>
+      </c>
+      <c r="AY201" s="8" t="s">
         <v>489</v>
-      </c>
-      <c r="AY201" s="8" t="s">
-        <v>492</v>
       </c>
       <c r="AZ201" s="8"/>
       <c r="BD201" t="str">
@@ -24636,7 +24656,7 @@
         <v>bad_client</v>
       </c>
       <c r="AT202" t="s">
-        <v>485</v>
+        <v>482</v>
       </c>
       <c r="AU202" t="str">
         <f>IF(AND(Dataset!F202="Savings",Dataset!AT202="eligible"),"YES","NO")</f>
@@ -24644,10 +24664,10 @@
       </c>
       <c r="AW202" s="8"/>
       <c r="AX202" s="12" t="s">
-        <v>489</v>
+        <v>486</v>
       </c>
       <c r="AY202" s="8" t="s">
-        <v>493</v>
+        <v>490</v>
       </c>
       <c r="AZ202" s="8"/>
       <c r="BD202" t="str">
@@ -24746,7 +24766,7 @@
         <v>bad_client</v>
       </c>
       <c r="AT203" t="s">
-        <v>485</v>
+        <v>482</v>
       </c>
       <c r="AU203" t="str">
         <f>IF(AND(Dataset!F203="Savings",Dataset!AT203="eligible"),"YES","NO")</f>
@@ -24754,10 +24774,10 @@
       </c>
       <c r="AW203" s="8"/>
       <c r="AX203" s="12" t="s">
+        <v>486</v>
+      </c>
+      <c r="AY203" s="8" t="s">
         <v>489</v>
-      </c>
-      <c r="AY203" s="8" t="s">
-        <v>492</v>
       </c>
       <c r="AZ203" s="8"/>
       <c r="BD203" t="str">
@@ -24856,7 +24876,7 @@
         <v>bad_client</v>
       </c>
       <c r="AT204" t="s">
-        <v>485</v>
+        <v>482</v>
       </c>
       <c r="AU204" t="str">
         <f>IF(AND(Dataset!F204="Savings",Dataset!AT204="eligible"),"YES","NO")</f>
@@ -24864,10 +24884,10 @@
       </c>
       <c r="AW204" s="8"/>
       <c r="AX204" s="12" t="s">
+        <v>487</v>
+      </c>
+      <c r="AY204" s="8" t="s">
         <v>490</v>
-      </c>
-      <c r="AY204" s="8" t="s">
-        <v>493</v>
       </c>
       <c r="AZ204" s="8"/>
       <c r="BD204" t="str">
@@ -24966,7 +24986,7 @@
         <v>bad_client</v>
       </c>
       <c r="AT205" t="s">
-        <v>485</v>
+        <v>482</v>
       </c>
       <c r="AU205" t="str">
         <f>IF(AND(Dataset!F205="Savings",Dataset!AT205="eligible"),"YES","NO")</f>
@@ -24974,10 +24994,10 @@
       </c>
       <c r="AW205" s="8"/>
       <c r="AX205" s="12" t="s">
-        <v>490</v>
+        <v>487</v>
       </c>
       <c r="AY205" s="8" t="s">
-        <v>492</v>
+        <v>489</v>
       </c>
       <c r="AZ205" s="8"/>
       <c r="BD205" t="str">
@@ -25076,7 +25096,7 @@
         <v>bad_client</v>
       </c>
       <c r="AT206" t="s">
-        <v>485</v>
+        <v>482</v>
       </c>
       <c r="AU206" t="str">
         <f>IF(AND(Dataset!F206="Savings",Dataset!AT206="eligible"),"YES","NO")</f>
@@ -25084,10 +25104,10 @@
       </c>
       <c r="AW206" s="8"/>
       <c r="AX206" s="12" t="s">
+        <v>487</v>
+      </c>
+      <c r="AY206" s="8" t="s">
         <v>490</v>
-      </c>
-      <c r="AY206" s="8" t="s">
-        <v>493</v>
       </c>
       <c r="AZ206" s="8"/>
       <c r="BD206" t="str">
@@ -25186,7 +25206,7 @@
         <v>bad_client</v>
       </c>
       <c r="AT207" t="s">
-        <v>485</v>
+        <v>482</v>
       </c>
       <c r="AU207" t="str">
         <f>IF(AND(Dataset!F207="Savings",Dataset!AT207="eligible"),"YES","NO")</f>
@@ -25194,10 +25214,10 @@
       </c>
       <c r="AW207" s="8"/>
       <c r="AX207" s="12" t="s">
-        <v>490</v>
+        <v>487</v>
       </c>
       <c r="AY207" s="8" t="s">
-        <v>492</v>
+        <v>489</v>
       </c>
       <c r="AZ207" s="8"/>
       <c r="BD207" t="str">
@@ -25296,7 +25316,7 @@
         <v>bad_client</v>
       </c>
       <c r="AT208" t="s">
-        <v>485</v>
+        <v>482</v>
       </c>
       <c r="AU208" t="str">
         <f>IF(AND(Dataset!F208="Savings",Dataset!AT208="eligible"),"YES","NO")</f>
@@ -25304,10 +25324,10 @@
       </c>
       <c r="AW208" s="8"/>
       <c r="AX208" s="12" t="s">
+        <v>487</v>
+      </c>
+      <c r="AY208" s="8" t="s">
         <v>490</v>
-      </c>
-      <c r="AY208" s="8" t="s">
-        <v>493</v>
       </c>
       <c r="AZ208" s="8"/>
       <c r="BD208" t="str">
@@ -25406,7 +25426,7 @@
         <v>bad_client</v>
       </c>
       <c r="AT209" t="s">
-        <v>485</v>
+        <v>482</v>
       </c>
       <c r="AU209" t="str">
         <f>IF(AND(Dataset!F209="Savings",Dataset!AT209="eligible"),"YES","NO")</f>
@@ -25414,10 +25434,10 @@
       </c>
       <c r="AW209" s="8"/>
       <c r="AX209" s="12" t="s">
-        <v>490</v>
+        <v>487</v>
       </c>
       <c r="AY209" s="8" t="s">
-        <v>492</v>
+        <v>489</v>
       </c>
       <c r="AZ209" s="8"/>
       <c r="BD209" t="str">
@@ -25516,7 +25536,7 @@
         <v>bad_client</v>
       </c>
       <c r="AT210" t="s">
-        <v>485</v>
+        <v>482</v>
       </c>
       <c r="AU210" t="str">
         <f>IF(AND(Dataset!F210="Savings",Dataset!AT210="eligible"),"YES","NO")</f>
@@ -25524,10 +25544,10 @@
       </c>
       <c r="AW210" s="8"/>
       <c r="AX210" s="12" t="s">
+        <v>487</v>
+      </c>
+      <c r="AY210" s="8" t="s">
         <v>490</v>
-      </c>
-      <c r="AY210" s="8" t="s">
-        <v>493</v>
       </c>
       <c r="AZ210" s="8"/>
       <c r="BD210" t="str">
@@ -25626,7 +25646,7 @@
         <v>bad_client</v>
       </c>
       <c r="AT211" t="s">
-        <v>485</v>
+        <v>482</v>
       </c>
       <c r="AU211" t="str">
         <f>IF(AND(Dataset!F211="Savings",Dataset!AT211="eligible"),"YES","NO")</f>
@@ -25634,10 +25654,10 @@
       </c>
       <c r="AW211" s="8"/>
       <c r="AX211" s="12" t="s">
-        <v>490</v>
+        <v>487</v>
       </c>
       <c r="AY211" s="8" t="s">
-        <v>492</v>
+        <v>489</v>
       </c>
       <c r="AZ211" s="8"/>
       <c r="BD211" t="str">
@@ -25736,7 +25756,7 @@
         <v>bad_client</v>
       </c>
       <c r="AT212" t="s">
-        <v>485</v>
+        <v>482</v>
       </c>
       <c r="AU212" t="str">
         <f>IF(AND(Dataset!F212="Savings",Dataset!AT212="eligible"),"YES","NO")</f>
@@ -25744,10 +25764,10 @@
       </c>
       <c r="AW212" s="8"/>
       <c r="AX212" s="12" t="s">
+        <v>487</v>
+      </c>
+      <c r="AY212" s="8" t="s">
         <v>490</v>
-      </c>
-      <c r="AY212" s="8" t="s">
-        <v>493</v>
       </c>
       <c r="AZ212" s="8"/>
       <c r="BD212" t="str">
@@ -25846,7 +25866,7 @@
         <v>bad_client</v>
       </c>
       <c r="AT213" t="s">
-        <v>485</v>
+        <v>482</v>
       </c>
       <c r="AU213" t="str">
         <f>IF(AND(Dataset!F213="Savings",Dataset!AT213="eligible"),"YES","NO")</f>
@@ -25854,10 +25874,10 @@
       </c>
       <c r="AW213" s="8"/>
       <c r="AX213" s="12" t="s">
-        <v>490</v>
+        <v>487</v>
       </c>
       <c r="AY213" s="8" t="s">
-        <v>492</v>
+        <v>489</v>
       </c>
       <c r="AZ213" s="8"/>
       <c r="BD213" t="str">
@@ -25956,7 +25976,7 @@
         <v>bad_client</v>
       </c>
       <c r="AT214" t="s">
-        <v>485</v>
+        <v>482</v>
       </c>
       <c r="AU214" t="str">
         <f>IF(AND(Dataset!F214="Savings",Dataset!AT214="eligible"),"YES","NO")</f>
@@ -25964,10 +25984,10 @@
       </c>
       <c r="AW214" s="8"/>
       <c r="AX214" s="12" t="s">
+        <v>487</v>
+      </c>
+      <c r="AY214" s="8" t="s">
         <v>490</v>
-      </c>
-      <c r="AY214" s="8" t="s">
-        <v>493</v>
       </c>
       <c r="AZ214" s="8"/>
       <c r="BD214" t="str">
@@ -26066,7 +26086,7 @@
         <v>bad_client</v>
       </c>
       <c r="AT215" t="s">
-        <v>485</v>
+        <v>482</v>
       </c>
       <c r="AU215" t="str">
         <f>IF(AND(Dataset!F215="Savings",Dataset!AT215="eligible"),"YES","NO")</f>
@@ -26074,10 +26094,10 @@
       </c>
       <c r="AW215" s="8"/>
       <c r="AX215" s="12" t="s">
+        <v>486</v>
+      </c>
+      <c r="AY215" s="8" t="s">
         <v>489</v>
-      </c>
-      <c r="AY215" s="8" t="s">
-        <v>492</v>
       </c>
       <c r="AZ215" s="8"/>
       <c r="BD215" t="str">
@@ -26176,7 +26196,7 @@
         <v>bad_client</v>
       </c>
       <c r="AT216" t="s">
-        <v>485</v>
+        <v>482</v>
       </c>
       <c r="AU216" t="str">
         <f>IF(AND(Dataset!F216="Savings",Dataset!AT216="eligible"),"YES","NO")</f>
@@ -26184,10 +26204,10 @@
       </c>
       <c r="AW216" s="8"/>
       <c r="AX216" s="12" t="s">
-        <v>489</v>
+        <v>486</v>
       </c>
       <c r="AY216" s="8" t="s">
-        <v>493</v>
+        <v>490</v>
       </c>
       <c r="AZ216" s="8"/>
       <c r="BD216" t="str">
@@ -26286,7 +26306,7 @@
         <v>bad_client</v>
       </c>
       <c r="AT217" t="s">
-        <v>485</v>
+        <v>482</v>
       </c>
       <c r="AU217" t="str">
         <f>IF(AND(Dataset!F217="Savings",Dataset!AT217="eligible"),"YES","NO")</f>
@@ -26294,10 +26314,10 @@
       </c>
       <c r="AW217" s="8"/>
       <c r="AX217" s="12" t="s">
+        <v>486</v>
+      </c>
+      <c r="AY217" s="8" t="s">
         <v>489</v>
-      </c>
-      <c r="AY217" s="8" t="s">
-        <v>492</v>
       </c>
       <c r="AZ217" s="8"/>
       <c r="BD217" t="str">
@@ -26396,7 +26416,7 @@
         <v>bad_client</v>
       </c>
       <c r="AT218" t="s">
-        <v>485</v>
+        <v>482</v>
       </c>
       <c r="AU218" t="str">
         <f>IF(AND(Dataset!F218="Savings",Dataset!AT218="eligible"),"YES","NO")</f>
@@ -26404,10 +26424,10 @@
       </c>
       <c r="AW218" s="8"/>
       <c r="AX218" s="12" t="s">
+        <v>487</v>
+      </c>
+      <c r="AY218" s="8" t="s">
         <v>490</v>
-      </c>
-      <c r="AY218" s="8" t="s">
-        <v>493</v>
       </c>
       <c r="AZ218" s="8"/>
       <c r="BD218" t="str">
@@ -26506,7 +26526,7 @@
         <v>bad_client</v>
       </c>
       <c r="AT219" t="s">
-        <v>485</v>
+        <v>482</v>
       </c>
       <c r="AU219" t="str">
         <f>IF(AND(Dataset!F219="Savings",Dataset!AT219="eligible"),"YES","NO")</f>
@@ -26514,10 +26534,10 @@
       </c>
       <c r="AW219" s="8"/>
       <c r="AX219" s="12" t="s">
-        <v>490</v>
+        <v>487</v>
       </c>
       <c r="AY219" s="8" t="s">
-        <v>492</v>
+        <v>489</v>
       </c>
       <c r="AZ219" s="8"/>
       <c r="BD219" t="str">
@@ -26616,7 +26636,7 @@
         <v>bad_client</v>
       </c>
       <c r="AT220" t="s">
-        <v>485</v>
+        <v>482</v>
       </c>
       <c r="AU220" t="str">
         <f>IF(AND(Dataset!F220="Savings",Dataset!AT220="eligible"),"YES","NO")</f>
@@ -26624,10 +26644,10 @@
       </c>
       <c r="AW220" s="8"/>
       <c r="AX220" s="12" t="s">
+        <v>487</v>
+      </c>
+      <c r="AY220" s="8" t="s">
         <v>490</v>
-      </c>
-      <c r="AY220" s="8" t="s">
-        <v>493</v>
       </c>
       <c r="AZ220" s="8"/>
       <c r="BD220" t="str">
@@ -26726,7 +26746,7 @@
         <v>bad_client</v>
       </c>
       <c r="AT221" t="s">
-        <v>485</v>
+        <v>482</v>
       </c>
       <c r="AU221" t="str">
         <f>IF(AND(Dataset!F221="Savings",Dataset!AT221="eligible"),"YES","NO")</f>
@@ -26734,10 +26754,10 @@
       </c>
       <c r="AW221" s="8"/>
       <c r="AX221" s="12" t="s">
-        <v>490</v>
+        <v>487</v>
       </c>
       <c r="AY221" s="8" t="s">
-        <v>492</v>
+        <v>489</v>
       </c>
       <c r="AZ221" s="8"/>
       <c r="BD221" t="str">
@@ -26836,7 +26856,7 @@
         <v>bad_client</v>
       </c>
       <c r="AT222" t="s">
-        <v>485</v>
+        <v>482</v>
       </c>
       <c r="AU222" t="str">
         <f>IF(AND(Dataset!F222="Savings",Dataset!AT222="eligible"),"YES","NO")</f>
@@ -26844,10 +26864,10 @@
       </c>
       <c r="AW222" s="8"/>
       <c r="AX222" s="12" t="s">
+        <v>487</v>
+      </c>
+      <c r="AY222" s="8" t="s">
         <v>490</v>
-      </c>
-      <c r="AY222" s="8" t="s">
-        <v>493</v>
       </c>
       <c r="AZ222" s="8"/>
       <c r="BD222" t="str">
@@ -26946,7 +26966,7 @@
         <v>bad_client</v>
       </c>
       <c r="AT223" t="s">
-        <v>485</v>
+        <v>482</v>
       </c>
       <c r="AU223" t="str">
         <f>IF(AND(Dataset!F223="Savings",Dataset!AT223="eligible"),"YES","NO")</f>
@@ -26954,10 +26974,10 @@
       </c>
       <c r="AW223" s="8"/>
       <c r="AX223" s="12" t="s">
-        <v>490</v>
+        <v>487</v>
       </c>
       <c r="AY223" s="8" t="s">
-        <v>492</v>
+        <v>489</v>
       </c>
       <c r="AZ223" s="8"/>
       <c r="BD223" t="str">
@@ -27056,7 +27076,7 @@
         <v>bad_client</v>
       </c>
       <c r="AT224" t="s">
-        <v>485</v>
+        <v>482</v>
       </c>
       <c r="AU224" t="str">
         <f>IF(AND(Dataset!F224="Savings",Dataset!AT224="eligible"),"YES","NO")</f>
@@ -27064,10 +27084,10 @@
       </c>
       <c r="AW224" s="8"/>
       <c r="AX224" s="12" t="s">
+        <v>487</v>
+      </c>
+      <c r="AY224" s="8" t="s">
         <v>490</v>
-      </c>
-      <c r="AY224" s="8" t="s">
-        <v>493</v>
       </c>
       <c r="AZ224" s="8"/>
       <c r="BD224" t="str">
@@ -27166,7 +27186,7 @@
         <v>good_client</v>
       </c>
       <c r="AT225" t="s">
-        <v>485</v>
+        <v>482</v>
       </c>
       <c r="AU225" t="str">
         <f>IF(AND(Dataset!F225="Savings",Dataset!AT225="eligible"),"YES","NO")</f>
@@ -27174,10 +27194,10 @@
       </c>
       <c r="AW225" s="8"/>
       <c r="AX225" s="12" t="s">
-        <v>490</v>
+        <v>487</v>
       </c>
       <c r="AY225" s="8" t="s">
-        <v>492</v>
+        <v>489</v>
       </c>
       <c r="AZ225" s="8"/>
       <c r="BD225" t="str">
@@ -27276,7 +27296,7 @@
         <v>bad_client</v>
       </c>
       <c r="AT226" t="s">
-        <v>485</v>
+        <v>482</v>
       </c>
       <c r="AU226" t="str">
         <f>IF(AND(Dataset!F226="Savings",Dataset!AT226="eligible"),"YES","NO")</f>
@@ -27284,10 +27304,10 @@
       </c>
       <c r="AW226" s="8"/>
       <c r="AX226" s="12" t="s">
-        <v>489</v>
+        <v>486</v>
       </c>
       <c r="AY226" s="8" t="s">
-        <v>493</v>
+        <v>490</v>
       </c>
       <c r="AZ226" s="8"/>
       <c r="BD226" t="str">
@@ -27386,7 +27406,7 @@
         <v>good_client</v>
       </c>
       <c r="AT227" t="s">
-        <v>485</v>
+        <v>482</v>
       </c>
       <c r="AU227" t="str">
         <f>IF(AND(Dataset!F227="Savings",Dataset!AT227="eligible"),"YES","NO")</f>
@@ -27394,10 +27414,10 @@
       </c>
       <c r="AW227" s="8"/>
       <c r="AX227" s="12" t="s">
+        <v>486</v>
+      </c>
+      <c r="AY227" s="8" t="s">
         <v>489</v>
-      </c>
-      <c r="AY227" s="8" t="s">
-        <v>492</v>
       </c>
       <c r="AZ227" s="8"/>
       <c r="BD227" t="str">
@@ -27496,7 +27516,7 @@
         <v>bad_client</v>
       </c>
       <c r="AT228" t="s">
-        <v>485</v>
+        <v>482</v>
       </c>
       <c r="AU228" t="str">
         <f>IF(AND(Dataset!F228="Savings",Dataset!AT228="eligible"),"YES","NO")</f>
@@ -27504,10 +27524,10 @@
       </c>
       <c r="AW228" s="8"/>
       <c r="AX228" s="12" t="s">
-        <v>489</v>
+        <v>486</v>
       </c>
       <c r="AY228" s="8" t="s">
-        <v>493</v>
+        <v>490</v>
       </c>
       <c r="AZ228" s="8"/>
       <c r="BD228" t="str">
@@ -27606,7 +27626,7 @@
         <v>bad_client</v>
       </c>
       <c r="AT229" t="s">
-        <v>485</v>
+        <v>482</v>
       </c>
       <c r="AU229" t="str">
         <f>IF(AND(Dataset!F229="Savings",Dataset!AT229="eligible"),"YES","NO")</f>
@@ -27614,10 +27634,10 @@
       </c>
       <c r="AW229" s="8"/>
       <c r="AX229" s="12" t="s">
+        <v>486</v>
+      </c>
+      <c r="AY229" s="8" t="s">
         <v>489</v>
-      </c>
-      <c r="AY229" s="8" t="s">
-        <v>492</v>
       </c>
       <c r="AZ229" s="8"/>
       <c r="BD229" t="str">
@@ -27716,7 +27736,7 @@
         <v>bad_client</v>
       </c>
       <c r="AT230" t="s">
-        <v>485</v>
+        <v>482</v>
       </c>
       <c r="AU230" t="str">
         <f>IF(AND(Dataset!F230="Savings",Dataset!AT230="eligible"),"YES","NO")</f>
@@ -27724,10 +27744,10 @@
       </c>
       <c r="AW230" s="8"/>
       <c r="AX230" s="12" t="s">
+        <v>487</v>
+      </c>
+      <c r="AY230" s="8" t="s">
         <v>490</v>
-      </c>
-      <c r="AY230" s="8" t="s">
-        <v>493</v>
       </c>
       <c r="AZ230" s="8"/>
       <c r="BD230" t="str">
@@ -27826,7 +27846,7 @@
         <v>bad_client</v>
       </c>
       <c r="AT231" t="s">
-        <v>485</v>
+        <v>482</v>
       </c>
       <c r="AU231" t="str">
         <f>IF(AND(Dataset!F231="Savings",Dataset!AT231="eligible"),"YES","NO")</f>
@@ -27834,10 +27854,10 @@
       </c>
       <c r="AW231" s="8"/>
       <c r="AX231" s="12" t="s">
-        <v>490</v>
+        <v>487</v>
       </c>
       <c r="AY231" s="8" t="s">
-        <v>492</v>
+        <v>489</v>
       </c>
       <c r="AZ231" s="8"/>
       <c r="BD231" t="str">
@@ -27936,7 +27956,7 @@
         <v>bad_client</v>
       </c>
       <c r="AT232" t="s">
-        <v>485</v>
+        <v>482</v>
       </c>
       <c r="AU232" t="str">
         <f>IF(AND(Dataset!F232="Savings",Dataset!AT232="eligible"),"YES","NO")</f>
@@ -27944,10 +27964,10 @@
       </c>
       <c r="AW232" s="8"/>
       <c r="AX232" s="12" t="s">
+        <v>487</v>
+      </c>
+      <c r="AY232" s="8" t="s">
         <v>490</v>
-      </c>
-      <c r="AY232" s="8" t="s">
-        <v>493</v>
       </c>
       <c r="AZ232" s="8"/>
       <c r="BD232" t="str">
@@ -28046,7 +28066,7 @@
         <v>good_client</v>
       </c>
       <c r="AT233" t="s">
-        <v>485</v>
+        <v>482</v>
       </c>
       <c r="AU233" t="str">
         <f>IF(AND(Dataset!F233="Savings",Dataset!AT233="eligible"),"YES","NO")</f>
@@ -28054,10 +28074,10 @@
       </c>
       <c r="AW233" s="8"/>
       <c r="AX233" s="12" t="s">
-        <v>490</v>
+        <v>487</v>
       </c>
       <c r="AY233" s="8" t="s">
-        <v>492</v>
+        <v>489</v>
       </c>
       <c r="AZ233" s="8"/>
       <c r="BD233" t="str">
@@ -28156,7 +28176,7 @@
         <v>bad_client</v>
       </c>
       <c r="AT234" t="s">
-        <v>485</v>
+        <v>482</v>
       </c>
       <c r="AU234" t="str">
         <f>IF(AND(Dataset!F234="Savings",Dataset!AT234="eligible"),"YES","NO")</f>
@@ -28164,10 +28184,10 @@
       </c>
       <c r="AW234" s="8"/>
       <c r="AX234" s="12" t="s">
+        <v>487</v>
+      </c>
+      <c r="AY234" s="8" t="s">
         <v>490</v>
-      </c>
-      <c r="AY234" s="8" t="s">
-        <v>493</v>
       </c>
       <c r="AZ234" s="8"/>
       <c r="BD234" t="str">
@@ -28266,7 +28286,7 @@
         <v>bad_client</v>
       </c>
       <c r="AT235" t="s">
-        <v>485</v>
+        <v>482</v>
       </c>
       <c r="AU235" t="str">
         <f>IF(AND(Dataset!F235="Savings",Dataset!AT235="eligible"),"YES","NO")</f>
@@ -28274,10 +28294,10 @@
       </c>
       <c r="AW235" s="8"/>
       <c r="AX235" s="12" t="s">
-        <v>490</v>
+        <v>487</v>
       </c>
       <c r="AY235" s="8" t="s">
-        <v>492</v>
+        <v>489</v>
       </c>
       <c r="AZ235" s="8"/>
       <c r="BD235" t="str">
@@ -28376,7 +28396,7 @@
         <v>bad_client</v>
       </c>
       <c r="AT236" t="s">
-        <v>485</v>
+        <v>482</v>
       </c>
       <c r="AU236" t="str">
         <f>IF(AND(Dataset!F236="Savings",Dataset!AT236="eligible"),"YES","NO")</f>
@@ -28384,10 +28404,10 @@
       </c>
       <c r="AW236" s="8"/>
       <c r="AX236" s="12" t="s">
-        <v>489</v>
+        <v>486</v>
       </c>
       <c r="AY236" s="8" t="s">
-        <v>493</v>
+        <v>490</v>
       </c>
       <c r="AZ236" s="8"/>
       <c r="BD236" t="str">
@@ -28486,7 +28506,7 @@
         <v>bad_client</v>
       </c>
       <c r="AT237" t="s">
-        <v>485</v>
+        <v>482</v>
       </c>
       <c r="AU237" t="str">
         <f>IF(AND(Dataset!F237="Savings",Dataset!AT237="eligible"),"YES","NO")</f>
@@ -28494,10 +28514,10 @@
       </c>
       <c r="AW237" s="8"/>
       <c r="AX237" s="12" t="s">
+        <v>486</v>
+      </c>
+      <c r="AY237" s="8" t="s">
         <v>489</v>
-      </c>
-      <c r="AY237" s="8" t="s">
-        <v>492</v>
       </c>
       <c r="AZ237" s="8"/>
       <c r="BD237" t="str">
@@ -28596,7 +28616,7 @@
         <v>bad_client</v>
       </c>
       <c r="AT238" t="s">
-        <v>485</v>
+        <v>482</v>
       </c>
       <c r="AU238" t="str">
         <f>IF(AND(Dataset!F238="Savings",Dataset!AT238="eligible"),"YES","NO")</f>
@@ -28604,10 +28624,10 @@
       </c>
       <c r="AW238" s="8"/>
       <c r="AX238" s="12" t="s">
-        <v>489</v>
+        <v>486</v>
       </c>
       <c r="AY238" s="8" t="s">
-        <v>493</v>
+        <v>490</v>
       </c>
       <c r="AZ238" s="8"/>
       <c r="BD238" t="str">
@@ -28706,7 +28726,7 @@
         <v>bad_client</v>
       </c>
       <c r="AT239" t="s">
-        <v>485</v>
+        <v>482</v>
       </c>
       <c r="AU239" t="str">
         <f>IF(AND(Dataset!F239="Savings",Dataset!AT239="eligible"),"YES","NO")</f>
@@ -28714,10 +28734,10 @@
       </c>
       <c r="AW239" s="8"/>
       <c r="AX239" s="12" t="s">
-        <v>490</v>
+        <v>487</v>
       </c>
       <c r="AY239" s="8" t="s">
-        <v>492</v>
+        <v>489</v>
       </c>
       <c r="AZ239" s="8"/>
       <c r="BD239" t="str">
@@ -28816,7 +28836,7 @@
         <v>bad_client</v>
       </c>
       <c r="AT240" t="s">
-        <v>485</v>
+        <v>482</v>
       </c>
       <c r="AU240" t="str">
         <f>IF(AND(Dataset!F240="Savings",Dataset!AT240="eligible"),"YES","NO")</f>
@@ -28824,10 +28844,10 @@
       </c>
       <c r="AW240" s="8"/>
       <c r="AX240" s="12" t="s">
+        <v>487</v>
+      </c>
+      <c r="AY240" s="8" t="s">
         <v>490</v>
-      </c>
-      <c r="AY240" s="8" t="s">
-        <v>493</v>
       </c>
       <c r="AZ240" s="8"/>
       <c r="BD240" t="str">
@@ -28926,7 +28946,7 @@
         <v>bad_client</v>
       </c>
       <c r="AT241" t="s">
-        <v>485</v>
+        <v>482</v>
       </c>
       <c r="AU241" t="str">
         <f>IF(AND(Dataset!F241="Savings",Dataset!AT241="eligible"),"YES","NO")</f>
@@ -28934,10 +28954,10 @@
       </c>
       <c r="AW241" s="8"/>
       <c r="AX241" s="12" t="s">
-        <v>490</v>
+        <v>487</v>
       </c>
       <c r="AY241" s="8" t="s">
-        <v>492</v>
+        <v>489</v>
       </c>
       <c r="AZ241" s="8"/>
       <c r="BD241" t="str">
@@ -29036,7 +29056,7 @@
         <v>good_client</v>
       </c>
       <c r="AT242" t="s">
-        <v>485</v>
+        <v>482</v>
       </c>
       <c r="AU242" t="str">
         <f>IF(AND(Dataset!F242="Savings",Dataset!AT242="eligible"),"YES","NO")</f>
@@ -29044,10 +29064,10 @@
       </c>
       <c r="AW242" s="8"/>
       <c r="AX242" s="12" t="s">
-        <v>490</v>
+        <v>487</v>
       </c>
       <c r="AY242" s="8" t="s">
-        <v>492</v>
+        <v>489</v>
       </c>
       <c r="AZ242" s="8"/>
       <c r="BD242" t="str">
@@ -29146,7 +29166,7 @@
         <v>bad_client</v>
       </c>
       <c r="AT243" t="s">
-        <v>485</v>
+        <v>482</v>
       </c>
       <c r="AU243" t="str">
         <f>IF(AND(Dataset!F243="Savings",Dataset!AT243="eligible"),"YES","NO")</f>
@@ -29154,10 +29174,10 @@
       </c>
       <c r="AW243" s="8"/>
       <c r="AX243" s="12" t="s">
+        <v>487</v>
+      </c>
+      <c r="AY243" s="8" t="s">
         <v>490</v>
-      </c>
-      <c r="AY243" s="8" t="s">
-        <v>493</v>
       </c>
       <c r="AZ243" s="8"/>
       <c r="BD243" t="str">
@@ -29256,7 +29276,7 @@
         <v>bad_client</v>
       </c>
       <c r="AT244" t="s">
-        <v>485</v>
+        <v>482</v>
       </c>
       <c r="AU244" t="str">
         <f>IF(AND(Dataset!F244="Savings",Dataset!AT244="eligible"),"YES","NO")</f>
@@ -29264,10 +29284,10 @@
       </c>
       <c r="AW244" s="8"/>
       <c r="AX244" s="12" t="s">
+        <v>486</v>
+      </c>
+      <c r="AY244" s="8" t="s">
         <v>489</v>
-      </c>
-      <c r="AY244" s="8" t="s">
-        <v>492</v>
       </c>
       <c r="AZ244" s="8"/>
       <c r="BD244" t="str">
@@ -29366,7 +29386,7 @@
         <v>bad_client</v>
       </c>
       <c r="AT245" t="s">
-        <v>485</v>
+        <v>482</v>
       </c>
       <c r="AU245" t="str">
         <f>IF(AND(Dataset!F245="Savings",Dataset!AT245="eligible"),"YES","NO")</f>
@@ -29374,10 +29394,10 @@
       </c>
       <c r="AW245" s="8"/>
       <c r="AX245" s="12" t="s">
-        <v>490</v>
+        <v>487</v>
       </c>
       <c r="AY245" s="8" t="s">
-        <v>492</v>
+        <v>489</v>
       </c>
       <c r="AZ245" s="8"/>
       <c r="BD245" t="str">
@@ -29476,7 +29496,7 @@
         <v>bad_client</v>
       </c>
       <c r="AT246" t="s">
-        <v>485</v>
+        <v>482</v>
       </c>
       <c r="AU246" t="str">
         <f>IF(AND(Dataset!F246="Savings",Dataset!AT246="eligible"),"YES","NO")</f>
@@ -29484,10 +29504,10 @@
       </c>
       <c r="AW246" s="8"/>
       <c r="AX246" s="12" t="s">
+        <v>487</v>
+      </c>
+      <c r="AY246" s="8" t="s">
         <v>490</v>
-      </c>
-      <c r="AY246" s="8" t="s">
-        <v>493</v>
       </c>
       <c r="AZ246" s="8"/>
       <c r="BD246" t="str">
@@ -29586,7 +29606,7 @@
         <v>bad_client</v>
       </c>
       <c r="AT247" t="s">
-        <v>485</v>
+        <v>482</v>
       </c>
       <c r="AU247" t="str">
         <f>IF(AND(Dataset!F247="Savings",Dataset!AT247="eligible"),"YES","NO")</f>
@@ -29594,10 +29614,10 @@
       </c>
       <c r="AW247" s="8"/>
       <c r="AX247" s="12" t="s">
-        <v>490</v>
+        <v>487</v>
       </c>
       <c r="AY247" s="8" t="s">
-        <v>492</v>
+        <v>489</v>
       </c>
       <c r="AZ247" s="8"/>
       <c r="BD247" t="str">
@@ -29696,7 +29716,7 @@
         <v>bad_client</v>
       </c>
       <c r="AT248" t="s">
-        <v>485</v>
+        <v>482</v>
       </c>
       <c r="AU248" t="str">
         <f>IF(AND(Dataset!F248="Savings",Dataset!AT248="eligible"),"YES","NO")</f>
@@ -29704,10 +29724,10 @@
       </c>
       <c r="AW248" s="8"/>
       <c r="AX248" s="12" t="s">
+        <v>487</v>
+      </c>
+      <c r="AY248" s="8" t="s">
         <v>490</v>
-      </c>
-      <c r="AY248" s="8" t="s">
-        <v>493</v>
       </c>
       <c r="AZ248" s="8"/>
       <c r="BD248" t="str">
@@ -29806,7 +29826,7 @@
         <v>bad_client</v>
       </c>
       <c r="AT249" t="s">
-        <v>485</v>
+        <v>482</v>
       </c>
       <c r="AU249" t="str">
         <f>IF(AND(Dataset!F249="Savings",Dataset!AT249="eligible"),"YES","NO")</f>
@@ -29814,10 +29834,10 @@
       </c>
       <c r="AW249" s="8"/>
       <c r="AX249" s="12" t="s">
-        <v>490</v>
+        <v>487</v>
       </c>
       <c r="AY249" s="8" t="s">
-        <v>492</v>
+        <v>489</v>
       </c>
       <c r="AZ249" s="8"/>
       <c r="BD249" t="str">
@@ -29916,7 +29936,7 @@
         <v>bad_client</v>
       </c>
       <c r="AT250" t="s">
-        <v>485</v>
+        <v>482</v>
       </c>
       <c r="AU250" t="str">
         <f>IF(AND(Dataset!F250="Savings",Dataset!AT250="eligible"),"YES","NO")</f>
@@ -29924,10 +29944,10 @@
       </c>
       <c r="AW250" s="8"/>
       <c r="AX250" s="12" t="s">
-        <v>490</v>
+        <v>487</v>
       </c>
       <c r="AY250" s="8" t="s">
-        <v>492</v>
+        <v>489</v>
       </c>
       <c r="AZ250" s="8"/>
       <c r="BD250" t="str">
@@ -30026,7 +30046,7 @@
         <v>bad_client</v>
       </c>
       <c r="AT251" t="s">
-        <v>485</v>
+        <v>482</v>
       </c>
       <c r="AU251" t="str">
         <f>IF(AND(Dataset!F251="Savings",Dataset!AT251="eligible"),"YES","NO")</f>
@@ -30034,10 +30054,10 @@
       </c>
       <c r="AW251" s="8"/>
       <c r="AX251" s="12" t="s">
-        <v>489</v>
+        <v>486</v>
       </c>
       <c r="AY251" s="8" t="s">
-        <v>493</v>
+        <v>490</v>
       </c>
       <c r="AZ251" s="8"/>
       <c r="BD251" t="str">
@@ -30136,7 +30156,7 @@
         <v>bad_client</v>
       </c>
       <c r="AT252" t="s">
-        <v>485</v>
+        <v>482</v>
       </c>
       <c r="AU252" t="str">
         <f>IF(AND(Dataset!F252="Savings",Dataset!AT252="eligible"),"YES","NO")</f>
@@ -30144,10 +30164,10 @@
       </c>
       <c r="AW252" s="8"/>
       <c r="AX252" s="12" t="s">
-        <v>490</v>
+        <v>487</v>
       </c>
       <c r="AY252" s="8" t="s">
-        <v>492</v>
+        <v>489</v>
       </c>
       <c r="AZ252" s="8"/>
       <c r="BD252" t="str">
@@ -30246,7 +30266,7 @@
         <v>bad_client</v>
       </c>
       <c r="AT253" t="s">
-        <v>485</v>
+        <v>482</v>
       </c>
       <c r="AU253" t="str">
         <f>IF(AND(Dataset!F253="Savings",Dataset!AT253="eligible"),"YES","NO")</f>
@@ -30254,10 +30274,10 @@
       </c>
       <c r="AW253" s="8"/>
       <c r="AX253" s="12" t="s">
+        <v>486</v>
+      </c>
+      <c r="AY253" s="8" t="s">
         <v>489</v>
-      </c>
-      <c r="AY253" s="8" t="s">
-        <v>492</v>
       </c>
       <c r="AZ253" s="8"/>
       <c r="BD253" t="str">
@@ -30356,7 +30376,7 @@
         <v>bad_client</v>
       </c>
       <c r="AT254" t="s">
-        <v>485</v>
+        <v>482</v>
       </c>
       <c r="AU254" t="str">
         <f>IF(AND(Dataset!F254="Savings",Dataset!AT254="eligible"),"YES","NO")</f>
@@ -30364,10 +30384,10 @@
       </c>
       <c r="AW254" s="8"/>
       <c r="AX254" s="12" t="s">
+        <v>487</v>
+      </c>
+      <c r="AY254" s="8" t="s">
         <v>490</v>
-      </c>
-      <c r="AY254" s="8" t="s">
-        <v>493</v>
       </c>
       <c r="AZ254" s="8"/>
       <c r="BD254" t="str">
@@ -30466,7 +30486,7 @@
         <v>bad_client</v>
       </c>
       <c r="AT255" t="s">
-        <v>485</v>
+        <v>482</v>
       </c>
       <c r="AU255" t="str">
         <f>IF(AND(Dataset!F255="Savings",Dataset!AT255="eligible"),"YES","NO")</f>
@@ -30474,10 +30494,10 @@
       </c>
       <c r="AW255" s="8"/>
       <c r="AX255" s="12" t="s">
-        <v>490</v>
+        <v>487</v>
       </c>
       <c r="AY255" s="8" t="s">
-        <v>492</v>
+        <v>489</v>
       </c>
       <c r="AZ255" s="8"/>
       <c r="BD255" t="str">
@@ -30576,7 +30596,7 @@
         <v>bad_client</v>
       </c>
       <c r="AT256" t="s">
-        <v>485</v>
+        <v>482</v>
       </c>
       <c r="AU256" t="str">
         <f>IF(AND(Dataset!F256="Savings",Dataset!AT256="eligible"),"YES","NO")</f>
@@ -30584,10 +30604,10 @@
       </c>
       <c r="AW256" s="8"/>
       <c r="AX256" s="12" t="s">
-        <v>489</v>
+        <v>486</v>
       </c>
       <c r="AY256" s="8" t="s">
-        <v>493</v>
+        <v>490</v>
       </c>
       <c r="AZ256" s="8"/>
       <c r="BD256" t="str">
@@ -30686,7 +30706,7 @@
         <v>bad_client</v>
       </c>
       <c r="AT257" t="s">
-        <v>485</v>
+        <v>482</v>
       </c>
       <c r="AU257" t="str">
         <f>IF(AND(Dataset!F257="Savings",Dataset!AT257="eligible"),"YES","NO")</f>
@@ -30694,10 +30714,10 @@
       </c>
       <c r="AW257" s="8"/>
       <c r="AX257" s="12" t="s">
-        <v>490</v>
+        <v>487</v>
       </c>
       <c r="AY257" s="8" t="s">
-        <v>492</v>
+        <v>489</v>
       </c>
       <c r="AZ257" s="8"/>
       <c r="BD257" t="str">
@@ -30796,7 +30816,7 @@
         <v>good_client</v>
       </c>
       <c r="AT258" t="s">
-        <v>485</v>
+        <v>482</v>
       </c>
       <c r="AU258" t="str">
         <f>IF(AND(Dataset!F258="Savings",Dataset!AT258="eligible"),"YES","NO")</f>
@@ -30804,10 +30824,10 @@
       </c>
       <c r="AW258" s="8"/>
       <c r="AX258" s="12" t="s">
+        <v>487</v>
+      </c>
+      <c r="AY258" s="8" t="s">
         <v>490</v>
-      </c>
-      <c r="AY258" s="8" t="s">
-        <v>493</v>
       </c>
       <c r="AZ258" s="8"/>
       <c r="BD258" t="str">
@@ -30906,7 +30926,7 @@
         <v>bad_client</v>
       </c>
       <c r="AT259" t="s">
-        <v>485</v>
+        <v>482</v>
       </c>
       <c r="AU259" t="str">
         <f>IF(AND(Dataset!F259="Savings",Dataset!AT259="eligible"),"YES","NO")</f>
@@ -30914,10 +30934,10 @@
       </c>
       <c r="AW259" s="8"/>
       <c r="AX259" s="12" t="s">
+        <v>486</v>
+      </c>
+      <c r="AY259" s="8" t="s">
         <v>489</v>
-      </c>
-      <c r="AY259" s="8" t="s">
-        <v>492</v>
       </c>
       <c r="AZ259" s="8"/>
       <c r="BD259" t="str">
@@ -31016,7 +31036,7 @@
         <v>bad_client</v>
       </c>
       <c r="AT260" t="s">
-        <v>485</v>
+        <v>482</v>
       </c>
       <c r="AU260" t="str">
         <f>IF(AND(Dataset!F260="Savings",Dataset!AT260="eligible"),"YES","NO")</f>
@@ -31024,10 +31044,10 @@
       </c>
       <c r="AW260" s="8"/>
       <c r="AX260" s="12" t="s">
+        <v>487</v>
+      </c>
+      <c r="AY260" s="8" t="s">
         <v>490</v>
-      </c>
-      <c r="AY260" s="8" t="s">
-        <v>493</v>
       </c>
       <c r="AZ260" s="8"/>
       <c r="BD260" t="str">
@@ -31126,7 +31146,7 @@
         <v>bad_client</v>
       </c>
       <c r="AT261" t="s">
-        <v>485</v>
+        <v>482</v>
       </c>
       <c r="AU261" t="str">
         <f>IF(AND(Dataset!F261="Savings",Dataset!AT261="eligible"),"YES","NO")</f>
@@ -31134,10 +31154,10 @@
       </c>
       <c r="AW261" s="8"/>
       <c r="AX261" s="12" t="s">
+        <v>486</v>
+      </c>
+      <c r="AY261" s="8" t="s">
         <v>489</v>
-      </c>
-      <c r="AY261" s="8" t="s">
-        <v>492</v>
       </c>
       <c r="AZ261" s="8"/>
       <c r="BD261" t="str">
@@ -31236,7 +31256,7 @@
         <v>bad_client</v>
       </c>
       <c r="AT262" t="s">
-        <v>485</v>
+        <v>482</v>
       </c>
       <c r="AU262" t="str">
         <f>IF(AND(Dataset!F262="Savings",Dataset!AT262="eligible"),"YES","NO")</f>
@@ -31244,10 +31264,10 @@
       </c>
       <c r="AW262" s="8"/>
       <c r="AX262" s="12" t="s">
+        <v>487</v>
+      </c>
+      <c r="AY262" s="8" t="s">
         <v>490</v>
-      </c>
-      <c r="AY262" s="8" t="s">
-        <v>493</v>
       </c>
       <c r="AZ262" s="8"/>
       <c r="BD262" t="str">
@@ -31346,7 +31366,7 @@
         <v>bad_client</v>
       </c>
       <c r="AT263" t="s">
-        <v>485</v>
+        <v>482</v>
       </c>
       <c r="AU263" t="str">
         <f>IF(AND(Dataset!F263="Savings",Dataset!AT263="eligible"),"YES","NO")</f>
@@ -31354,10 +31374,10 @@
       </c>
       <c r="AW263" s="8"/>
       <c r="AX263" s="12" t="s">
-        <v>490</v>
+        <v>487</v>
       </c>
       <c r="AY263" s="8" t="s">
-        <v>492</v>
+        <v>489</v>
       </c>
       <c r="AZ263" s="8"/>
       <c r="BD263" t="str">
@@ -31456,7 +31476,7 @@
         <v>bad_client</v>
       </c>
       <c r="AT264" t="s">
-        <v>485</v>
+        <v>482</v>
       </c>
       <c r="AU264" t="str">
         <f>IF(AND(Dataset!F264="Savings",Dataset!AT264="eligible"),"YES","NO")</f>
@@ -31464,10 +31484,10 @@
       </c>
       <c r="AW264" s="8"/>
       <c r="AX264" s="12" t="s">
+        <v>487</v>
+      </c>
+      <c r="AY264" s="8" t="s">
         <v>490</v>
-      </c>
-      <c r="AY264" s="8" t="s">
-        <v>493</v>
       </c>
       <c r="AZ264" s="8"/>
       <c r="BD264" t="str">
@@ -31566,7 +31586,7 @@
         <v>bad_client</v>
       </c>
       <c r="AT265" t="s">
-        <v>485</v>
+        <v>482</v>
       </c>
       <c r="AU265" t="str">
         <f>IF(AND(Dataset!F265="Savings",Dataset!AT265="eligible"),"YES","NO")</f>
@@ -31574,10 +31594,10 @@
       </c>
       <c r="AW265" s="8"/>
       <c r="AX265" s="12" t="s">
-        <v>490</v>
+        <v>487</v>
       </c>
       <c r="AY265" s="8" t="s">
-        <v>492</v>
+        <v>489</v>
       </c>
       <c r="AZ265" s="8"/>
       <c r="BD265" t="str">
@@ -31676,7 +31696,7 @@
         <v>bad_client</v>
       </c>
       <c r="AT266" t="s">
-        <v>485</v>
+        <v>482</v>
       </c>
       <c r="AU266" t="str">
         <f>IF(AND(Dataset!F266="Savings",Dataset!AT266="eligible"),"YES","NO")</f>
@@ -31684,10 +31704,10 @@
       </c>
       <c r="AW266" s="8"/>
       <c r="AX266" s="12" t="s">
-        <v>489</v>
+        <v>486</v>
       </c>
       <c r="AY266" s="8" t="s">
-        <v>493</v>
+        <v>490</v>
       </c>
       <c r="AZ266" s="8"/>
       <c r="BD266" t="str">
@@ -31786,7 +31806,7 @@
         <v>bad_client</v>
       </c>
       <c r="AT267" t="s">
-        <v>485</v>
+        <v>482</v>
       </c>
       <c r="AU267" t="str">
         <f>IF(AND(Dataset!F267="Savings",Dataset!AT267="eligible"),"YES","NO")</f>
@@ -31794,10 +31814,10 @@
       </c>
       <c r="AW267" s="8"/>
       <c r="AX267" s="12" t="s">
+        <v>486</v>
+      </c>
+      <c r="AY267" s="8" t="s">
         <v>489</v>
-      </c>
-      <c r="AY267" s="8" t="s">
-        <v>492</v>
       </c>
       <c r="AZ267" s="8"/>
       <c r="BD267" t="str">
@@ -31896,7 +31916,7 @@
         <v>bad_client</v>
       </c>
       <c r="AT268" t="s">
-        <v>485</v>
+        <v>482</v>
       </c>
       <c r="AU268" t="str">
         <f>IF(AND(Dataset!F268="Savings",Dataset!AT268="eligible"),"YES","NO")</f>
@@ -31904,10 +31924,10 @@
       </c>
       <c r="AW268" s="8"/>
       <c r="AX268" s="12" t="s">
+        <v>487</v>
+      </c>
+      <c r="AY268" s="8" t="s">
         <v>490</v>
-      </c>
-      <c r="AY268" s="8" t="s">
-        <v>493</v>
       </c>
       <c r="AZ268" s="8"/>
       <c r="BD268" t="str">
@@ -32006,7 +32026,7 @@
         <v>bad_client</v>
       </c>
       <c r="AT269" t="s">
-        <v>485</v>
+        <v>482</v>
       </c>
       <c r="AU269" t="str">
         <f>IF(AND(Dataset!F269="Savings",Dataset!AT269="eligible"),"YES","NO")</f>
@@ -32014,10 +32034,10 @@
       </c>
       <c r="AW269" s="8"/>
       <c r="AX269" s="12" t="s">
-        <v>490</v>
+        <v>487</v>
       </c>
       <c r="AY269" s="8" t="s">
-        <v>492</v>
+        <v>489</v>
       </c>
       <c r="AZ269" s="8"/>
       <c r="BD269" t="str">
@@ -32116,7 +32136,7 @@
         <v>bad_client</v>
       </c>
       <c r="AT270" t="s">
-        <v>485</v>
+        <v>482</v>
       </c>
       <c r="AU270" t="str">
         <f>IF(AND(Dataset!F270="Savings",Dataset!AT270="eligible"),"YES","NO")</f>
@@ -32124,10 +32144,10 @@
       </c>
       <c r="AW270" s="8"/>
       <c r="AX270" s="12" t="s">
-        <v>489</v>
+        <v>486</v>
       </c>
       <c r="AY270" s="8" t="s">
-        <v>493</v>
+        <v>490</v>
       </c>
       <c r="AZ270" s="8"/>
       <c r="BD270" t="str">
@@ -32226,7 +32246,7 @@
         <v>bad_client</v>
       </c>
       <c r="AT271" t="s">
-        <v>485</v>
+        <v>482</v>
       </c>
       <c r="AU271" t="str">
         <f>IF(AND(Dataset!F271="Savings",Dataset!AT271="eligible"),"YES","NO")</f>
@@ -32234,10 +32254,10 @@
       </c>
       <c r="AW271" s="8"/>
       <c r="AX271" s="12" t="s">
+        <v>486</v>
+      </c>
+      <c r="AY271" s="8" t="s">
         <v>489</v>
-      </c>
-      <c r="AY271" s="8" t="s">
-        <v>492</v>
       </c>
       <c r="AZ271" s="8"/>
       <c r="BD271" t="str">
@@ -32336,7 +32356,7 @@
         <v>bad_client</v>
       </c>
       <c r="AT272" t="s">
-        <v>485</v>
+        <v>482</v>
       </c>
       <c r="AU272" t="str">
         <f>IF(AND(Dataset!F272="Savings",Dataset!AT272="eligible"),"YES","NO")</f>
@@ -32344,10 +32364,10 @@
       </c>
       <c r="AW272" s="8"/>
       <c r="AX272" s="12" t="s">
+        <v>487</v>
+      </c>
+      <c r="AY272" s="8" t="s">
         <v>490</v>
-      </c>
-      <c r="AY272" s="8" t="s">
-        <v>493</v>
       </c>
       <c r="AZ272" s="8"/>
       <c r="BD272" t="str">
@@ -32446,7 +32466,7 @@
         <v>bad_client</v>
       </c>
       <c r="AT273" t="s">
-        <v>485</v>
+        <v>482</v>
       </c>
       <c r="AU273" t="str">
         <f>IF(AND(Dataset!F273="Savings",Dataset!AT273="eligible"),"YES","NO")</f>
@@ -32454,10 +32474,10 @@
       </c>
       <c r="AW273" s="8"/>
       <c r="AX273" s="12" t="s">
-        <v>490</v>
+        <v>487</v>
       </c>
       <c r="AY273" s="8" t="s">
-        <v>492</v>
+        <v>489</v>
       </c>
       <c r="AZ273" s="8"/>
       <c r="BD273" t="str">
@@ -32556,7 +32576,7 @@
         <v>bad_client</v>
       </c>
       <c r="AT274" t="s">
-        <v>485</v>
+        <v>482</v>
       </c>
       <c r="AU274" t="str">
         <f>IF(AND(Dataset!F274="Savings",Dataset!AT274="eligible"),"YES","NO")</f>
@@ -32564,10 +32584,10 @@
       </c>
       <c r="AW274" s="8"/>
       <c r="AX274" s="12" t="s">
+        <v>487</v>
+      </c>
+      <c r="AY274" s="8" t="s">
         <v>490</v>
-      </c>
-      <c r="AY274" s="8" t="s">
-        <v>493</v>
       </c>
       <c r="AZ274" s="8"/>
       <c r="BD274" t="str">
@@ -32666,7 +32686,7 @@
         <v>good_client</v>
       </c>
       <c r="AT275" t="s">
-        <v>485</v>
+        <v>482</v>
       </c>
       <c r="AU275" t="str">
         <f>IF(AND(Dataset!F275="Savings",Dataset!AT275="eligible"),"YES","NO")</f>
@@ -32674,10 +32694,10 @@
       </c>
       <c r="AW275" s="8"/>
       <c r="AX275" s="12" t="s">
-        <v>490</v>
+        <v>487</v>
       </c>
       <c r="AY275" s="8" t="s">
-        <v>492</v>
+        <v>489</v>
       </c>
       <c r="AZ275" s="8"/>
       <c r="BD275" t="str">
@@ -32776,7 +32796,7 @@
         <v>bad_client</v>
       </c>
       <c r="AT276" t="s">
-        <v>485</v>
+        <v>482</v>
       </c>
       <c r="AU276" t="str">
         <f>IF(AND(Dataset!F276="Savings",Dataset!AT276="eligible"),"YES","NO")</f>
@@ -32784,10 +32804,10 @@
       </c>
       <c r="AW276" s="8"/>
       <c r="AX276" s="12" t="s">
+        <v>487</v>
+      </c>
+      <c r="AY276" s="8" t="s">
         <v>490</v>
-      </c>
-      <c r="AY276" s="8" t="s">
-        <v>493</v>
       </c>
       <c r="AZ276" s="8"/>
       <c r="BD276" t="str">
@@ -32886,7 +32906,7 @@
         <v>bad_client</v>
       </c>
       <c r="AT277" t="s">
-        <v>485</v>
+        <v>482</v>
       </c>
       <c r="AU277" t="str">
         <f>IF(AND(Dataset!F277="Savings",Dataset!AT277="eligible"),"YES","NO")</f>
@@ -32894,10 +32914,10 @@
       </c>
       <c r="AW277" s="8"/>
       <c r="AX277" s="12" t="s">
-        <v>490</v>
+        <v>487</v>
       </c>
       <c r="AY277" s="8" t="s">
-        <v>492</v>
+        <v>489</v>
       </c>
       <c r="AZ277" s="8"/>
       <c r="BD277" t="str">
@@ -32996,7 +33016,7 @@
         <v>bad_client</v>
       </c>
       <c r="AT278" t="s">
-        <v>485</v>
+        <v>482</v>
       </c>
       <c r="AU278" t="str">
         <f>IF(AND(Dataset!F278="Savings",Dataset!AT278="eligible"),"YES","NO")</f>
@@ -33004,10 +33024,10 @@
       </c>
       <c r="AW278" s="8"/>
       <c r="AX278" s="12" t="s">
-        <v>489</v>
+        <v>486</v>
       </c>
       <c r="AY278" s="8" t="s">
-        <v>493</v>
+        <v>490</v>
       </c>
       <c r="AZ278" s="8"/>
       <c r="BD278" t="str">
@@ -33106,7 +33126,7 @@
         <v>bad_client</v>
       </c>
       <c r="AT279" t="s">
-        <v>485</v>
+        <v>482</v>
       </c>
       <c r="AU279" t="str">
         <f>IF(AND(Dataset!F279="Savings",Dataset!AT279="eligible"),"YES","NO")</f>
@@ -33114,10 +33134,10 @@
       </c>
       <c r="AW279" s="8"/>
       <c r="AX279" s="12" t="s">
+        <v>486</v>
+      </c>
+      <c r="AY279" s="8" t="s">
         <v>489</v>
-      </c>
-      <c r="AY279" s="8" t="s">
-        <v>492</v>
       </c>
       <c r="AZ279" s="8"/>
       <c r="BD279" t="str">
@@ -33216,7 +33236,7 @@
         <v>bad_client</v>
       </c>
       <c r="AT280" t="s">
-        <v>485</v>
+        <v>482</v>
       </c>
       <c r="AU280" t="str">
         <f>IF(AND(Dataset!F280="Savings",Dataset!AT280="eligible"),"YES","NO")</f>
@@ -33224,10 +33244,10 @@
       </c>
       <c r="AW280" s="8"/>
       <c r="AX280" s="12" t="s">
-        <v>489</v>
+        <v>486</v>
       </c>
       <c r="AY280" s="8" t="s">
-        <v>493</v>
+        <v>490</v>
       </c>
       <c r="AZ280" s="8"/>
       <c r="BD280" t="str">
@@ -33326,7 +33346,7 @@
         <v>bad_client</v>
       </c>
       <c r="AT281" t="s">
-        <v>485</v>
+        <v>482</v>
       </c>
       <c r="AU281" t="str">
         <f>IF(AND(Dataset!F281="Savings",Dataset!AT281="eligible"),"YES","NO")</f>
@@ -33334,10 +33354,10 @@
       </c>
       <c r="AW281" s="8"/>
       <c r="AX281" s="12" t="s">
+        <v>486</v>
+      </c>
+      <c r="AY281" s="8" t="s">
         <v>489</v>
-      </c>
-      <c r="AY281" s="8" t="s">
-        <v>492</v>
       </c>
       <c r="AZ281" s="8"/>
       <c r="BD281" t="str">
@@ -33436,7 +33456,7 @@
         <v>bad_client</v>
       </c>
       <c r="AT282" t="s">
-        <v>485</v>
+        <v>482</v>
       </c>
       <c r="AU282" t="str">
         <f>IF(AND(Dataset!F282="Savings",Dataset!AT282="eligible"),"YES","NO")</f>
@@ -33444,10 +33464,10 @@
       </c>
       <c r="AW282" s="8"/>
       <c r="AX282" s="12" t="s">
-        <v>489</v>
+        <v>486</v>
       </c>
       <c r="AY282" s="8" t="s">
-        <v>493</v>
+        <v>490</v>
       </c>
       <c r="AZ282" s="8"/>
       <c r="BD282" t="str">
@@ -33546,7 +33566,7 @@
         <v>bad_client</v>
       </c>
       <c r="AT283" t="s">
-        <v>485</v>
+        <v>482</v>
       </c>
       <c r="AU283" t="str">
         <f>IF(AND(Dataset!F283="Savings",Dataset!AT283="eligible"),"YES","NO")</f>
@@ -33554,10 +33574,10 @@
       </c>
       <c r="AW283" s="8"/>
       <c r="AX283" s="12" t="s">
+        <v>486</v>
+      </c>
+      <c r="AY283" s="8" t="s">
         <v>489</v>
-      </c>
-      <c r="AY283" s="8" t="s">
-        <v>492</v>
       </c>
       <c r="AZ283" s="8"/>
       <c r="BD283" t="str">
@@ -33656,7 +33676,7 @@
         <v>bad_client</v>
       </c>
       <c r="AT284" t="s">
-        <v>485</v>
+        <v>482</v>
       </c>
       <c r="AU284" t="str">
         <f>IF(AND(Dataset!F284="Savings",Dataset!AT284="eligible"),"YES","NO")</f>
@@ -33664,10 +33684,10 @@
       </c>
       <c r="AW284" s="8"/>
       <c r="AX284" s="12" t="s">
+        <v>487</v>
+      </c>
+      <c r="AY284" s="8" t="s">
         <v>490</v>
-      </c>
-      <c r="AY284" s="8" t="s">
-        <v>493</v>
       </c>
       <c r="AZ284" s="8"/>
       <c r="BD284" t="str">
@@ -33766,7 +33786,7 @@
         <v>bad_client</v>
       </c>
       <c r="AT285" t="s">
-        <v>485</v>
+        <v>482</v>
       </c>
       <c r="AU285" t="str">
         <f>IF(AND(Dataset!F285="Savings",Dataset!AT285="eligible"),"YES","NO")</f>
@@ -33774,10 +33794,10 @@
       </c>
       <c r="AW285" s="8"/>
       <c r="AX285" s="12" t="s">
-        <v>490</v>
+        <v>487</v>
       </c>
       <c r="AY285" s="8" t="s">
-        <v>492</v>
+        <v>489</v>
       </c>
       <c r="AZ285" s="8"/>
       <c r="BD285" t="str">
@@ -33876,7 +33896,7 @@
         <v>bad_client</v>
       </c>
       <c r="AT286" t="s">
-        <v>485</v>
+        <v>482</v>
       </c>
       <c r="AU286" t="str">
         <f>IF(AND(Dataset!F286="Savings",Dataset!AT286="eligible"),"YES","NO")</f>
@@ -33884,10 +33904,10 @@
       </c>
       <c r="AW286" s="8"/>
       <c r="AX286" s="12" t="s">
+        <v>487</v>
+      </c>
+      <c r="AY286" s="8" t="s">
         <v>490</v>
-      </c>
-      <c r="AY286" s="8" t="s">
-        <v>493</v>
       </c>
       <c r="AZ286" s="8"/>
       <c r="BD286" t="str">
@@ -33986,7 +34006,7 @@
         <v>bad_client</v>
       </c>
       <c r="AT287" t="s">
-        <v>485</v>
+        <v>482</v>
       </c>
       <c r="AU287" t="str">
         <f>IF(AND(Dataset!F287="Savings",Dataset!AT287="eligible"),"YES","NO")</f>
@@ -33994,10 +34014,10 @@
       </c>
       <c r="AW287" s="8"/>
       <c r="AX287" s="12" t="s">
-        <v>490</v>
+        <v>487</v>
       </c>
       <c r="AY287" s="8" t="s">
-        <v>492</v>
+        <v>489</v>
       </c>
       <c r="AZ287" s="8"/>
       <c r="BD287" t="str">
@@ -34096,7 +34116,7 @@
         <v>bad_client</v>
       </c>
       <c r="AT288" t="s">
-        <v>485</v>
+        <v>482</v>
       </c>
       <c r="AU288" t="str">
         <f>IF(AND(Dataset!F288="Savings",Dataset!AT288="eligible"),"YES","NO")</f>
@@ -34104,10 +34124,10 @@
       </c>
       <c r="AW288" s="8"/>
       <c r="AX288" s="12" t="s">
+        <v>487</v>
+      </c>
+      <c r="AY288" s="8" t="s">
         <v>490</v>
-      </c>
-      <c r="AY288" s="8" t="s">
-        <v>493</v>
       </c>
       <c r="AZ288" s="8"/>
       <c r="BD288" t="str">
@@ -34206,7 +34226,7 @@
         <v>bad_client</v>
       </c>
       <c r="AT289" t="s">
-        <v>485</v>
+        <v>482</v>
       </c>
       <c r="AU289" t="str">
         <f>IF(AND(Dataset!F289="Savings",Dataset!AT289="eligible"),"YES","NO")</f>
@@ -34214,10 +34234,10 @@
       </c>
       <c r="AW289" s="8"/>
       <c r="AX289" s="12" t="s">
-        <v>490</v>
+        <v>487</v>
       </c>
       <c r="AY289" s="8" t="s">
-        <v>492</v>
+        <v>489</v>
       </c>
       <c r="AZ289" s="8"/>
       <c r="BD289" t="str">
@@ -34316,7 +34336,7 @@
         <v>bad_client</v>
       </c>
       <c r="AT290" t="s">
-        <v>485</v>
+        <v>482</v>
       </c>
       <c r="AU290" t="str">
         <f>IF(AND(Dataset!F290="Savings",Dataset!AT290="eligible"),"YES","NO")</f>
@@ -34324,10 +34344,10 @@
       </c>
       <c r="AW290" s="8"/>
       <c r="AX290" s="12" t="s">
+        <v>487</v>
+      </c>
+      <c r="AY290" s="8" t="s">
         <v>490</v>
-      </c>
-      <c r="AY290" s="8" t="s">
-        <v>493</v>
       </c>
       <c r="AZ290" s="8"/>
       <c r="BD290" t="str">
@@ -34426,7 +34446,7 @@
         <v>bad_client</v>
       </c>
       <c r="AT291" t="s">
-        <v>485</v>
+        <v>482</v>
       </c>
       <c r="AU291" t="str">
         <f>IF(AND(Dataset!F291="Savings",Dataset!AT291="eligible"),"YES","NO")</f>
@@ -34434,10 +34454,10 @@
       </c>
       <c r="AW291" s="8"/>
       <c r="AX291" s="12" t="s">
-        <v>490</v>
+        <v>487</v>
       </c>
       <c r="AY291" s="8" t="s">
-        <v>492</v>
+        <v>489</v>
       </c>
       <c r="AZ291" s="8"/>
       <c r="BD291" t="str">
@@ -34536,7 +34556,7 @@
         <v>bad_client</v>
       </c>
       <c r="AT292" t="s">
-        <v>485</v>
+        <v>482</v>
       </c>
       <c r="AU292" t="str">
         <f>IF(AND(Dataset!F292="Savings",Dataset!AT292="eligible"),"YES","NO")</f>
@@ -34544,10 +34564,10 @@
       </c>
       <c r="AW292" s="8"/>
       <c r="AX292" s="12" t="s">
+        <v>487</v>
+      </c>
+      <c r="AY292" s="8" t="s">
         <v>490</v>
-      </c>
-      <c r="AY292" s="8" t="s">
-        <v>493</v>
       </c>
       <c r="AZ292" s="8"/>
       <c r="BD292" t="str">
@@ -34646,7 +34666,7 @@
         <v>bad_client</v>
       </c>
       <c r="AT293" t="s">
-        <v>485</v>
+        <v>482</v>
       </c>
       <c r="AU293" t="str">
         <f>IF(AND(Dataset!F293="Savings",Dataset!AT293="eligible"),"YES","NO")</f>
@@ -34654,10 +34674,10 @@
       </c>
       <c r="AW293" s="8"/>
       <c r="AX293" s="12" t="s">
-        <v>490</v>
+        <v>487</v>
       </c>
       <c r="AY293" s="8" t="s">
-        <v>492</v>
+        <v>489</v>
       </c>
       <c r="AZ293" s="8"/>
       <c r="BD293" t="str">
@@ -34756,7 +34776,7 @@
         <v>bad_client</v>
       </c>
       <c r="AT294" t="s">
-        <v>485</v>
+        <v>482</v>
       </c>
       <c r="AU294" t="str">
         <f>IF(AND(Dataset!F294="Savings",Dataset!AT294="eligible"),"YES","NO")</f>
@@ -34764,10 +34784,10 @@
       </c>
       <c r="AW294" s="8"/>
       <c r="AX294" s="12" t="s">
+        <v>487</v>
+      </c>
+      <c r="AY294" s="8" t="s">
         <v>490</v>
-      </c>
-      <c r="AY294" s="8" t="s">
-        <v>493</v>
       </c>
       <c r="AZ294" s="8"/>
       <c r="BD294" t="str">
@@ -34866,7 +34886,7 @@
         <v>bad_client</v>
       </c>
       <c r="AT295" t="s">
-        <v>485</v>
+        <v>482</v>
       </c>
       <c r="AU295" t="str">
         <f>IF(AND(Dataset!F295="Savings",Dataset!AT295="eligible"),"YES","NO")</f>
@@ -34874,10 +34894,10 @@
       </c>
       <c r="AW295" s="8"/>
       <c r="AX295" s="12" t="s">
+        <v>486</v>
+      </c>
+      <c r="AY295" s="8" t="s">
         <v>489</v>
-      </c>
-      <c r="AY295" s="8" t="s">
-        <v>492</v>
       </c>
       <c r="AZ295" s="8"/>
       <c r="BD295" t="str">
@@ -34976,7 +34996,7 @@
         <v>bad_client</v>
       </c>
       <c r="AT296" t="s">
-        <v>485</v>
+        <v>482</v>
       </c>
       <c r="AU296" t="str">
         <f>IF(AND(Dataset!F296="Savings",Dataset!AT296="eligible"),"YES","NO")</f>
@@ -34984,10 +35004,10 @@
       </c>
       <c r="AW296" s="8"/>
       <c r="AX296" s="12" t="s">
-        <v>489</v>
+        <v>486</v>
       </c>
       <c r="AY296" s="8" t="s">
-        <v>493</v>
+        <v>490</v>
       </c>
       <c r="AZ296" s="8"/>
       <c r="BD296" t="str">
@@ -35086,7 +35106,7 @@
         <v>bad_client</v>
       </c>
       <c r="AT297" t="s">
-        <v>485</v>
+        <v>482</v>
       </c>
       <c r="AU297" t="str">
         <f>IF(AND(Dataset!F297="Savings",Dataset!AT297="eligible"),"YES","NO")</f>
@@ -35094,10 +35114,10 @@
       </c>
       <c r="AW297" s="8"/>
       <c r="AX297" s="12" t="s">
+        <v>486</v>
+      </c>
+      <c r="AY297" s="8" t="s">
         <v>489</v>
-      </c>
-      <c r="AY297" s="8" t="s">
-        <v>492</v>
       </c>
       <c r="AZ297" s="8"/>
       <c r="BD297" t="str">
@@ -35196,7 +35216,7 @@
         <v>bad_client</v>
       </c>
       <c r="AT298" t="s">
-        <v>485</v>
+        <v>482</v>
       </c>
       <c r="AU298" t="str">
         <f>IF(AND(Dataset!F298="Savings",Dataset!AT298="eligible"),"YES","NO")</f>
@@ -35204,10 +35224,10 @@
       </c>
       <c r="AW298" s="8"/>
       <c r="AX298" s="12" t="s">
+        <v>487</v>
+      </c>
+      <c r="AY298" s="8" t="s">
         <v>490</v>
-      </c>
-      <c r="AY298" s="8" t="s">
-        <v>493</v>
       </c>
       <c r="AZ298" s="8"/>
       <c r="BD298" t="str">
@@ -35306,7 +35326,7 @@
         <v>bad_client</v>
       </c>
       <c r="AT299" t="s">
-        <v>485</v>
+        <v>482</v>
       </c>
       <c r="AU299" t="str">
         <f>IF(AND(Dataset!F299="Savings",Dataset!AT299="eligible"),"YES","NO")</f>
@@ -35314,10 +35334,10 @@
       </c>
       <c r="AW299" s="8"/>
       <c r="AX299" s="12" t="s">
-        <v>490</v>
+        <v>487</v>
       </c>
       <c r="AY299" s="8" t="s">
-        <v>492</v>
+        <v>489</v>
       </c>
       <c r="AZ299" s="8"/>
       <c r="BD299" t="str">
@@ -35416,7 +35436,7 @@
         <v>bad_client</v>
       </c>
       <c r="AT300" t="s">
-        <v>485</v>
+        <v>482</v>
       </c>
       <c r="AU300" t="str">
         <f>IF(AND(Dataset!F300="Savings",Dataset!AT300="eligible"),"YES","NO")</f>
@@ -35424,10 +35444,10 @@
       </c>
       <c r="AW300" s="8"/>
       <c r="AX300" s="12" t="s">
+        <v>487</v>
+      </c>
+      <c r="AY300" s="8" t="s">
         <v>490</v>
-      </c>
-      <c r="AY300" s="8" t="s">
-        <v>493</v>
       </c>
       <c r="AZ300" s="8"/>
       <c r="BD300" t="str">
@@ -35526,7 +35546,7 @@
         <v>bad_client</v>
       </c>
       <c r="AT301" t="s">
-        <v>485</v>
+        <v>482</v>
       </c>
       <c r="AU301" t="str">
         <f>IF(AND(Dataset!F301="Savings",Dataset!AT301="eligible"),"YES","NO")</f>
@@ -35534,10 +35554,10 @@
       </c>
       <c r="AW301" s="8"/>
       <c r="AX301" s="12" t="s">
-        <v>490</v>
+        <v>487</v>
       </c>
       <c r="AY301" s="8" t="s">
-        <v>492</v>
+        <v>489</v>
       </c>
       <c r="AZ301" s="8"/>
       <c r="BD301" t="str">
@@ -35636,7 +35656,7 @@
         <v>bad_client</v>
       </c>
       <c r="AT302" t="s">
-        <v>485</v>
+        <v>482</v>
       </c>
       <c r="AU302" t="str">
         <f>IF(AND(Dataset!F302="Savings",Dataset!AT302="eligible"),"YES","NO")</f>
@@ -35644,10 +35664,10 @@
       </c>
       <c r="AW302" s="8"/>
       <c r="AX302" s="12" t="s">
+        <v>487</v>
+      </c>
+      <c r="AY302" s="8" t="s">
         <v>490</v>
-      </c>
-      <c r="AY302" s="8" t="s">
-        <v>493</v>
       </c>
       <c r="AZ302" s="8"/>
       <c r="BD302" t="str">
@@ -35746,7 +35766,7 @@
         <v>bad_client</v>
       </c>
       <c r="AT303" t="s">
-        <v>485</v>
+        <v>482</v>
       </c>
       <c r="AU303" t="str">
         <f>IF(AND(Dataset!F303="Savings",Dataset!AT303="eligible"),"YES","NO")</f>
@@ -35754,10 +35774,10 @@
       </c>
       <c r="AW303" s="8"/>
       <c r="AX303" s="12" t="s">
-        <v>490</v>
+        <v>487</v>
       </c>
       <c r="AY303" s="8" t="s">
-        <v>492</v>
+        <v>489</v>
       </c>
       <c r="AZ303" s="8"/>
       <c r="BD303" t="str">
@@ -35855,7 +35875,7 @@
         <v>good_client</v>
       </c>
       <c r="AT304" t="s">
-        <v>485</v>
+        <v>482</v>
       </c>
       <c r="AU304" t="str">
         <f>IF(AND(Dataset!F304="Savings",Dataset!AT304="eligible"),"YES","NO")</f>
@@ -35863,10 +35883,10 @@
       </c>
       <c r="AW304" s="8"/>
       <c r="AX304" s="12" t="s">
+        <v>487</v>
+      </c>
+      <c r="AY304" s="8" t="s">
         <v>490</v>
-      </c>
-      <c r="AY304" s="8" t="s">
-        <v>493</v>
       </c>
       <c r="AZ304" s="8"/>
       <c r="BD304" t="str">
@@ -35965,7 +35985,7 @@
         <v>bad_client</v>
       </c>
       <c r="AT305" t="s">
-        <v>485</v>
+        <v>482</v>
       </c>
       <c r="AU305" t="str">
         <f>IF(AND(Dataset!F305="Savings",Dataset!AT305="eligible"),"YES","NO")</f>
@@ -35973,10 +35993,10 @@
       </c>
       <c r="AW305" s="8"/>
       <c r="AX305" s="12" t="s">
-        <v>490</v>
+        <v>487</v>
       </c>
       <c r="AY305" s="8" t="s">
-        <v>492</v>
+        <v>489</v>
       </c>
       <c r="AZ305" s="8"/>
       <c r="BD305" t="str">
@@ -36075,7 +36095,7 @@
         <v>bad_client</v>
       </c>
       <c r="AT306" t="s">
-        <v>485</v>
+        <v>482</v>
       </c>
       <c r="AU306" t="str">
         <f>IF(AND(Dataset!F306="Savings",Dataset!AT306="eligible"),"YES","NO")</f>
@@ -36083,10 +36103,10 @@
       </c>
       <c r="AW306" s="8"/>
       <c r="AX306" s="12" t="s">
-        <v>489</v>
+        <v>486</v>
       </c>
       <c r="AY306" s="8" t="s">
-        <v>493</v>
+        <v>490</v>
       </c>
       <c r="AZ306" s="8"/>
       <c r="BD306" t="str">
@@ -36185,7 +36205,7 @@
         <v>bad_client</v>
       </c>
       <c r="AT307" t="s">
-        <v>485</v>
+        <v>482</v>
       </c>
       <c r="AU307" t="str">
         <f>IF(AND(Dataset!F307="Savings",Dataset!AT307="eligible"),"YES","NO")</f>
@@ -36193,10 +36213,10 @@
       </c>
       <c r="AW307" s="8"/>
       <c r="AX307" s="12" t="s">
-        <v>490</v>
+        <v>487</v>
       </c>
       <c r="AY307" s="8" t="s">
-        <v>492</v>
+        <v>489</v>
       </c>
       <c r="AZ307" s="8"/>
       <c r="BD307" t="str">
@@ -36295,7 +36315,7 @@
         <v>bad_client</v>
       </c>
       <c r="AT308" t="s">
-        <v>485</v>
+        <v>482</v>
       </c>
       <c r="AU308" t="str">
         <f>IF(AND(Dataset!F308="Savings",Dataset!AT308="eligible"),"YES","NO")</f>
@@ -36303,10 +36323,10 @@
       </c>
       <c r="AW308" s="8"/>
       <c r="AX308" s="12" t="s">
+        <v>487</v>
+      </c>
+      <c r="AY308" s="8" t="s">
         <v>490</v>
-      </c>
-      <c r="AY308" s="8" t="s">
-        <v>493</v>
       </c>
       <c r="AZ308" s="8"/>
       <c r="BD308" t="str">
@@ -36405,7 +36425,7 @@
         <v>bad_client</v>
       </c>
       <c r="AT309" t="s">
-        <v>485</v>
+        <v>482</v>
       </c>
       <c r="AU309" t="str">
         <f>IF(AND(Dataset!F309="Savings",Dataset!AT309="eligible"),"YES","NO")</f>
@@ -36413,10 +36433,10 @@
       </c>
       <c r="AW309" s="8"/>
       <c r="AX309" s="12" t="s">
-        <v>490</v>
+        <v>487</v>
       </c>
       <c r="AY309" s="8" t="s">
-        <v>492</v>
+        <v>489</v>
       </c>
       <c r="AZ309" s="8"/>
       <c r="BD309" t="str">
@@ -36515,7 +36535,7 @@
         <v>bad_client</v>
       </c>
       <c r="AT310" t="s">
-        <v>485</v>
+        <v>482</v>
       </c>
       <c r="AU310" t="str">
         <f>IF(AND(Dataset!F310="Savings",Dataset!AT310="eligible"),"YES","NO")</f>
@@ -36523,10 +36543,10 @@
       </c>
       <c r="AW310" s="8"/>
       <c r="AX310" s="12" t="s">
+        <v>487</v>
+      </c>
+      <c r="AY310" s="8" t="s">
         <v>490</v>
-      </c>
-      <c r="AY310" s="8" t="s">
-        <v>493</v>
       </c>
       <c r="AZ310" s="8"/>
       <c r="BD310" t="str">
@@ -36625,7 +36645,7 @@
         <v>bad_client</v>
       </c>
       <c r="AT311" t="s">
-        <v>485</v>
+        <v>482</v>
       </c>
       <c r="AU311" t="str">
         <f>IF(AND(Dataset!F311="Savings",Dataset!AT311="eligible"),"YES","NO")</f>
@@ -36633,10 +36653,10 @@
       </c>
       <c r="AW311" s="8"/>
       <c r="AX311" s="12" t="s">
-        <v>490</v>
+        <v>487</v>
       </c>
       <c r="AY311" s="8" t="s">
-        <v>492</v>
+        <v>489</v>
       </c>
       <c r="AZ311" s="8"/>
       <c r="BD311" t="str">
@@ -36735,7 +36755,7 @@
         <v>bad_client</v>
       </c>
       <c r="AT312" t="s">
-        <v>485</v>
+        <v>482</v>
       </c>
       <c r="AU312" t="str">
         <f>IF(AND(Dataset!F312="Savings",Dataset!AT312="eligible"),"YES","NO")</f>
@@ -36743,10 +36763,10 @@
       </c>
       <c r="AW312" s="8"/>
       <c r="AX312" s="12" t="s">
+        <v>487</v>
+      </c>
+      <c r="AY312" s="8" t="s">
         <v>490</v>
-      </c>
-      <c r="AY312" s="8" t="s">
-        <v>493</v>
       </c>
       <c r="AZ312" s="8"/>
       <c r="BD312" t="str">
@@ -36845,7 +36865,7 @@
         <v>bad_client</v>
       </c>
       <c r="AT313" t="s">
-        <v>485</v>
+        <v>482</v>
       </c>
       <c r="AU313" t="str">
         <f>IF(AND(Dataset!F313="Savings",Dataset!AT313="eligible"),"YES","NO")</f>
@@ -36853,10 +36873,10 @@
       </c>
       <c r="AW313" s="8"/>
       <c r="AX313" s="12" t="s">
+        <v>486</v>
+      </c>
+      <c r="AY313" s="8" t="s">
         <v>489</v>
-      </c>
-      <c r="AY313" s="8" t="s">
-        <v>492</v>
       </c>
       <c r="AZ313" s="8"/>
       <c r="BD313" t="str">
@@ -36955,7 +36975,7 @@
         <v>bad_client</v>
       </c>
       <c r="AT314" t="s">
-        <v>485</v>
+        <v>482</v>
       </c>
       <c r="AU314" t="str">
         <f>IF(AND(Dataset!F314="Savings",Dataset!AT314="eligible"),"YES","NO")</f>
@@ -36963,10 +36983,10 @@
       </c>
       <c r="AW314" s="8"/>
       <c r="AX314" s="12" t="s">
+        <v>487</v>
+      </c>
+      <c r="AY314" s="8" t="s">
         <v>490</v>
-      </c>
-      <c r="AY314" s="8" t="s">
-        <v>493</v>
       </c>
       <c r="AZ314" s="8"/>
       <c r="BD314" t="str">
@@ -37065,7 +37085,7 @@
         <v>bad_client</v>
       </c>
       <c r="AT315" t="s">
-        <v>485</v>
+        <v>482</v>
       </c>
       <c r="AU315" t="str">
         <f>IF(AND(Dataset!F315="Savings",Dataset!AT315="eligible"),"YES","NO")</f>
@@ -37073,10 +37093,10 @@
       </c>
       <c r="AW315" s="8"/>
       <c r="AX315" s="12" t="s">
+        <v>486</v>
+      </c>
+      <c r="AY315" s="8" t="s">
         <v>489</v>
-      </c>
-      <c r="AY315" s="8" t="s">
-        <v>492</v>
       </c>
       <c r="AZ315" s="8"/>
       <c r="BD315" t="str">
@@ -37175,7 +37195,7 @@
         <v>bad_client</v>
       </c>
       <c r="AT316" t="s">
-        <v>485</v>
+        <v>482</v>
       </c>
       <c r="AU316" t="str">
         <f>IF(AND(Dataset!F316="Savings",Dataset!AT316="eligible"),"YES","NO")</f>
@@ -37183,10 +37203,10 @@
       </c>
       <c r="AW316" s="8"/>
       <c r="AX316" s="12" t="s">
+        <v>487</v>
+      </c>
+      <c r="AY316" s="8" t="s">
         <v>490</v>
-      </c>
-      <c r="AY316" s="8" t="s">
-        <v>493</v>
       </c>
       <c r="AZ316" s="8"/>
       <c r="BD316" t="str">
@@ -37285,7 +37305,7 @@
         <v>bad_client</v>
       </c>
       <c r="AT317" t="s">
-        <v>485</v>
+        <v>482</v>
       </c>
       <c r="AU317" t="str">
         <f>IF(AND(Dataset!F317="Savings",Dataset!AT317="eligible"),"YES","NO")</f>
@@ -37293,10 +37313,10 @@
       </c>
       <c r="AW317" s="8"/>
       <c r="AX317" s="12" t="s">
-        <v>490</v>
+        <v>487</v>
       </c>
       <c r="AY317" s="8" t="s">
-        <v>492</v>
+        <v>489</v>
       </c>
       <c r="AZ317" s="8"/>
       <c r="BD317" t="str">
@@ -37395,7 +37415,7 @@
         <v>bad_client</v>
       </c>
       <c r="AT318" t="s">
-        <v>485</v>
+        <v>482</v>
       </c>
       <c r="AU318" t="str">
         <f>IF(AND(Dataset!F318="Savings",Dataset!AT318="eligible"),"YES","NO")</f>
@@ -37403,10 +37423,10 @@
       </c>
       <c r="AW318" s="8"/>
       <c r="AX318" s="12" t="s">
-        <v>489</v>
+        <v>486</v>
       </c>
       <c r="AY318" s="8" t="s">
-        <v>493</v>
+        <v>490</v>
       </c>
       <c r="AZ318" s="8"/>
       <c r="BD318" t="str">
@@ -37505,7 +37525,7 @@
         <v>bad_client</v>
       </c>
       <c r="AT319" t="s">
-        <v>485</v>
+        <v>482</v>
       </c>
       <c r="AU319" t="str">
         <f>IF(AND(Dataset!F319="Savings",Dataset!AT319="eligible"),"YES","NO")</f>
@@ -37513,10 +37533,10 @@
       </c>
       <c r="AW319" s="8"/>
       <c r="AX319" s="12" t="s">
-        <v>490</v>
+        <v>487</v>
       </c>
       <c r="AY319" s="8" t="s">
-        <v>492</v>
+        <v>489</v>
       </c>
       <c r="AZ319" s="8"/>
       <c r="BD319" t="str">
@@ -37615,7 +37635,7 @@
         <v>good_client</v>
       </c>
       <c r="AT320" t="s">
-        <v>485</v>
+        <v>482</v>
       </c>
       <c r="AU320" t="str">
         <f>IF(AND(Dataset!F320="Savings",Dataset!AT320="eligible"),"YES","NO")</f>
@@ -37623,10 +37643,10 @@
       </c>
       <c r="AW320" s="8"/>
       <c r="AX320" s="12" t="s">
+        <v>487</v>
+      </c>
+      <c r="AY320" s="8" t="s">
         <v>490</v>
-      </c>
-      <c r="AY320" s="8" t="s">
-        <v>493</v>
       </c>
       <c r="AZ320" s="8"/>
       <c r="BD320" t="str">
@@ -37725,7 +37745,7 @@
         <v>bad_client</v>
       </c>
       <c r="AT321" t="s">
-        <v>485</v>
+        <v>482</v>
       </c>
       <c r="AU321" t="str">
         <f>IF(AND(Dataset!F321="Savings",Dataset!AT321="eligible"),"YES","NO")</f>
@@ -37733,10 +37753,10 @@
       </c>
       <c r="AW321" s="8"/>
       <c r="AX321" s="12" t="s">
+        <v>486</v>
+      </c>
+      <c r="AY321" s="8" t="s">
         <v>489</v>
-      </c>
-      <c r="AY321" s="8" t="s">
-        <v>492</v>
       </c>
       <c r="AZ321" s="8"/>
       <c r="BD321" t="str">
@@ -37835,7 +37855,7 @@
         <v>bad_client</v>
       </c>
       <c r="AT322" t="s">
-        <v>485</v>
+        <v>482</v>
       </c>
       <c r="AU322" t="str">
         <f>IF(AND(Dataset!F322="Savings",Dataset!AT322="eligible"),"YES","NO")</f>
@@ -37843,10 +37863,10 @@
       </c>
       <c r="AW322" s="8"/>
       <c r="AX322" s="12" t="s">
+        <v>487</v>
+      </c>
+      <c r="AY322" s="8" t="s">
         <v>490</v>
-      </c>
-      <c r="AY322" s="8" t="s">
-        <v>493</v>
       </c>
       <c r="AZ322" s="8"/>
       <c r="BD322" t="str">
@@ -37945,7 +37965,7 @@
         <v>good_client</v>
       </c>
       <c r="AT323" t="s">
-        <v>485</v>
+        <v>482</v>
       </c>
       <c r="AU323" t="str">
         <f>IF(AND(Dataset!F323="Savings",Dataset!AT323="eligible"),"YES","NO")</f>
@@ -37953,10 +37973,10 @@
       </c>
       <c r="AW323" s="8"/>
       <c r="AX323" s="12" t="s">
+        <v>486</v>
+      </c>
+      <c r="AY323" s="8" t="s">
         <v>489</v>
-      </c>
-      <c r="AY323" s="8" t="s">
-        <v>492</v>
       </c>
       <c r="AZ323" s="8"/>
       <c r="BD323" t="str">
@@ -38055,7 +38075,7 @@
         <v>bad_client</v>
       </c>
       <c r="AT324" t="s">
-        <v>485</v>
+        <v>482</v>
       </c>
       <c r="AU324" t="str">
         <f>IF(AND(Dataset!F324="Savings",Dataset!AT324="eligible"),"YES","NO")</f>
@@ -38063,10 +38083,10 @@
       </c>
       <c r="AW324" s="8"/>
       <c r="AX324" s="12" t="s">
+        <v>487</v>
+      </c>
+      <c r="AY324" s="8" t="s">
         <v>490</v>
-      </c>
-      <c r="AY324" s="8" t="s">
-        <v>493</v>
       </c>
       <c r="AZ324" s="8"/>
       <c r="BD324" t="str">
@@ -38165,7 +38185,7 @@
         <v>good_client</v>
       </c>
       <c r="AT325" t="s">
-        <v>485</v>
+        <v>482</v>
       </c>
       <c r="AU325" t="str">
         <f>IF(AND(Dataset!F325="Savings",Dataset!AT325="eligible"),"YES","NO")</f>
@@ -38173,10 +38193,10 @@
       </c>
       <c r="AW325" s="8"/>
       <c r="AX325" s="12" t="s">
-        <v>490</v>
+        <v>487</v>
       </c>
       <c r="AY325" s="8" t="s">
-        <v>492</v>
+        <v>489</v>
       </c>
       <c r="AZ325" s="8"/>
       <c r="BD325" t="str">
@@ -38275,7 +38295,7 @@
         <v>bad_client</v>
       </c>
       <c r="AT326" t="s">
-        <v>485</v>
+        <v>482</v>
       </c>
       <c r="AU326" t="str">
         <f>IF(AND(Dataset!F326="Savings",Dataset!AT326="eligible"),"YES","NO")</f>
@@ -38283,10 +38303,10 @@
       </c>
       <c r="AW326" s="8"/>
       <c r="AX326" s="12" t="s">
+        <v>487</v>
+      </c>
+      <c r="AY326" s="8" t="s">
         <v>490</v>
-      </c>
-      <c r="AY326" s="8" t="s">
-        <v>493</v>
       </c>
       <c r="AZ326" s="8"/>
       <c r="BD326" t="str">
@@ -38385,7 +38405,7 @@
         <v>good_client</v>
       </c>
       <c r="AT327" t="s">
-        <v>485</v>
+        <v>482</v>
       </c>
       <c r="AU327" t="str">
         <f>IF(AND(Dataset!F327="Savings",Dataset!AT327="eligible"),"YES","NO")</f>
@@ -38393,10 +38413,10 @@
       </c>
       <c r="AW327" s="8"/>
       <c r="AX327" s="12" t="s">
-        <v>490</v>
+        <v>487</v>
       </c>
       <c r="AY327" s="8" t="s">
-        <v>492</v>
+        <v>489</v>
       </c>
       <c r="AZ327" s="8"/>
       <c r="BD327" t="str">
@@ -38495,7 +38515,7 @@
         <v>bad_client</v>
       </c>
       <c r="AT328" t="s">
-        <v>485</v>
+        <v>482</v>
       </c>
       <c r="AU328" t="str">
         <f>IF(AND(Dataset!F328="Savings",Dataset!AT328="eligible"),"YES","NO")</f>
@@ -38503,10 +38523,10 @@
       </c>
       <c r="AW328" s="8"/>
       <c r="AX328" s="12" t="s">
-        <v>489</v>
+        <v>486</v>
       </c>
       <c r="AY328" s="8" t="s">
-        <v>493</v>
+        <v>490</v>
       </c>
       <c r="AZ328" s="8"/>
       <c r="BD328" t="str">
@@ -38605,7 +38625,7 @@
         <v>good_client</v>
       </c>
       <c r="AT329" t="s">
-        <v>485</v>
+        <v>482</v>
       </c>
       <c r="AU329" t="str">
         <f>IF(AND(Dataset!F329="Savings",Dataset!AT329="eligible"),"YES","NO")</f>
@@ -38613,10 +38633,10 @@
       </c>
       <c r="AW329" s="8"/>
       <c r="AX329" s="12" t="s">
+        <v>486</v>
+      </c>
+      <c r="AY329" s="8" t="s">
         <v>489</v>
-      </c>
-      <c r="AY329" s="8" t="s">
-        <v>492</v>
       </c>
       <c r="AZ329" s="8"/>
       <c r="BD329" t="str">
@@ -38715,7 +38735,7 @@
         <v>bad_client</v>
       </c>
       <c r="AT330" t="s">
-        <v>485</v>
+        <v>482</v>
       </c>
       <c r="AU330" t="str">
         <f>IF(AND(Dataset!F330="Savings",Dataset!AT330="eligible"),"YES","NO")</f>
@@ -38723,10 +38743,10 @@
       </c>
       <c r="AW330" s="8"/>
       <c r="AX330" s="12" t="s">
+        <v>487</v>
+      </c>
+      <c r="AY330" s="8" t="s">
         <v>490</v>
-      </c>
-      <c r="AY330" s="8" t="s">
-        <v>493</v>
       </c>
       <c r="AZ330" s="8"/>
       <c r="BD330" t="str">
@@ -38825,7 +38845,7 @@
         <v>good_client</v>
       </c>
       <c r="AT331" t="s">
-        <v>485</v>
+        <v>482</v>
       </c>
       <c r="AU331" t="str">
         <f>IF(AND(Dataset!F331="Savings",Dataset!AT331="eligible"),"YES","NO")</f>
@@ -38833,10 +38853,10 @@
       </c>
       <c r="AW331" s="8"/>
       <c r="AX331" s="12" t="s">
-        <v>490</v>
+        <v>487</v>
       </c>
       <c r="AY331" s="8" t="s">
-        <v>492</v>
+        <v>489</v>
       </c>
       <c r="AZ331" s="8"/>
       <c r="BD331" t="str">
@@ -38935,7 +38955,7 @@
         <v>bad_client</v>
       </c>
       <c r="AT332" t="s">
-        <v>485</v>
+        <v>482</v>
       </c>
       <c r="AU332" t="str">
         <f>IF(AND(Dataset!F332="Savings",Dataset!AT332="eligible"),"YES","NO")</f>
@@ -38943,10 +38963,10 @@
       </c>
       <c r="AW332" s="8"/>
       <c r="AX332" s="12" t="s">
-        <v>489</v>
+        <v>486</v>
       </c>
       <c r="AY332" s="8" t="s">
-        <v>493</v>
+        <v>490</v>
       </c>
       <c r="AZ332" s="8"/>
       <c r="BD332" t="str">
@@ -39045,7 +39065,7 @@
         <v>good_client</v>
       </c>
       <c r="AT333" t="s">
-        <v>485</v>
+        <v>482</v>
       </c>
       <c r="AU333" t="str">
         <f>IF(AND(Dataset!F333="Savings",Dataset!AT333="eligible"),"YES","NO")</f>
@@ -39053,10 +39073,10 @@
       </c>
       <c r="AW333" s="8"/>
       <c r="AX333" s="12" t="s">
+        <v>486</v>
+      </c>
+      <c r="AY333" s="8" t="s">
         <v>489</v>
-      </c>
-      <c r="AY333" s="8" t="s">
-        <v>492</v>
       </c>
       <c r="AZ333" s="8"/>
       <c r="BD333" t="str">
@@ -39155,7 +39175,7 @@
         <v>bad_client</v>
       </c>
       <c r="AT334" t="s">
-        <v>485</v>
+        <v>482</v>
       </c>
       <c r="AU334" t="str">
         <f>IF(AND(Dataset!F334="Savings",Dataset!AT334="eligible"),"YES","NO")</f>
@@ -39163,10 +39183,10 @@
       </c>
       <c r="AW334" s="8"/>
       <c r="AX334" s="12" t="s">
+        <v>487</v>
+      </c>
+      <c r="AY334" s="8" t="s">
         <v>490</v>
-      </c>
-      <c r="AY334" s="8" t="s">
-        <v>493</v>
       </c>
       <c r="AZ334" s="8"/>
       <c r="BD334" t="str">
@@ -39265,7 +39285,7 @@
         <v>good_client</v>
       </c>
       <c r="AT335" t="s">
-        <v>485</v>
+        <v>482</v>
       </c>
       <c r="AU335" t="str">
         <f>IF(AND(Dataset!F335="Savings",Dataset!AT335="eligible"),"YES","NO")</f>
@@ -39273,10 +39293,10 @@
       </c>
       <c r="AW335" s="8"/>
       <c r="AX335" s="12" t="s">
-        <v>490</v>
+        <v>487</v>
       </c>
       <c r="AY335" s="8" t="s">
-        <v>492</v>
+        <v>489</v>
       </c>
       <c r="AZ335" s="8"/>
       <c r="BD335" t="str">
@@ -39375,7 +39395,7 @@
         <v>bad_client</v>
       </c>
       <c r="AT336" t="s">
-        <v>485</v>
+        <v>482</v>
       </c>
       <c r="AU336" t="str">
         <f>IF(AND(Dataset!F336="Savings",Dataset!AT336="eligible"),"YES","NO")</f>
@@ -39383,10 +39403,10 @@
       </c>
       <c r="AW336" s="8"/>
       <c r="AX336" s="12" t="s">
+        <v>487</v>
+      </c>
+      <c r="AY336" s="8" t="s">
         <v>490</v>
-      </c>
-      <c r="AY336" s="8" t="s">
-        <v>493</v>
       </c>
       <c r="AZ336" s="8"/>
       <c r="BD336" t="str">
@@ -39485,7 +39505,7 @@
         <v>good_client</v>
       </c>
       <c r="AT337" t="s">
-        <v>485</v>
+        <v>482</v>
       </c>
       <c r="AU337" t="str">
         <f>IF(AND(Dataset!F337="Savings",Dataset!AT337="eligible"),"YES","NO")</f>
@@ -39493,10 +39513,10 @@
       </c>
       <c r="AW337" s="8"/>
       <c r="AX337" s="12" t="s">
-        <v>490</v>
+        <v>487</v>
       </c>
       <c r="AY337" s="8" t="s">
-        <v>492</v>
+        <v>489</v>
       </c>
       <c r="AZ337" s="8"/>
       <c r="BD337" t="str">
@@ -39595,7 +39615,7 @@
         <v>bad_client</v>
       </c>
       <c r="AT338" t="s">
-        <v>485</v>
+        <v>482</v>
       </c>
       <c r="AU338" t="str">
         <f>IF(AND(Dataset!F338="Savings",Dataset!AT338="eligible"),"YES","NO")</f>
@@ -39603,10 +39623,10 @@
       </c>
       <c r="AW338" s="8"/>
       <c r="AX338" s="12" t="s">
+        <v>487</v>
+      </c>
+      <c r="AY338" s="8" t="s">
         <v>490</v>
-      </c>
-      <c r="AY338" s="8" t="s">
-        <v>493</v>
       </c>
       <c r="AZ338" s="8"/>
       <c r="BD338" t="str">
@@ -39705,7 +39725,7 @@
         <v>good_client</v>
       </c>
       <c r="AT339" t="s">
-        <v>485</v>
+        <v>482</v>
       </c>
       <c r="AU339" t="str">
         <f>IF(AND(Dataset!F339="Savings",Dataset!AT339="eligible"),"YES","NO")</f>
@@ -39713,10 +39733,10 @@
       </c>
       <c r="AW339" s="8"/>
       <c r="AX339" s="12" t="s">
-        <v>490</v>
+        <v>487</v>
       </c>
       <c r="AY339" s="8" t="s">
-        <v>492</v>
+        <v>489</v>
       </c>
       <c r="AZ339" s="8"/>
       <c r="BD339" t="str">
@@ -39815,7 +39835,7 @@
         <v>bad_client</v>
       </c>
       <c r="AT340" t="s">
-        <v>485</v>
+        <v>482</v>
       </c>
       <c r="AU340" t="str">
         <f>IF(AND(Dataset!F340="Savings",Dataset!AT340="eligible"),"YES","NO")</f>
@@ -39823,10 +39843,10 @@
       </c>
       <c r="AW340" s="8"/>
       <c r="AX340" s="12" t="s">
-        <v>489</v>
+        <v>486</v>
       </c>
       <c r="AY340" s="8" t="s">
-        <v>493</v>
+        <v>490</v>
       </c>
       <c r="AZ340" s="8"/>
       <c r="BD340" t="str">
@@ -39925,7 +39945,7 @@
         <v>good_client</v>
       </c>
       <c r="AT341" t="s">
-        <v>485</v>
+        <v>482</v>
       </c>
       <c r="AU341" t="str">
         <f>IF(AND(Dataset!F341="Savings",Dataset!AT341="eligible"),"YES","NO")</f>
@@ -39933,10 +39953,10 @@
       </c>
       <c r="AW341" s="8"/>
       <c r="AX341" s="12" t="s">
+        <v>486</v>
+      </c>
+      <c r="AY341" s="8" t="s">
         <v>489</v>
-      </c>
-      <c r="AY341" s="8" t="s">
-        <v>492</v>
       </c>
       <c r="AZ341" s="8"/>
       <c r="BD341" t="str">
@@ -40035,7 +40055,7 @@
         <v>bad_client</v>
       </c>
       <c r="AT342" t="s">
-        <v>485</v>
+        <v>482</v>
       </c>
       <c r="AU342" t="str">
         <f>IF(AND(Dataset!F342="Savings",Dataset!AT342="eligible"),"YES","NO")</f>
@@ -40043,10 +40063,10 @@
       </c>
       <c r="AW342" s="8"/>
       <c r="AX342" s="12" t="s">
-        <v>489</v>
+        <v>486</v>
       </c>
       <c r="AY342" s="8" t="s">
-        <v>493</v>
+        <v>490</v>
       </c>
       <c r="AZ342" s="8"/>
       <c r="BD342" t="str">
@@ -40145,7 +40165,7 @@
         <v>bad_client</v>
       </c>
       <c r="AT343" t="s">
-        <v>485</v>
+        <v>482</v>
       </c>
       <c r="AU343" t="str">
         <f>IF(AND(Dataset!F343="Savings",Dataset!AT343="eligible"),"YES","NO")</f>
@@ -40153,10 +40173,10 @@
       </c>
       <c r="AW343" s="8"/>
       <c r="AX343" s="12" t="s">
+        <v>486</v>
+      </c>
+      <c r="AY343" s="8" t="s">
         <v>489</v>
-      </c>
-      <c r="AY343" s="8" t="s">
-        <v>492</v>
       </c>
       <c r="AZ343" s="8"/>
       <c r="BD343" t="str">
@@ -40255,7 +40275,7 @@
         <v>bad_client</v>
       </c>
       <c r="AT344" t="s">
-        <v>485</v>
+        <v>482</v>
       </c>
       <c r="AU344" t="str">
         <f>IF(AND(Dataset!F344="Savings",Dataset!AT344="eligible"),"YES","NO")</f>
@@ -40263,10 +40283,10 @@
       </c>
       <c r="AW344" s="8"/>
       <c r="AX344" s="12" t="s">
-        <v>489</v>
+        <v>486</v>
       </c>
       <c r="AY344" s="8" t="s">
-        <v>493</v>
+        <v>490</v>
       </c>
       <c r="AZ344" s="8"/>
       <c r="BD344" t="str">
@@ -40365,7 +40385,7 @@
         <v>bad_client</v>
       </c>
       <c r="AT345" t="s">
-        <v>485</v>
+        <v>482</v>
       </c>
       <c r="AU345" t="str">
         <f>IF(AND(Dataset!F345="Savings",Dataset!AT345="eligible"),"YES","NO")</f>
@@ -40373,10 +40393,10 @@
       </c>
       <c r="AW345" s="8"/>
       <c r="AX345" s="12" t="s">
+        <v>486</v>
+      </c>
+      <c r="AY345" s="8" t="s">
         <v>489</v>
-      </c>
-      <c r="AY345" s="8" t="s">
-        <v>492</v>
       </c>
       <c r="AZ345" s="8"/>
       <c r="BD345" t="str">
@@ -40475,7 +40495,7 @@
         <v>bad_client</v>
       </c>
       <c r="AT346" t="s">
-        <v>485</v>
+        <v>482</v>
       </c>
       <c r="AU346" t="str">
         <f>IF(AND(Dataset!F346="Savings",Dataset!AT346="eligible"),"YES","NO")</f>
@@ -40483,10 +40503,10 @@
       </c>
       <c r="AW346" s="8"/>
       <c r="AX346" s="12" t="s">
+        <v>487</v>
+      </c>
+      <c r="AY346" s="8" t="s">
         <v>490</v>
-      </c>
-      <c r="AY346" s="8" t="s">
-        <v>493</v>
       </c>
       <c r="AZ346" s="8"/>
       <c r="BD346" t="str">
@@ -40585,7 +40605,7 @@
         <v>bad_client</v>
       </c>
       <c r="AT347" t="s">
-        <v>485</v>
+        <v>482</v>
       </c>
       <c r="AU347" t="str">
         <f>IF(AND(Dataset!F347="Savings",Dataset!AT347="eligible"),"YES","NO")</f>
@@ -40593,10 +40613,10 @@
       </c>
       <c r="AW347" s="8"/>
       <c r="AX347" s="12" t="s">
-        <v>490</v>
+        <v>487</v>
       </c>
       <c r="AY347" s="8" t="s">
-        <v>492</v>
+        <v>489</v>
       </c>
       <c r="AZ347" s="8"/>
       <c r="BD347" t="str">
@@ -40695,7 +40715,7 @@
         <v>bad_client</v>
       </c>
       <c r="AT348" t="s">
-        <v>485</v>
+        <v>482</v>
       </c>
       <c r="AU348" t="str">
         <f>IF(AND(Dataset!F348="Savings",Dataset!AT348="eligible"),"YES","NO")</f>
@@ -40703,10 +40723,10 @@
       </c>
       <c r="AW348" s="8"/>
       <c r="AX348" s="12" t="s">
+        <v>487</v>
+      </c>
+      <c r="AY348" s="8" t="s">
         <v>490</v>
-      </c>
-      <c r="AY348" s="8" t="s">
-        <v>493</v>
       </c>
       <c r="AZ348" s="8"/>
       <c r="BD348" t="str">
@@ -40805,7 +40825,7 @@
         <v>bad_client</v>
       </c>
       <c r="AT349" t="s">
-        <v>485</v>
+        <v>482</v>
       </c>
       <c r="AU349" t="str">
         <f>IF(AND(Dataset!F349="Savings",Dataset!AT349="eligible"),"YES","NO")</f>
@@ -40813,10 +40833,10 @@
       </c>
       <c r="AW349" s="8"/>
       <c r="AX349" s="12" t="s">
-        <v>490</v>
+        <v>487</v>
       </c>
       <c r="AY349" s="8" t="s">
-        <v>492</v>
+        <v>489</v>
       </c>
       <c r="AZ349" s="8"/>
       <c r="BD349" t="str">
@@ -40915,7 +40935,7 @@
         <v>bad_client</v>
       </c>
       <c r="AT350" t="s">
-        <v>485</v>
+        <v>482</v>
       </c>
       <c r="AU350" t="str">
         <f>IF(AND(Dataset!F350="Savings",Dataset!AT350="eligible"),"YES","NO")</f>
@@ -40923,10 +40943,10 @@
       </c>
       <c r="AW350" s="8"/>
       <c r="AX350" s="12" t="s">
+        <v>487</v>
+      </c>
+      <c r="AY350" s="8" t="s">
         <v>490</v>
-      </c>
-      <c r="AY350" s="8" t="s">
-        <v>493</v>
       </c>
       <c r="AZ350" s="8"/>
       <c r="BD350" t="str">
@@ -41180,12 +41200,12 @@
   <dimension ref="A1:P46"/>
   <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <sheetData>
-    <row r="1" spans="1:7" ht="18" x14ac:dyDescent="0.35">
+    <row r="1" spans="1:12" ht="18" x14ac:dyDescent="0.35">
       <c r="B1" s="6" t="s">
         <v>346</v>
       </c>
     </row>
-    <row r="2" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="2" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A2" t="s">
         <v>83</v>
       </c>
@@ -41193,24 +41213,24 @@
         <v>345</v>
       </c>
     </row>
-    <row r="3" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="3" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A3" t="s">
         <v>347</v>
       </c>
       <c r="B3" t="s">
-        <v>467</v>
-      </c>
-    </row>
-    <row r="4" spans="1:7" x14ac:dyDescent="0.3">
+        <v>464</v>
+      </c>
+    </row>
+    <row r="4" spans="1:12" x14ac:dyDescent="0.3">
       <c r="B4" t="s">
-        <v>468</v>
+        <v>465</v>
       </c>
       <c r="F4" s="7">
         <f>AVERAGE(Dataset!H2:H350)</f>
         <v>60260.744985673351</v>
       </c>
     </row>
-    <row r="7" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="7" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A7" t="s">
         <v>84</v>
       </c>
@@ -41218,19 +41238,19 @@
         <v>348</v>
       </c>
     </row>
-    <row r="8" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="8" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A8" t="s">
         <v>349</v>
       </c>
       <c r="B8" t="s">
-        <v>395</v>
+        <v>394</v>
       </c>
       <c r="F8" s="7">
         <f>MEDIAN(Dataset!G2:G350)</f>
         <v>5500</v>
       </c>
     </row>
-    <row r="10" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="10" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A10" t="s">
         <v>85</v>
       </c>
@@ -41238,42 +41258,52 @@
         <v>350</v>
       </c>
     </row>
-    <row r="11" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="11" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A11" t="s">
         <v>351</v>
       </c>
       <c r="B11" t="s">
-        <v>394</v>
+        <v>393</v>
       </c>
       <c r="G11" s="7">
         <f>SMALL(Dataset!J2:J350,5)</f>
         <v>0</v>
       </c>
     </row>
-    <row r="12" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="12" spans="1:12" x14ac:dyDescent="0.3">
       <c r="B12" t="s">
         <v>352</v>
       </c>
     </row>
-    <row r="14" spans="1:7" x14ac:dyDescent="0.3">
-      <c r="A14" t="s">
+    <row r="14" spans="1:12" x14ac:dyDescent="0.3">
+      <c r="A14" s="14" t="s">
         <v>86</v>
       </c>
       <c r="B14" t="s">
         <v>353</v>
       </c>
     </row>
-    <row r="15" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="15" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A15" t="s">
         <v>354</v>
       </c>
       <c r="B15" t="s">
-        <v>393</v>
+        <v>392</v>
       </c>
       <c r="F15" s="7">
         <f>LARGE(Dataset!K2:K350,3)</f>
         <v>750</v>
       </c>
+      <c r="G15" t="s">
+        <v>493</v>
+      </c>
+      <c r="H15" t="s">
+        <v>492</v>
+      </c>
+      <c r="L15" s="7">
+        <f>LARGE(_xlfn.UNIQUE(Dataset!K2:K350),3)</f>
+        <v>730</v>
+      </c>
     </row>
     <row r="17" spans="1:16" x14ac:dyDescent="0.3">
       <c r="A17" t="s">
@@ -41288,7 +41318,7 @@
         <v>356</v>
       </c>
       <c r="B18" t="s">
-        <v>392</v>
+        <v>391</v>
       </c>
       <c r="F18" s="7">
         <f>_xlfn.MODE.SNGL(Dataset!K2:K350)</f>
@@ -41308,11 +41338,11 @@
         <v>357</v>
       </c>
       <c r="B21" t="s">
-        <v>391</v>
+        <v>494</v>
       </c>
       <c r="P21" s="7">
-        <f>COUNTIFS(Dataset!D2:D350,"&gt;30",Dataset!N2:N350,Dataset!N337,Dataset!M2:M350,Dataset!M334)</f>
-        <v>41</v>
+        <f>COUNTIFS(Dataset!D2:D350,"&gt;30",Dataset!E2:E350,"F",Dataset!M2:M350,"Premium",Dataset!N2:N350,"Active")</f>
+        <v>0</v>
       </c>
     </row>
     <row r="23" spans="1:16" x14ac:dyDescent="0.3">
@@ -41364,7 +41394,7 @@
       </c>
     </row>
     <row r="32" spans="1:16" x14ac:dyDescent="0.3">
-      <c r="A32" s="8" t="s">
+      <c r="A32" s="14" t="s">
         <v>92</v>
       </c>
       <c r="B32" t="s">
@@ -41501,7 +41531,7 @@
     </row>
     <row r="4" spans="1:13" x14ac:dyDescent="0.3">
       <c r="B4" t="s">
-        <v>474</v>
+        <v>471</v>
       </c>
       <c r="M4" s="7" cm="1">
         <f t="array" ref="M4">_xlfn.PERCENTILE.INC(IF(Dataset!N2:N350="Active",Dataset!H2:H350),0.5)</f>
@@ -41513,7 +41543,7 @@
         <v>84</v>
       </c>
       <c r="B6" t="s">
-        <v>396</v>
+        <v>395</v>
       </c>
     </row>
     <row r="7" spans="1:13" x14ac:dyDescent="0.3">
@@ -41521,7 +41551,7 @@
         <v>349</v>
       </c>
       <c r="B7" t="s">
-        <v>397</v>
+        <v>396</v>
       </c>
       <c r="M7" s="7">
         <f>COUNTIF(Dataset!I2:I350,Dataset!I335)</f>
@@ -41530,7 +41560,7 @@
     </row>
     <row r="8" spans="1:13" x14ac:dyDescent="0.3">
       <c r="B8" t="s">
-        <v>398</v>
+        <v>397</v>
       </c>
       <c r="M8" s="7">
         <f>MAX(Dataset!J2:J350)</f>
@@ -41542,7 +41572,7 @@
         <v>85</v>
       </c>
       <c r="B10" t="s">
-        <v>399</v>
+        <v>398</v>
       </c>
     </row>
     <row r="11" spans="1:13" x14ac:dyDescent="0.3">
@@ -41550,19 +41580,19 @@
         <v>351</v>
       </c>
       <c r="B11" t="s">
-        <v>400</v>
+        <v>495</v>
       </c>
       <c r="M11" s="7" cm="1">
-        <f t="array" ref="M11">SMALL(IF(Dataset!I2:I350="No",Dataset!G2:G350),3)</f>
-        <v>1500</v>
+        <f t="array" ref="M11">SMALL(_xlfn.UNIQUE(IF(Dataset!I2:I350="no",Dataset!G2:G350)),3)</f>
+        <v>2200</v>
       </c>
     </row>
     <row r="13" spans="1:13" x14ac:dyDescent="0.3">
-      <c r="A13" s="8" t="s">
+      <c r="A13" s="13" t="s">
         <v>86</v>
       </c>
       <c r="B13" t="s">
-        <v>401</v>
+        <v>399</v>
       </c>
     </row>
     <row r="14" spans="1:13" x14ac:dyDescent="0.3">
@@ -41570,7 +41600,7 @@
         <v>354</v>
       </c>
       <c r="B14" t="s">
-        <v>402</v>
+        <v>400</v>
       </c>
     </row>
     <row r="16" spans="1:13" x14ac:dyDescent="0.3">
@@ -41578,19 +41608,19 @@
         <v>87</v>
       </c>
       <c r="B16" t="s">
-        <v>403</v>
+        <v>401</v>
       </c>
     </row>
     <row r="17" spans="1:15" x14ac:dyDescent="0.3">
       <c r="A17" t="s">
-        <v>404</v>
+        <v>402</v>
       </c>
       <c r="B17" t="s">
-        <v>405</v>
+        <v>403</v>
       </c>
       <c r="O17" s="7" cm="1">
-        <f t="array" ref="O17">SMALL(IF(Dataset!E2:E350="F",Dataset!H2:H350),2)</f>
-        <v>45000</v>
+        <f t="array" ref="O17">SMALL(_xlfn.UNIQUE(IF(Dataset!E2:E350="F",Dataset!H2:H350)),2)</f>
+        <v>47000</v>
       </c>
     </row>
     <row r="19" spans="1:15" x14ac:dyDescent="0.3">
@@ -41598,15 +41628,15 @@
         <v>88</v>
       </c>
       <c r="B19" t="s">
-        <v>406</v>
+        <v>404</v>
       </c>
     </row>
     <row r="20" spans="1:15" x14ac:dyDescent="0.3">
       <c r="A20" t="s">
-        <v>407</v>
+        <v>405</v>
       </c>
       <c r="B20" t="s">
-        <v>408</v>
+        <v>406</v>
       </c>
       <c r="L20" s="7" cm="1">
         <f t="array" ref="L20">_xlfn.MODE.MULT(Dataset!G2:G350)</f>
@@ -41615,7 +41645,7 @@
     </row>
     <row r="21" spans="1:15" x14ac:dyDescent="0.3">
       <c r="B21" t="s">
-        <v>475</v>
+        <v>472</v>
       </c>
       <c r="L21" s="7">
         <f>AVERAGE(Dataset!G2:G350)</f>
@@ -41627,15 +41657,15 @@
         <v>89</v>
       </c>
       <c r="B23" t="s">
-        <v>409</v>
+        <v>407</v>
       </c>
     </row>
     <row r="24" spans="1:15" x14ac:dyDescent="0.3">
       <c r="A24" t="s">
-        <v>410</v>
+        <v>408</v>
       </c>
       <c r="B24" t="s">
-        <v>411</v>
+        <v>409</v>
       </c>
       <c r="K24" s="7">
         <f>_xlfn.PERCENTILE.INC(Dataset!H2:H350,0.75)</f>
@@ -41644,7 +41674,7 @@
     </row>
     <row r="25" spans="1:15" x14ac:dyDescent="0.3">
       <c r="B25" t="s">
-        <v>412</v>
+        <v>410</v>
       </c>
       <c r="K25" s="7">
         <f>_xlfn.PERCENTILE.INC(Dataset!G2:G350,0.75)</f>
@@ -41656,7 +41686,7 @@
         <v>90</v>
       </c>
       <c r="B27" t="s">
-        <v>413</v>
+        <v>411</v>
       </c>
     </row>
     <row r="28" spans="1:15" x14ac:dyDescent="0.3">
@@ -41664,7 +41694,7 @@
         <v>366</v>
       </c>
       <c r="B28" t="s">
-        <v>414</v>
+        <v>412</v>
       </c>
     </row>
     <row r="30" spans="1:15" x14ac:dyDescent="0.3">
@@ -41672,7 +41702,7 @@
         <v>91</v>
       </c>
       <c r="B30" t="s">
-        <v>415</v>
+        <v>413</v>
       </c>
     </row>
     <row r="31" spans="1:15" x14ac:dyDescent="0.3">
@@ -41680,7 +41710,7 @@
         <v>370</v>
       </c>
       <c r="B31" t="s">
-        <v>416</v>
+        <v>414</v>
       </c>
     </row>
     <row r="33" spans="1:13" x14ac:dyDescent="0.3">
@@ -41688,7 +41718,7 @@
         <v>92</v>
       </c>
       <c r="B33" t="s">
-        <v>417</v>
+        <v>415</v>
       </c>
     </row>
     <row r="34" spans="1:13" x14ac:dyDescent="0.3">
@@ -41696,7 +41726,7 @@
         <v>374</v>
       </c>
       <c r="B34" t="s">
-        <v>418</v>
+        <v>416</v>
       </c>
     </row>
     <row r="36" spans="1:13" x14ac:dyDescent="0.3">
@@ -41704,15 +41734,15 @@
         <v>93</v>
       </c>
       <c r="B36" t="s">
-        <v>419</v>
+        <v>417</v>
       </c>
     </row>
     <row r="37" spans="1:13" x14ac:dyDescent="0.3">
       <c r="A37" t="s">
-        <v>420</v>
+        <v>418</v>
       </c>
       <c r="B37" t="s">
-        <v>421</v>
+        <v>419</v>
       </c>
       <c r="M37" s="7">
         <f>SUMIF(Dataset!S2:S350,Dataset!S3,Dataset!H2:H350)</f>
@@ -41724,7 +41754,7 @@
         <v>94</v>
       </c>
       <c r="B39" t="s">
-        <v>422</v>
+        <v>420</v>
       </c>
     </row>
     <row r="40" spans="1:13" x14ac:dyDescent="0.3">
@@ -41732,7 +41762,7 @@
         <v>380</v>
       </c>
       <c r="B40" t="s">
-        <v>423</v>
+        <v>421</v>
       </c>
     </row>
     <row r="42" spans="1:13" x14ac:dyDescent="0.3">
@@ -41740,15 +41770,15 @@
         <v>95</v>
       </c>
       <c r="B42" t="s">
-        <v>424</v>
+        <v>422</v>
       </c>
     </row>
     <row r="43" spans="1:13" x14ac:dyDescent="0.3">
       <c r="A43" t="s">
-        <v>425</v>
+        <v>423</v>
       </c>
       <c r="B43" t="s">
-        <v>426</v>
+        <v>424</v>
       </c>
       <c r="L43" s="7">
         <f>COUNTIF(Dataset!L2:L350,Dataset!L339)</f>
@@ -41757,7 +41787,7 @@
     </row>
     <row r="44" spans="1:13" x14ac:dyDescent="0.3">
       <c r="B44" t="s">
-        <v>427</v>
+        <v>425</v>
       </c>
       <c r="L44" s="7">
         <f>SUMIF(Dataset!L2:L350,Dataset!L339,Dataset!G2:G350)</f>
@@ -41766,7 +41796,7 @@
     </row>
     <row r="45" spans="1:13" x14ac:dyDescent="0.3">
       <c r="B45" t="s">
-        <v>428</v>
+        <v>426</v>
       </c>
       <c r="L45" s="7">
         <f>_xlfn.MAXIFS(Dataset!G2:G350,Dataset!L2:L350,Dataset!L331)</f>
@@ -41796,7 +41826,7 @@
         <v>83</v>
       </c>
       <c r="B2" t="s">
-        <v>429</v>
+        <v>427</v>
       </c>
     </row>
     <row r="3" spans="1:21" x14ac:dyDescent="0.3">
@@ -41804,7 +41834,7 @@
         <v>347</v>
       </c>
       <c r="B3" t="s">
-        <v>430</v>
+        <v>428</v>
       </c>
       <c r="U3" s="7">
         <f>_xlfn.MAXIFS(Dataset!G2:G350,Dataset!E2:E350,Dataset!E330,Dataset!L2:L350,Dataset!L334,Dataset!K2:K350,"&gt;500")</f>
@@ -41816,7 +41846,7 @@
         <v>84</v>
       </c>
       <c r="B5" t="s">
-        <v>431</v>
+        <v>429</v>
       </c>
     </row>
     <row r="6" spans="1:21" x14ac:dyDescent="0.3">
@@ -41824,7 +41854,7 @@
         <v>349</v>
       </c>
       <c r="B6" t="s">
-        <v>432</v>
+        <v>430</v>
       </c>
     </row>
     <row r="8" spans="1:21" x14ac:dyDescent="0.3">
@@ -41832,7 +41862,7 @@
         <v>85</v>
       </c>
       <c r="B8" t="s">
-        <v>433</v>
+        <v>431</v>
       </c>
     </row>
     <row r="9" spans="1:21" x14ac:dyDescent="0.3">
@@ -41840,16 +41870,16 @@
         <v>351</v>
       </c>
       <c r="B9" t="s">
-        <v>434</v>
+        <v>496</v>
       </c>
       <c r="S9" s="7">
-        <f>_xlfn.MINIFS(Dataset!G2:G350,Dataset!E2:E350,Dataset!E330,Dataset!N2:N350,Dataset!N339)</f>
-        <v>4500</v>
+        <f>_xlfn.MINIFS(Dataset!G2:G350,Dataset!E2:E350,"F",Dataset!N2:N350,"Inactive")</f>
+        <v>1500</v>
       </c>
     </row>
     <row r="10" spans="1:21" x14ac:dyDescent="0.3">
       <c r="B10" t="s">
-        <v>435</v>
+        <v>432</v>
       </c>
       <c r="S10" s="7">
         <f>COUNTIF(Dataset!N2:N350,Dataset!N337)</f>
@@ -41861,7 +41891,7 @@
         <v>86</v>
       </c>
       <c r="B12" t="s">
-        <v>436</v>
+        <v>433</v>
       </c>
     </row>
     <row r="13" spans="1:21" x14ac:dyDescent="0.3">
@@ -41869,7 +41899,7 @@
         <v>354</v>
       </c>
       <c r="B13" t="s">
-        <v>437</v>
+        <v>434</v>
       </c>
     </row>
     <row r="15" spans="1:21" x14ac:dyDescent="0.3">
@@ -41877,7 +41907,7 @@
         <v>87</v>
       </c>
       <c r="B15" t="s">
-        <v>438</v>
+        <v>435</v>
       </c>
     </row>
     <row r="16" spans="1:21" x14ac:dyDescent="0.3">
@@ -41885,7 +41915,7 @@
         <v>356</v>
       </c>
       <c r="B16" t="s">
-        <v>466</v>
+        <v>463</v>
       </c>
       <c r="N16" s="7">
         <f>_xlfn.MAXIFS(Dataset!G2:G350,Dataset!AT2:AT350,"eligible")</f>
@@ -41894,15 +41924,15 @@
     </row>
     <row r="17" spans="1:18" x14ac:dyDescent="0.3">
       <c r="B17" t="s">
-        <v>486</v>
+        <v>483</v>
       </c>
     </row>
     <row r="19" spans="1:18" x14ac:dyDescent="0.3">
-      <c r="A19" s="8" t="s">
+      <c r="A19" s="14" t="s">
         <v>88</v>
       </c>
       <c r="B19" t="s">
-        <v>439</v>
+        <v>436</v>
       </c>
     </row>
     <row r="20" spans="1:18" x14ac:dyDescent="0.3">
@@ -41910,15 +41940,15 @@
         <v>357</v>
       </c>
       <c r="B20" t="s">
-        <v>440</v>
+        <v>437</v>
       </c>
     </row>
     <row r="22" spans="1:18" x14ac:dyDescent="0.3">
-      <c r="A22" s="8" t="s">
+      <c r="A22" s="14" t="s">
         <v>89</v>
       </c>
       <c r="B22" t="s">
-        <v>441</v>
+        <v>438</v>
       </c>
     </row>
     <row r="23" spans="1:18" x14ac:dyDescent="0.3">
@@ -41926,7 +41956,7 @@
         <v>361</v>
       </c>
       <c r="B23" t="s">
-        <v>442</v>
+        <v>439</v>
       </c>
     </row>
     <row r="25" spans="1:18" x14ac:dyDescent="0.3">
@@ -41934,7 +41964,7 @@
         <v>90</v>
       </c>
       <c r="B25" t="s">
-        <v>443</v>
+        <v>440</v>
       </c>
     </row>
     <row r="26" spans="1:18" x14ac:dyDescent="0.3">
@@ -41942,7 +41972,7 @@
         <v>366</v>
       </c>
       <c r="B26" t="s">
-        <v>444</v>
+        <v>441</v>
       </c>
       <c r="R26" s="7" cm="1">
         <f t="array" ref="R26">_xlfn.PERCENTILE.INC(IF(Dataset!L2:L350="Mutual Funds",Dataset!G2:G350),0.2)</f>
@@ -41954,7 +41984,7 @@
         <v>91</v>
       </c>
       <c r="B28" t="s">
-        <v>445</v>
+        <v>442</v>
       </c>
     </row>
     <row r="29" spans="1:18" x14ac:dyDescent="0.3">
@@ -41962,7 +41992,7 @@
         <v>370</v>
       </c>
       <c r="B29" t="s">
-        <v>446</v>
+        <v>443</v>
       </c>
       <c r="O29" s="7">
         <f>_xlfn.MAXIFS(Dataset!H2:H350,Dataset!L2:L350,Dataset!L2)</f>
@@ -41971,7 +42001,7 @@
     </row>
     <row r="30" spans="1:18" x14ac:dyDescent="0.3">
       <c r="B30" t="s">
-        <v>447</v>
+        <v>444</v>
       </c>
       <c r="O30" s="7">
         <f>_xlfn.MAXIFS(Dataset!H2:H350,Dataset!L2:L350,Dataset!L3)</f>
@@ -41980,7 +42010,7 @@
     </row>
     <row r="31" spans="1:18" x14ac:dyDescent="0.3">
       <c r="B31" t="s">
-        <v>448</v>
+        <v>445</v>
       </c>
       <c r="O31" s="7">
         <f>_xlfn.MAXIFS(Dataset!H2:H350,Dataset!L2:L350,Dataset!L5)</f>
@@ -41989,7 +42019,7 @@
     </row>
     <row r="32" spans="1:18" x14ac:dyDescent="0.3">
       <c r="B32" t="s">
-        <v>449</v>
+        <v>446</v>
       </c>
       <c r="O32" s="7">
         <f>_xlfn.MAXIFS(Dataset!H2:H350,Dataset!L2:L350,Dataset!L4)</f>
@@ -42001,7 +42031,7 @@
         <v>92</v>
       </c>
       <c r="B34" t="s">
-        <v>450</v>
+        <v>447</v>
       </c>
     </row>
     <row r="35" spans="1:17" x14ac:dyDescent="0.3">
@@ -42009,7 +42039,7 @@
         <v>374</v>
       </c>
       <c r="B35" t="s">
-        <v>451</v>
+        <v>448</v>
       </c>
       <c r="O35" s="7">
         <f>_xlfn.MAXIFS(Dataset!H2:H350,Dataset!M2:M350,Dataset!M2)</f>
@@ -42018,7 +42048,7 @@
     </row>
     <row r="36" spans="1:17" x14ac:dyDescent="0.3">
       <c r="B36" t="s">
-        <v>452</v>
+        <v>449</v>
       </c>
       <c r="O36" s="7">
         <f>_xlfn.MAXIFS(Dataset!H2:H350,Dataset!M2:M350,Dataset!M3)</f>
@@ -42027,7 +42057,7 @@
     </row>
     <row r="37" spans="1:17" x14ac:dyDescent="0.3">
       <c r="B37" t="s">
-        <v>453</v>
+        <v>450</v>
       </c>
       <c r="O37" s="7">
         <f>_xlfn.MAXIFS(Dataset!H2:H350,Dataset!M2:M350,Dataset!M4)</f>
@@ -42039,7 +42069,7 @@
         <v>93</v>
       </c>
       <c r="B39" t="s">
-        <v>454</v>
+        <v>451</v>
       </c>
     </row>
     <row r="40" spans="1:17" x14ac:dyDescent="0.3">
@@ -42047,7 +42077,7 @@
         <v>376</v>
       </c>
       <c r="B40" t="s">
-        <v>455</v>
+        <v>452</v>
       </c>
       <c r="N40" s="7" cm="1">
         <f t="array" ref="N40">SMALL(IF(Dataset!E2:E350="F",Dataset!H2:H350),2)</f>
@@ -42059,7 +42089,7 @@
         <v>94</v>
       </c>
       <c r="B42" t="s">
-        <v>456</v>
+        <v>453</v>
       </c>
     </row>
     <row r="43" spans="1:17" x14ac:dyDescent="0.3">
@@ -42067,16 +42097,16 @@
         <v>380</v>
       </c>
       <c r="B43" t="s">
-        <v>457</v>
+        <v>454</v>
       </c>
       <c r="N43" s="7">
-        <f>COUNTIF(Dataset!H2:H350,"&gt;6000")</f>
-        <v>349</v>
+        <f>COUNTIF(Dataset!G2:G350,"&gt;6000")</f>
+        <v>136</v>
       </c>
     </row>
     <row r="44" spans="1:17" x14ac:dyDescent="0.3">
       <c r="B44" t="s">
-        <v>458</v>
+        <v>455</v>
       </c>
       <c r="Q44" s="7">
         <f>MAX(Dataset!H2:H350)</f>
@@ -42088,7 +42118,7 @@
         <v>95</v>
       </c>
       <c r="B46" t="s">
-        <v>459</v>
+        <v>456</v>
       </c>
     </row>
     <row r="47" spans="1:17" x14ac:dyDescent="0.3">
@@ -42096,7 +42126,7 @@
         <v>383</v>
       </c>
       <c r="B47" t="s">
-        <v>460</v>
+        <v>457</v>
       </c>
       <c r="M47" s="7">
         <f>SUMIF(Dataset!F2:F350,Dataset!F330,Dataset!H2:H350)</f>
@@ -42105,7 +42135,7 @@
     </row>
     <row r="48" spans="1:17" x14ac:dyDescent="0.3">
       <c r="B48" t="s">
-        <v>461</v>
+        <v>458</v>
       </c>
       <c r="M48" s="7">
         <f>_xlfn.MAXIFS(Dataset!H2:H350,Dataset!F2:F350,Dataset!F340)</f>
@@ -42117,20 +42147,20 @@
         <v>96</v>
       </c>
       <c r="B50" t="s">
-        <v>462</v>
+        <v>459</v>
       </c>
     </row>
     <row r="51" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A51" t="s">
-        <v>463</v>
+        <v>460</v>
       </c>
       <c r="B51" t="s">
-        <v>464</v>
+        <v>461</v>
       </c>
     </row>
     <row r="52" spans="1:5" x14ac:dyDescent="0.3">
       <c r="B52" t="s">
-        <v>465</v>
+        <v>462</v>
       </c>
       <c r="E52" s="7">
         <f>_xlfn.MINIFS(Dataset!F1:F349,Dataset!H1:H349,Dataset!H1,Dataset!I1:I349,Dataset!I2)</f>
